--- a/pages/TP_Master.xlsx
+++ b/pages/TP_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samb\CNZPD\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1817722-B16A-4E74-9842-7E8D9B5682A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE596BFB-52E4-4080-B172-2E7BE06BC95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9135" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I391"/>
+  <dimension ref="A1:I521"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -11345,6 +11345,396 @@
         <v>12</v>
       </c>
     </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B392" s="1"/>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B393" s="1"/>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B394" s="1"/>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B395" s="1"/>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B396" s="1"/>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B397" s="1"/>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B398" s="1"/>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B399" s="1"/>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B400" s="1"/>
+    </row>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B401" s="1"/>
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B402" s="1"/>
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B403" s="1"/>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B404" s="1"/>
+    </row>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B405" s="1"/>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B406" s="1"/>
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B407" s="1"/>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B408" s="1"/>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B409" s="1"/>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B410" s="1"/>
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B411" s="1"/>
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B412" s="1"/>
+    </row>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B413" s="1"/>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B414" s="1"/>
+    </row>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B415" s="1"/>
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B416" s="1"/>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B417" s="1"/>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B418" s="1"/>
+    </row>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B419" s="1"/>
+    </row>
+    <row r="420" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B420" s="1"/>
+    </row>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B421" s="1"/>
+    </row>
+    <row r="422" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B422" s="1"/>
+    </row>
+    <row r="423" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B423" s="1"/>
+    </row>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B424" s="1"/>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B425" s="1"/>
+    </row>
+    <row r="426" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B426" s="1"/>
+    </row>
+    <row r="427" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B427" s="1"/>
+    </row>
+    <row r="428" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B428" s="1"/>
+    </row>
+    <row r="429" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B429" s="1"/>
+    </row>
+    <row r="430" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B430" s="1"/>
+    </row>
+    <row r="431" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B431" s="1"/>
+    </row>
+    <row r="432" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B432" s="1"/>
+    </row>
+    <row r="433" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B433" s="1"/>
+    </row>
+    <row r="434" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B434" s="1"/>
+    </row>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B435" s="1"/>
+    </row>
+    <row r="436" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B436" s="1"/>
+    </row>
+    <row r="437" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B437" s="1"/>
+    </row>
+    <row r="438" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B438" s="1"/>
+    </row>
+    <row r="439" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B439" s="1"/>
+    </row>
+    <row r="440" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B440" s="1"/>
+    </row>
+    <row r="441" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B441" s="1"/>
+    </row>
+    <row r="442" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B442" s="1"/>
+    </row>
+    <row r="443" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B443" s="1"/>
+    </row>
+    <row r="444" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B444" s="1"/>
+    </row>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B445" s="1"/>
+    </row>
+    <row r="446" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B446" s="1"/>
+    </row>
+    <row r="447" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B447" s="1"/>
+    </row>
+    <row r="448" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B448" s="1"/>
+    </row>
+    <row r="449" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B449" s="1"/>
+    </row>
+    <row r="450" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B450" s="1"/>
+    </row>
+    <row r="451" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B451" s="1"/>
+    </row>
+    <row r="452" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B452" s="1"/>
+    </row>
+    <row r="453" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B453" s="1"/>
+    </row>
+    <row r="454" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B454" s="1"/>
+    </row>
+    <row r="455" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B455" s="1"/>
+    </row>
+    <row r="456" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B456" s="1"/>
+    </row>
+    <row r="457" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B457" s="1"/>
+    </row>
+    <row r="458" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B458" s="1"/>
+    </row>
+    <row r="459" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B459" s="1"/>
+    </row>
+    <row r="460" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B460" s="1"/>
+    </row>
+    <row r="461" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B461" s="1"/>
+    </row>
+    <row r="462" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B462" s="1"/>
+    </row>
+    <row r="463" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B463" s="1"/>
+    </row>
+    <row r="464" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B464" s="1"/>
+    </row>
+    <row r="465" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B465" s="1"/>
+    </row>
+    <row r="466" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B466" s="1"/>
+    </row>
+    <row r="467" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B467" s="1"/>
+    </row>
+    <row r="468" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B468" s="1"/>
+    </row>
+    <row r="469" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B469" s="1"/>
+    </row>
+    <row r="470" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B470" s="1"/>
+    </row>
+    <row r="471" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B471" s="1"/>
+    </row>
+    <row r="472" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B472" s="1"/>
+    </row>
+    <row r="473" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B473" s="1"/>
+    </row>
+    <row r="474" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B474" s="1"/>
+    </row>
+    <row r="475" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B475" s="1"/>
+    </row>
+    <row r="476" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B476" s="1"/>
+    </row>
+    <row r="477" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B477" s="1"/>
+    </row>
+    <row r="478" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B478" s="1"/>
+    </row>
+    <row r="479" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B479" s="1"/>
+    </row>
+    <row r="480" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B480" s="1"/>
+    </row>
+    <row r="481" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B481" s="1"/>
+    </row>
+    <row r="482" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B482" s="1"/>
+    </row>
+    <row r="483" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B483" s="1"/>
+    </row>
+    <row r="484" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B484" s="1"/>
+    </row>
+    <row r="485" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B485" s="1"/>
+    </row>
+    <row r="486" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B486" s="1"/>
+    </row>
+    <row r="487" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B487" s="1"/>
+    </row>
+    <row r="488" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B488" s="1"/>
+    </row>
+    <row r="489" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B489" s="1"/>
+    </row>
+    <row r="490" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B490" s="1"/>
+    </row>
+    <row r="491" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B491" s="1"/>
+    </row>
+    <row r="492" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B492" s="1"/>
+    </row>
+    <row r="493" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B493" s="1"/>
+    </row>
+    <row r="494" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B494" s="1"/>
+    </row>
+    <row r="495" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B495" s="1"/>
+    </row>
+    <row r="496" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B496" s="1"/>
+    </row>
+    <row r="497" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B497" s="1"/>
+    </row>
+    <row r="498" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B498" s="1"/>
+    </row>
+    <row r="499" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B499" s="1"/>
+    </row>
+    <row r="500" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B500" s="1"/>
+    </row>
+    <row r="501" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B501" s="1"/>
+    </row>
+    <row r="502" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B502" s="1"/>
+    </row>
+    <row r="503" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B503" s="1"/>
+    </row>
+    <row r="504" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B504" s="1"/>
+    </row>
+    <row r="505" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B505" s="1"/>
+    </row>
+    <row r="506" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B506" s="1"/>
+    </row>
+    <row r="507" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B507" s="1"/>
+    </row>
+    <row r="508" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B508" s="1"/>
+    </row>
+    <row r="509" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B509" s="1"/>
+    </row>
+    <row r="510" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B510" s="1"/>
+    </row>
+    <row r="511" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B511" s="1"/>
+    </row>
+    <row r="512" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B512" s="1"/>
+    </row>
+    <row r="513" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B513" s="1"/>
+    </row>
+    <row r="514" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B514" s="1"/>
+    </row>
+    <row r="515" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B515" s="1"/>
+    </row>
+    <row r="516" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B516" s="1"/>
+    </row>
+    <row r="517" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B517" s="1"/>
+    </row>
+    <row r="518" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B518" s="1"/>
+    </row>
+    <row r="519" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B519" s="1"/>
+    </row>
+    <row r="520" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B520" s="1"/>
+    </row>
+    <row r="521" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B521" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/pages/TP_Master.xlsx
+++ b/pages/TP_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samb\CNZPD\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE596BFB-52E4-4080-B172-2E7BE06BC95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F989470-5632-4E29-9598-0D92B8662F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-9135" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37470" yWindow="-3690" windowWidth="6285" windowHeight="7665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="37">
   <si>
     <t>Distance</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>g</t>
+  </si>
+  <si>
+    <t>test test test test</t>
   </si>
 </sst>
 </file>
@@ -11346,222 +11349,1717 @@
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B392" s="1"/>
+      <c r="A392" t="s">
+        <v>36</v>
+      </c>
+      <c r="B392" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>0</v>
+      </c>
+      <c r="E392" t="s">
+        <v>7</v>
+      </c>
+      <c r="F392">
+        <v>0</v>
+      </c>
+      <c r="G392">
+        <v>0</v>
+      </c>
+      <c r="H392">
+        <v>0</v>
+      </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B393" s="1"/>
+      <c r="A393" t="s">
+        <v>36</v>
+      </c>
+      <c r="B393" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C393">
+        <v>62.5</v>
+      </c>
+      <c r="D393">
+        <v>6.9400000000000546</v>
+      </c>
+      <c r="E393" t="s">
+        <v>7</v>
+      </c>
+      <c r="F393">
+        <v>32.42</v>
+      </c>
+      <c r="G393">
+        <v>32.42</v>
+      </c>
+      <c r="H393">
+        <v>6.94</v>
+      </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B394" s="1"/>
+      <c r="A394" t="s">
+        <v>36</v>
+      </c>
+      <c r="B394" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C394">
+        <v>125</v>
+      </c>
+      <c r="D394">
+        <v>11.680000000000055</v>
+      </c>
+      <c r="E394" t="s">
+        <v>7</v>
+      </c>
+      <c r="F394">
+        <v>47.47</v>
+      </c>
+      <c r="G394">
+        <v>47.47</v>
+      </c>
+      <c r="H394">
+        <v>4.74</v>
+      </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B395" s="1"/>
+      <c r="A395" t="s">
+        <v>36</v>
+      </c>
+      <c r="B395" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C395">
+        <v>187.5</v>
+      </c>
+      <c r="D395">
+        <v>15.800000000000061</v>
+      </c>
+      <c r="E395" t="s">
+        <v>7</v>
+      </c>
+      <c r="F395">
+        <v>54.61</v>
+      </c>
+      <c r="G395">
+        <v>54.61</v>
+      </c>
+      <c r="H395">
+        <v>4.12</v>
+      </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B396" s="1"/>
+      <c r="A396" t="s">
+        <v>36</v>
+      </c>
+      <c r="B396" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C396">
+        <v>250</v>
+      </c>
+      <c r="D396">
+        <v>19.700000000000031</v>
+      </c>
+      <c r="E396" t="s">
+        <v>7</v>
+      </c>
+      <c r="F396">
+        <v>57.69</v>
+      </c>
+      <c r="G396">
+        <v>57.69</v>
+      </c>
+      <c r="H396">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B397" s="1"/>
+      <c r="A397" t="s">
+        <v>36</v>
+      </c>
+      <c r="B397" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C397">
+        <v>312.5</v>
+      </c>
+      <c r="D397">
+        <v>23.460000000000022</v>
+      </c>
+      <c r="E397" t="s">
+        <v>7</v>
+      </c>
+      <c r="F397">
+        <v>59.84</v>
+      </c>
+      <c r="G397">
+        <v>59.84</v>
+      </c>
+      <c r="H397">
+        <v>3.76</v>
+      </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B398" s="1"/>
+      <c r="A398" t="s">
+        <v>36</v>
+      </c>
+      <c r="B398" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C398">
+        <v>375</v>
+      </c>
+      <c r="D398">
+        <v>27.160000000000061</v>
+      </c>
+      <c r="E398" t="s">
+        <v>7</v>
+      </c>
+      <c r="F398">
+        <v>60.81</v>
+      </c>
+      <c r="G398">
+        <v>60.81</v>
+      </c>
+      <c r="H398">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B399" s="1"/>
+      <c r="A399" t="s">
+        <v>36</v>
+      </c>
+      <c r="B399" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C399">
+        <v>437.5</v>
+      </c>
+      <c r="D399">
+        <v>30.920000000000051</v>
+      </c>
+      <c r="E399" t="s">
+        <v>7</v>
+      </c>
+      <c r="F399">
+        <v>59.84</v>
+      </c>
+      <c r="G399">
+        <v>59.84</v>
+      </c>
+      <c r="H399">
+        <v>3.76</v>
+      </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B400" s="1"/>
-    </row>
-    <row r="401" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B401" s="1"/>
-    </row>
-    <row r="402" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B402" s="1"/>
-    </row>
-    <row r="403" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B403" s="1"/>
-    </row>
-    <row r="404" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B404" s="1"/>
-    </row>
-    <row r="405" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B405" s="1"/>
-    </row>
-    <row r="406" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B406" s="1"/>
-    </row>
-    <row r="407" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B407" s="1"/>
-    </row>
-    <row r="408" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B408" s="1"/>
-    </row>
-    <row r="409" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B409" s="1"/>
-    </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B410" s="1"/>
-    </row>
-    <row r="411" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B411" s="1"/>
-    </row>
-    <row r="412" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B412" s="1"/>
-    </row>
-    <row r="413" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B413" s="1"/>
-    </row>
-    <row r="414" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B414" s="1"/>
-    </row>
-    <row r="415" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B415" s="1"/>
-    </row>
-    <row r="416" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B416" s="1"/>
-    </row>
-    <row r="417" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B417" s="1"/>
-    </row>
-    <row r="418" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B418" s="1"/>
-    </row>
-    <row r="419" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B419" s="1"/>
-    </row>
-    <row r="420" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B420" s="1"/>
-    </row>
-    <row r="421" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B421" s="1"/>
-    </row>
-    <row r="422" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B422" s="1"/>
-    </row>
-    <row r="423" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B423" s="1"/>
-    </row>
-    <row r="424" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B424" s="1"/>
-    </row>
-    <row r="425" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B425" s="1"/>
-    </row>
-    <row r="426" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B426" s="1"/>
-    </row>
-    <row r="427" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B427" s="1"/>
-    </row>
-    <row r="428" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B428" s="1"/>
-    </row>
-    <row r="429" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B429" s="1"/>
-    </row>
-    <row r="430" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B430" s="1"/>
-    </row>
-    <row r="431" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B431" s="1"/>
-    </row>
-    <row r="432" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B432" s="1"/>
-    </row>
-    <row r="433" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B433" s="1"/>
-    </row>
-    <row r="434" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B434" s="1"/>
-    </row>
-    <row r="435" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B435" s="1"/>
-    </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B436" s="1"/>
-    </row>
-    <row r="437" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B437" s="1"/>
-    </row>
-    <row r="438" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B438" s="1"/>
-    </row>
-    <row r="439" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B439" s="1"/>
-    </row>
-    <row r="440" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B440" s="1"/>
-    </row>
-    <row r="441" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B441" s="1"/>
-    </row>
-    <row r="442" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B442" s="1"/>
-    </row>
-    <row r="443" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B443" s="1"/>
-    </row>
-    <row r="444" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B444" s="1"/>
-    </row>
-    <row r="445" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B445" s="1"/>
-    </row>
-    <row r="446" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B446" s="1"/>
-    </row>
-    <row r="447" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B447" s="1"/>
-    </row>
-    <row r="448" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B448" s="1"/>
-    </row>
-    <row r="449" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B449" s="1"/>
-    </row>
-    <row r="450" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B450" s="1"/>
-    </row>
-    <row r="451" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B451" s="1"/>
-    </row>
-    <row r="452" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B452" s="1"/>
-    </row>
-    <row r="453" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B453" s="1"/>
-    </row>
-    <row r="454" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B454" s="1"/>
-    </row>
-    <row r="455" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B455" s="1"/>
-    </row>
-    <row r="456" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B456" s="1"/>
-    </row>
-    <row r="457" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>36</v>
+      </c>
+      <c r="B400" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C400">
+        <v>500</v>
+      </c>
+      <c r="D400">
+        <v>34.580000000000013</v>
+      </c>
+      <c r="E400" t="s">
+        <v>7</v>
+      </c>
+      <c r="F400">
+        <v>61.48</v>
+      </c>
+      <c r="G400">
+        <v>61.48</v>
+      </c>
+      <c r="H400">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>36</v>
+      </c>
+      <c r="B401" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C401">
+        <v>562.5</v>
+      </c>
+      <c r="D401">
+        <v>38.22</v>
+      </c>
+      <c r="E401" t="s">
+        <v>9</v>
+      </c>
+      <c r="F401">
+        <v>63.2</v>
+      </c>
+      <c r="G401">
+        <v>61.81</v>
+      </c>
+      <c r="H401">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>36</v>
+      </c>
+      <c r="B402" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C402">
+        <v>625</v>
+      </c>
+      <c r="D402">
+        <v>41.839999999999996</v>
+      </c>
+      <c r="E402" t="s">
+        <v>7</v>
+      </c>
+      <c r="F402">
+        <v>62.15</v>
+      </c>
+      <c r="G402">
+        <v>62.15</v>
+      </c>
+      <c r="H402">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>36</v>
+      </c>
+      <c r="B403" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C403">
+        <v>687.5</v>
+      </c>
+      <c r="D403">
+        <v>45.599999999999987</v>
+      </c>
+      <c r="E403" t="s">
+        <v>7</v>
+      </c>
+      <c r="F403">
+        <v>59.84</v>
+      </c>
+      <c r="G403">
+        <v>59.84</v>
+      </c>
+      <c r="H403">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>36</v>
+      </c>
+      <c r="B404" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C404">
+        <v>750</v>
+      </c>
+      <c r="D404">
+        <v>49.159999999999926</v>
+      </c>
+      <c r="E404" t="s">
+        <v>7</v>
+      </c>
+      <c r="F404">
+        <v>63.2</v>
+      </c>
+      <c r="G404">
+        <v>63.2</v>
+      </c>
+      <c r="H404">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>36</v>
+      </c>
+      <c r="B405" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C405">
+        <v>812.5</v>
+      </c>
+      <c r="D405">
+        <v>52.759999999999948</v>
+      </c>
+      <c r="E405" t="s">
+        <v>7</v>
+      </c>
+      <c r="F405">
+        <v>62.5</v>
+      </c>
+      <c r="G405">
+        <v>62.5</v>
+      </c>
+      <c r="H405">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>36</v>
+      </c>
+      <c r="B406" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C406">
+        <v>875</v>
+      </c>
+      <c r="D406">
+        <v>56.319999999999887</v>
+      </c>
+      <c r="E406" t="s">
+        <v>7</v>
+      </c>
+      <c r="F406">
+        <v>63.2</v>
+      </c>
+      <c r="G406">
+        <v>63.2</v>
+      </c>
+      <c r="H406">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>36</v>
+      </c>
+      <c r="B407" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C407">
+        <v>937.5</v>
+      </c>
+      <c r="D407">
+        <v>59.899999999999928</v>
+      </c>
+      <c r="E407" t="s">
+        <v>7</v>
+      </c>
+      <c r="F407">
+        <v>62.85</v>
+      </c>
+      <c r="G407">
+        <v>62.85</v>
+      </c>
+      <c r="H407">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>36</v>
+      </c>
+      <c r="B408" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C408">
+        <v>1000</v>
+      </c>
+      <c r="D408">
+        <v>63.419999999999902</v>
+      </c>
+      <c r="E408" t="s">
+        <v>7</v>
+      </c>
+      <c r="F408">
+        <v>63.92</v>
+      </c>
+      <c r="G408">
+        <v>63.92</v>
+      </c>
+      <c r="H408">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>36</v>
+      </c>
+      <c r="B409" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C409">
+        <v>1062.5</v>
+      </c>
+      <c r="D409">
+        <v>66.95999999999998</v>
+      </c>
+      <c r="E409" t="s">
+        <v>9</v>
+      </c>
+      <c r="F409">
+        <v>65.03</v>
+      </c>
+      <c r="G409">
+        <v>63.56</v>
+      </c>
+      <c r="H409">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>36</v>
+      </c>
+      <c r="B410" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C410">
+        <v>1125</v>
+      </c>
+      <c r="D410">
+        <v>70.500000000000057</v>
+      </c>
+      <c r="E410" t="s">
+        <v>7</v>
+      </c>
+      <c r="F410">
+        <v>63.56</v>
+      </c>
+      <c r="G410">
+        <v>63.56</v>
+      </c>
+      <c r="H410">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>36</v>
+      </c>
+      <c r="B411" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C411">
+        <v>1187.5</v>
+      </c>
+      <c r="D411">
+        <v>74.160000000000025</v>
+      </c>
+      <c r="E411" t="s">
+        <v>7</v>
+      </c>
+      <c r="F411">
+        <v>61.48</v>
+      </c>
+      <c r="G411">
+        <v>61.48</v>
+      </c>
+      <c r="H411">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>36</v>
+      </c>
+      <c r="B412" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C412">
+        <v>1250</v>
+      </c>
+      <c r="D412">
+        <v>77.699999999999989</v>
+      </c>
+      <c r="E412" t="s">
+        <v>7</v>
+      </c>
+      <c r="F412">
+        <v>63.56</v>
+      </c>
+      <c r="G412">
+        <v>63.56</v>
+      </c>
+      <c r="H412">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>36</v>
+      </c>
+      <c r="B413" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C413">
+        <v>1312.5</v>
+      </c>
+      <c r="D413">
+        <v>81.239999999999952</v>
+      </c>
+      <c r="E413" t="s">
+        <v>7</v>
+      </c>
+      <c r="F413">
+        <v>63.56</v>
+      </c>
+      <c r="G413">
+        <v>63.56</v>
+      </c>
+      <c r="H413">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>36</v>
+      </c>
+      <c r="B414" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C414">
+        <v>1375</v>
+      </c>
+      <c r="D414">
+        <v>84.739999999999952</v>
+      </c>
+      <c r="E414" t="s">
+        <v>7</v>
+      </c>
+      <c r="F414">
+        <v>64.290000000000006</v>
+      </c>
+      <c r="G414">
+        <v>64.290000000000006</v>
+      </c>
+      <c r="H414">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>36</v>
+      </c>
+      <c r="B415" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C415">
+        <v>1437.5</v>
+      </c>
+      <c r="D415">
+        <v>88.259999999999934</v>
+      </c>
+      <c r="E415" t="s">
+        <v>7</v>
+      </c>
+      <c r="F415">
+        <v>63.92</v>
+      </c>
+      <c r="G415">
+        <v>63.92</v>
+      </c>
+      <c r="H415">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>36</v>
+      </c>
+      <c r="B416" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C416">
+        <v>1500</v>
+      </c>
+      <c r="D416">
+        <v>91.799999999999898</v>
+      </c>
+      <c r="E416" t="s">
+        <v>7</v>
+      </c>
+      <c r="F416">
+        <v>63.56</v>
+      </c>
+      <c r="G416">
+        <v>63.56</v>
+      </c>
+      <c r="H416">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>36</v>
+      </c>
+      <c r="B417" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C417">
+        <v>1562.5</v>
+      </c>
+      <c r="D417">
+        <v>95.359999999999957</v>
+      </c>
+      <c r="E417" t="s">
+        <v>7</v>
+      </c>
+      <c r="F417">
+        <v>63.2</v>
+      </c>
+      <c r="G417">
+        <v>63.2</v>
+      </c>
+      <c r="H417">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>36</v>
+      </c>
+      <c r="B418" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C418">
+        <v>1625</v>
+      </c>
+      <c r="D418">
+        <v>98.919999999999902</v>
+      </c>
+      <c r="E418" t="s">
+        <v>7</v>
+      </c>
+      <c r="F418">
+        <v>63.2</v>
+      </c>
+      <c r="G418">
+        <v>63.2</v>
+      </c>
+      <c r="H418">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>36</v>
+      </c>
+      <c r="B419" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C419">
+        <v>1687.5</v>
+      </c>
+      <c r="D419">
+        <v>102.49999999999994</v>
+      </c>
+      <c r="E419" t="s">
+        <v>9</v>
+      </c>
+      <c r="F419">
+        <v>64.290000000000006</v>
+      </c>
+      <c r="G419">
+        <v>62.85</v>
+      </c>
+      <c r="H419">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>36</v>
+      </c>
+      <c r="B420" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C420">
+        <v>1750</v>
+      </c>
+      <c r="D420">
+        <v>106.07999999999998</v>
+      </c>
+      <c r="E420" t="s">
+        <v>7</v>
+      </c>
+      <c r="F420">
+        <v>62.85</v>
+      </c>
+      <c r="G420">
+        <v>62.85</v>
+      </c>
+      <c r="H420">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>36</v>
+      </c>
+      <c r="B421" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C421">
+        <v>1812.5</v>
+      </c>
+      <c r="D421">
+        <v>109.80000000000001</v>
+      </c>
+      <c r="E421" t="s">
+        <v>7</v>
+      </c>
+      <c r="F421">
+        <v>60.48</v>
+      </c>
+      <c r="G421">
+        <v>60.48</v>
+      </c>
+      <c r="H421">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>36</v>
+      </c>
+      <c r="B422" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C422">
+        <v>1875</v>
+      </c>
+      <c r="D422">
+        <v>113.39999999999991</v>
+      </c>
+      <c r="E422" t="s">
+        <v>7</v>
+      </c>
+      <c r="F422">
+        <v>62.5</v>
+      </c>
+      <c r="G422">
+        <v>62.5</v>
+      </c>
+      <c r="H422">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>36</v>
+      </c>
+      <c r="B423" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C423">
+        <v>1937.5</v>
+      </c>
+      <c r="D423">
+        <v>117.01999999999991</v>
+      </c>
+      <c r="E423" t="s">
+        <v>7</v>
+      </c>
+      <c r="F423">
+        <v>62.15</v>
+      </c>
+      <c r="G423">
+        <v>62.15</v>
+      </c>
+      <c r="H423">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>36</v>
+      </c>
+      <c r="B424" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C424">
+        <v>2000</v>
+      </c>
+      <c r="D424">
+        <v>120.61999999999981</v>
+      </c>
+      <c r="E424" t="s">
+        <v>7</v>
+      </c>
+      <c r="F424">
+        <v>62.5</v>
+      </c>
+      <c r="G424">
+        <v>62.5</v>
+      </c>
+      <c r="H424">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>36</v>
+      </c>
+      <c r="B425" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C425">
+        <v>2062.5</v>
+      </c>
+      <c r="D425">
+        <v>124.25999999999991</v>
+      </c>
+      <c r="E425" t="s">
+        <v>7</v>
+      </c>
+      <c r="F425">
+        <v>61.81</v>
+      </c>
+      <c r="G425">
+        <v>61.81</v>
+      </c>
+      <c r="H425">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>36</v>
+      </c>
+      <c r="B426" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C426">
+        <v>2125</v>
+      </c>
+      <c r="D426">
+        <v>127.9</v>
+      </c>
+      <c r="E426" t="s">
+        <v>7</v>
+      </c>
+      <c r="F426">
+        <v>61.81</v>
+      </c>
+      <c r="G426">
+        <v>61.81</v>
+      </c>
+      <c r="H426">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>36</v>
+      </c>
+      <c r="B427" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C427">
+        <v>2187.5</v>
+      </c>
+      <c r="D427">
+        <v>131.54</v>
+      </c>
+      <c r="E427" t="s">
+        <v>9</v>
+      </c>
+      <c r="F427">
+        <v>63.2</v>
+      </c>
+      <c r="G427">
+        <v>61.81</v>
+      </c>
+      <c r="H427">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>36</v>
+      </c>
+      <c r="B428" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C428">
+        <v>2250</v>
+      </c>
+      <c r="D428">
+        <v>135.23999999999992</v>
+      </c>
+      <c r="E428" t="s">
+        <v>7</v>
+      </c>
+      <c r="F428">
+        <v>60.81</v>
+      </c>
+      <c r="G428">
+        <v>60.81</v>
+      </c>
+      <c r="H428">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
+        <v>36</v>
+      </c>
+      <c r="B429" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C429">
+        <v>2312.5</v>
+      </c>
+      <c r="D429">
+        <v>139.0199999999999</v>
+      </c>
+      <c r="E429" t="s">
+        <v>7</v>
+      </c>
+      <c r="F429">
+        <v>59.52</v>
+      </c>
+      <c r="G429">
+        <v>59.52</v>
+      </c>
+      <c r="H429">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
+        <v>36</v>
+      </c>
+      <c r="B430" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C430">
+        <v>2375</v>
+      </c>
+      <c r="D430">
+        <v>142.75999999999991</v>
+      </c>
+      <c r="E430" t="s">
+        <v>7</v>
+      </c>
+      <c r="F430">
+        <v>60.16</v>
+      </c>
+      <c r="G430">
+        <v>60.16</v>
+      </c>
+      <c r="H430">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
+        <v>36</v>
+      </c>
+      <c r="B431" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C431">
+        <v>2437.5</v>
+      </c>
+      <c r="D431">
+        <v>146.61999999999992</v>
+      </c>
+      <c r="E431" t="s">
+        <v>9</v>
+      </c>
+      <c r="F431">
+        <v>59.52</v>
+      </c>
+      <c r="G431">
+        <v>58.29</v>
+      </c>
+      <c r="H431">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>36</v>
+      </c>
+      <c r="B432" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C432">
+        <v>2500</v>
+      </c>
+      <c r="D432">
+        <v>150.29999999999987</v>
+      </c>
+      <c r="E432" t="s">
+        <v>7</v>
+      </c>
+      <c r="F432">
+        <v>61.14</v>
+      </c>
+      <c r="G432">
+        <v>61.14</v>
+      </c>
+      <c r="H432">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
+        <v>36</v>
+      </c>
+      <c r="B433" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C433">
+        <v>2562.5</v>
+      </c>
+      <c r="D433">
+        <v>153.97999999999993</v>
+      </c>
+      <c r="E433" t="s">
+        <v>7</v>
+      </c>
+      <c r="F433">
+        <v>61.14</v>
+      </c>
+      <c r="G433">
+        <v>61.14</v>
+      </c>
+      <c r="H433">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>36</v>
+      </c>
+      <c r="B434" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C434">
+        <v>2625</v>
+      </c>
+      <c r="D434">
+        <v>157.6399999999999</v>
+      </c>
+      <c r="E434" t="s">
+        <v>7</v>
+      </c>
+      <c r="F434">
+        <v>61.48</v>
+      </c>
+      <c r="G434">
+        <v>61.48</v>
+      </c>
+      <c r="H434">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>36</v>
+      </c>
+      <c r="B435" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C435">
+        <v>2687.5</v>
+      </c>
+      <c r="D435">
+        <v>161.31999999999996</v>
+      </c>
+      <c r="E435" t="s">
+        <v>7</v>
+      </c>
+      <c r="F435">
+        <v>61.14</v>
+      </c>
+      <c r="G435">
+        <v>61.14</v>
+      </c>
+      <c r="H435">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>36</v>
+      </c>
+      <c r="B436" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C436">
+        <v>2750</v>
+      </c>
+      <c r="D436">
+        <v>164.92</v>
+      </c>
+      <c r="E436" t="s">
+        <v>7</v>
+      </c>
+      <c r="F436">
+        <v>62.5</v>
+      </c>
+      <c r="G436">
+        <v>62.5</v>
+      </c>
+      <c r="H436">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>36</v>
+      </c>
+      <c r="B437" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C437">
+        <v>2812.5</v>
+      </c>
+      <c r="D437">
+        <v>168.55999999999997</v>
+      </c>
+      <c r="E437" t="s">
+        <v>9</v>
+      </c>
+      <c r="F437">
+        <v>63.2</v>
+      </c>
+      <c r="G437">
+        <v>61.81</v>
+      </c>
+      <c r="H437">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>36</v>
+      </c>
+      <c r="B438" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C438">
+        <v>2875</v>
+      </c>
+      <c r="D438">
+        <v>172.17999999999986</v>
+      </c>
+      <c r="E438" t="s">
+        <v>7</v>
+      </c>
+      <c r="F438">
+        <v>62.15</v>
+      </c>
+      <c r="G438">
+        <v>62.15</v>
+      </c>
+      <c r="H438">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>36</v>
+      </c>
+      <c r="B439" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C439">
+        <v>2937.5</v>
+      </c>
+      <c r="D439">
+        <v>175.89999999999989</v>
+      </c>
+      <c r="E439" t="s">
+        <v>7</v>
+      </c>
+      <c r="F439">
+        <v>60.48</v>
+      </c>
+      <c r="G439">
+        <v>60.48</v>
+      </c>
+      <c r="H439">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
+        <v>36</v>
+      </c>
+      <c r="B440" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C440">
+        <v>3000</v>
+      </c>
+      <c r="D440">
+        <v>179.45999999999995</v>
+      </c>
+      <c r="E440" t="s">
+        <v>7</v>
+      </c>
+      <c r="F440">
+        <v>63.2</v>
+      </c>
+      <c r="G440">
+        <v>63.2</v>
+      </c>
+      <c r="H440">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
+        <v>36</v>
+      </c>
+      <c r="B441" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C441">
+        <v>3062.5</v>
+      </c>
+      <c r="D441">
+        <v>183.05999999999997</v>
+      </c>
+      <c r="E441" t="s">
+        <v>7</v>
+      </c>
+      <c r="F441">
+        <v>62.5</v>
+      </c>
+      <c r="G441">
+        <v>62.5</v>
+      </c>
+      <c r="H441">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
+        <v>36</v>
+      </c>
+      <c r="B442" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C442">
+        <v>3125</v>
+      </c>
+      <c r="D442">
+        <v>186.61999999999992</v>
+      </c>
+      <c r="E442" t="s">
+        <v>7</v>
+      </c>
+      <c r="F442">
+        <v>63.2</v>
+      </c>
+      <c r="G442">
+        <v>63.2</v>
+      </c>
+      <c r="H442">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
+        <v>36</v>
+      </c>
+      <c r="B443" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C443">
+        <v>3187.5</v>
+      </c>
+      <c r="D443">
+        <v>190.21999999999994</v>
+      </c>
+      <c r="E443" t="s">
+        <v>7</v>
+      </c>
+      <c r="F443">
+        <v>62.5</v>
+      </c>
+      <c r="G443">
+        <v>62.5</v>
+      </c>
+      <c r="H443">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
+        <v>36</v>
+      </c>
+      <c r="B444" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C444">
+        <v>3250</v>
+      </c>
+      <c r="D444">
+        <v>193.77999999999989</v>
+      </c>
+      <c r="E444" t="s">
+        <v>7</v>
+      </c>
+      <c r="F444">
+        <v>63.2</v>
+      </c>
+      <c r="G444">
+        <v>63.2</v>
+      </c>
+      <c r="H444">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
+        <v>36</v>
+      </c>
+      <c r="B445" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C445">
+        <v>3312.5</v>
+      </c>
+      <c r="D445">
+        <v>197.35999999999993</v>
+      </c>
+      <c r="E445" t="s">
+        <v>7</v>
+      </c>
+      <c r="F445">
+        <v>62.85</v>
+      </c>
+      <c r="G445">
+        <v>62.85</v>
+      </c>
+      <c r="H445">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>36</v>
+      </c>
+      <c r="B446" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C446">
+        <v>3375</v>
+      </c>
+      <c r="D446">
+        <v>200.95999999999995</v>
+      </c>
+      <c r="E446" t="s">
+        <v>7</v>
+      </c>
+      <c r="F446">
+        <v>62.5</v>
+      </c>
+      <c r="G446">
+        <v>62.5</v>
+      </c>
+      <c r="H446">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>36</v>
+      </c>
+      <c r="B447" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C447">
+        <v>3437.5</v>
+      </c>
+      <c r="D447">
+        <v>204.55999999999997</v>
+      </c>
+      <c r="E447" t="s">
+        <v>9</v>
+      </c>
+      <c r="F447">
+        <v>63.92</v>
+      </c>
+      <c r="G447">
+        <v>62.5</v>
+      </c>
+      <c r="H447">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
+        <v>36</v>
+      </c>
+      <c r="B448" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C448">
+        <v>3500</v>
+      </c>
+      <c r="D448">
+        <v>208.21999999999983</v>
+      </c>
+      <c r="E448" t="s">
+        <v>7</v>
+      </c>
+      <c r="F448">
+        <v>61.48</v>
+      </c>
+      <c r="G448">
+        <v>61.48</v>
+      </c>
+      <c r="H448">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
+        <v>36</v>
+      </c>
+      <c r="B449" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C449">
+        <v>3562.5</v>
+      </c>
+      <c r="D449">
+        <v>211.93999999999986</v>
+      </c>
+      <c r="E449" t="s">
+        <v>7</v>
+      </c>
+      <c r="F449">
+        <v>60.48</v>
+      </c>
+      <c r="G449">
+        <v>60.48</v>
+      </c>
+      <c r="H449">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
+        <v>36</v>
+      </c>
+      <c r="B450" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C450">
+        <v>3625</v>
+      </c>
+      <c r="D450">
+        <v>215.61999999999992</v>
+      </c>
+      <c r="E450" t="s">
+        <v>7</v>
+      </c>
+      <c r="F450">
+        <v>61.14</v>
+      </c>
+      <c r="G450">
+        <v>61.14</v>
+      </c>
+      <c r="H450">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
+        <v>36</v>
+      </c>
+      <c r="B451" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C451">
+        <v>3687.5</v>
+      </c>
+      <c r="D451">
+        <v>219.29999999999998</v>
+      </c>
+      <c r="E451" t="s">
+        <v>7</v>
+      </c>
+      <c r="F451">
+        <v>61.14</v>
+      </c>
+      <c r="G451">
+        <v>61.14</v>
+      </c>
+      <c r="H451">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
+        <v>36</v>
+      </c>
+      <c r="B452" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C452">
+        <v>3750</v>
+      </c>
+      <c r="D452">
+        <v>222.9999999999998</v>
+      </c>
+      <c r="E452" t="s">
+        <v>7</v>
+      </c>
+      <c r="F452">
+        <v>60.81</v>
+      </c>
+      <c r="G452">
+        <v>60.81</v>
+      </c>
+      <c r="H452">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
+        <v>36</v>
+      </c>
+      <c r="B453" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C453">
+        <v>3812.5</v>
+      </c>
+      <c r="D453">
+        <v>226.69999999999985</v>
+      </c>
+      <c r="E453" t="s">
+        <v>7</v>
+      </c>
+      <c r="F453">
+        <v>60.81</v>
+      </c>
+      <c r="G453">
+        <v>60.81</v>
+      </c>
+      <c r="H453">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
+        <v>36</v>
+      </c>
+      <c r="B454" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C454">
+        <v>3875</v>
+      </c>
+      <c r="D454">
+        <v>230.41999999999987</v>
+      </c>
+      <c r="E454" t="s">
+        <v>7</v>
+      </c>
+      <c r="F454">
+        <v>60.48</v>
+      </c>
+      <c r="G454">
+        <v>60.48</v>
+      </c>
+      <c r="H454">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A455" t="s">
+        <v>36</v>
+      </c>
+      <c r="B455" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C455">
+        <v>3937.5</v>
+      </c>
+      <c r="D455">
+        <v>234.15999999999988</v>
+      </c>
+      <c r="E455" t="s">
+        <v>7</v>
+      </c>
+      <c r="F455">
+        <v>60.16</v>
+      </c>
+      <c r="G455">
+        <v>60.16</v>
+      </c>
+      <c r="H455">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A456" t="s">
+        <v>36</v>
+      </c>
+      <c r="B456" s="1">
+        <v>45029</v>
+      </c>
+      <c r="C456">
+        <v>4000</v>
+      </c>
+      <c r="D456">
+        <v>238.09999999999994</v>
+      </c>
+      <c r="E456" t="s">
+        <v>7</v>
+      </c>
+      <c r="F456">
+        <v>57.11</v>
+      </c>
+      <c r="G456">
+        <v>57.11</v>
+      </c>
+      <c r="H456">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B457" s="1"/>
     </row>
-    <row r="458" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B458" s="1"/>
     </row>
-    <row r="459" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B459" s="1"/>
     </row>
-    <row r="460" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B460" s="1"/>
     </row>
-    <row r="461" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B461" s="1"/>
     </row>
-    <row r="462" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B462" s="1"/>
     </row>
-    <row r="463" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B463" s="1"/>
     </row>
-    <row r="464" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B464" s="1"/>
     </row>
     <row r="465" spans="2:2" x14ac:dyDescent="0.35">

--- a/pages/TP_Master.xlsx
+++ b/pages/TP_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samb\CNZPD\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F989470-5632-4E29-9598-0D92B8662F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CAFF62-7BA1-4275-8AB0-AA0B670C2728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37470" yWindow="-3690" windowWidth="6285" windowHeight="7665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9135" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="36">
   <si>
     <t>Distance</t>
   </si>
@@ -128,9 +128,6 @@
   </si>
   <si>
     <t>g</t>
-  </si>
-  <si>
-    <t>test test test test</t>
   </si>
 </sst>
 </file>
@@ -11349,1717 +11346,222 @@
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A392" t="s">
-        <v>36</v>
-      </c>
-      <c r="B392" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C392">
-        <v>0</v>
-      </c>
-      <c r="D392">
-        <v>0</v>
-      </c>
-      <c r="E392" t="s">
-        <v>7</v>
-      </c>
-      <c r="F392">
-        <v>0</v>
-      </c>
-      <c r="G392">
-        <v>0</v>
-      </c>
-      <c r="H392">
-        <v>0</v>
-      </c>
+      <c r="B392" s="1"/>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A393" t="s">
-        <v>36</v>
-      </c>
-      <c r="B393" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C393">
-        <v>62.5</v>
-      </c>
-      <c r="D393">
-        <v>6.9400000000000546</v>
-      </c>
-      <c r="E393" t="s">
-        <v>7</v>
-      </c>
-      <c r="F393">
-        <v>32.42</v>
-      </c>
-      <c r="G393">
-        <v>32.42</v>
-      </c>
-      <c r="H393">
-        <v>6.94</v>
-      </c>
+      <c r="B393" s="1"/>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A394" t="s">
-        <v>36</v>
-      </c>
-      <c r="B394" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C394">
-        <v>125</v>
-      </c>
-      <c r="D394">
-        <v>11.680000000000055</v>
-      </c>
-      <c r="E394" t="s">
-        <v>7</v>
-      </c>
-      <c r="F394">
-        <v>47.47</v>
-      </c>
-      <c r="G394">
-        <v>47.47</v>
-      </c>
-      <c r="H394">
-        <v>4.74</v>
-      </c>
+      <c r="B394" s="1"/>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A395" t="s">
-        <v>36</v>
-      </c>
-      <c r="B395" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C395">
-        <v>187.5</v>
-      </c>
-      <c r="D395">
-        <v>15.800000000000061</v>
-      </c>
-      <c r="E395" t="s">
-        <v>7</v>
-      </c>
-      <c r="F395">
-        <v>54.61</v>
-      </c>
-      <c r="G395">
-        <v>54.61</v>
-      </c>
-      <c r="H395">
-        <v>4.12</v>
-      </c>
+      <c r="B395" s="1"/>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A396" t="s">
-        <v>36</v>
-      </c>
-      <c r="B396" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C396">
-        <v>250</v>
-      </c>
-      <c r="D396">
-        <v>19.700000000000031</v>
-      </c>
-      <c r="E396" t="s">
-        <v>7</v>
-      </c>
-      <c r="F396">
-        <v>57.69</v>
-      </c>
-      <c r="G396">
-        <v>57.69</v>
-      </c>
-      <c r="H396">
-        <v>3.9</v>
-      </c>
+      <c r="B396" s="1"/>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A397" t="s">
-        <v>36</v>
-      </c>
-      <c r="B397" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C397">
-        <v>312.5</v>
-      </c>
-      <c r="D397">
-        <v>23.460000000000022</v>
-      </c>
-      <c r="E397" t="s">
-        <v>7</v>
-      </c>
-      <c r="F397">
-        <v>59.84</v>
-      </c>
-      <c r="G397">
-        <v>59.84</v>
-      </c>
-      <c r="H397">
-        <v>3.76</v>
-      </c>
+      <c r="B397" s="1"/>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A398" t="s">
-        <v>36</v>
-      </c>
-      <c r="B398" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C398">
-        <v>375</v>
-      </c>
-      <c r="D398">
-        <v>27.160000000000061</v>
-      </c>
-      <c r="E398" t="s">
-        <v>7</v>
-      </c>
-      <c r="F398">
-        <v>60.81</v>
-      </c>
-      <c r="G398">
-        <v>60.81</v>
-      </c>
-      <c r="H398">
-        <v>3.7</v>
-      </c>
+      <c r="B398" s="1"/>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A399" t="s">
-        <v>36</v>
-      </c>
-      <c r="B399" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C399">
-        <v>437.5</v>
-      </c>
-      <c r="D399">
-        <v>30.920000000000051</v>
-      </c>
-      <c r="E399" t="s">
-        <v>7</v>
-      </c>
-      <c r="F399">
-        <v>59.84</v>
-      </c>
-      <c r="G399">
-        <v>59.84</v>
-      </c>
-      <c r="H399">
-        <v>3.76</v>
-      </c>
+      <c r="B399" s="1"/>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A400" t="s">
-        <v>36</v>
-      </c>
-      <c r="B400" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C400">
-        <v>500</v>
-      </c>
-      <c r="D400">
-        <v>34.580000000000013</v>
-      </c>
-      <c r="E400" t="s">
-        <v>7</v>
-      </c>
-      <c r="F400">
-        <v>61.48</v>
-      </c>
-      <c r="G400">
-        <v>61.48</v>
-      </c>
-      <c r="H400">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A401" t="s">
-        <v>36</v>
-      </c>
-      <c r="B401" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C401">
-        <v>562.5</v>
-      </c>
-      <c r="D401">
-        <v>38.22</v>
-      </c>
-      <c r="E401" t="s">
-        <v>9</v>
-      </c>
-      <c r="F401">
-        <v>63.2</v>
-      </c>
-      <c r="G401">
-        <v>61.81</v>
-      </c>
-      <c r="H401">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A402" t="s">
-        <v>36</v>
-      </c>
-      <c r="B402" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C402">
-        <v>625</v>
-      </c>
-      <c r="D402">
-        <v>41.839999999999996</v>
-      </c>
-      <c r="E402" t="s">
-        <v>7</v>
-      </c>
-      <c r="F402">
-        <v>62.15</v>
-      </c>
-      <c r="G402">
-        <v>62.15</v>
-      </c>
-      <c r="H402">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A403" t="s">
-        <v>36</v>
-      </c>
-      <c r="B403" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C403">
-        <v>687.5</v>
-      </c>
-      <c r="D403">
-        <v>45.599999999999987</v>
-      </c>
-      <c r="E403" t="s">
-        <v>7</v>
-      </c>
-      <c r="F403">
-        <v>59.84</v>
-      </c>
-      <c r="G403">
-        <v>59.84</v>
-      </c>
-      <c r="H403">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A404" t="s">
-        <v>36</v>
-      </c>
-      <c r="B404" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C404">
-        <v>750</v>
-      </c>
-      <c r="D404">
-        <v>49.159999999999926</v>
-      </c>
-      <c r="E404" t="s">
-        <v>7</v>
-      </c>
-      <c r="F404">
-        <v>63.2</v>
-      </c>
-      <c r="G404">
-        <v>63.2</v>
-      </c>
-      <c r="H404">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A405" t="s">
-        <v>36</v>
-      </c>
-      <c r="B405" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C405">
-        <v>812.5</v>
-      </c>
-      <c r="D405">
-        <v>52.759999999999948</v>
-      </c>
-      <c r="E405" t="s">
-        <v>7</v>
-      </c>
-      <c r="F405">
-        <v>62.5</v>
-      </c>
-      <c r="G405">
-        <v>62.5</v>
-      </c>
-      <c r="H405">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A406" t="s">
-        <v>36</v>
-      </c>
-      <c r="B406" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C406">
-        <v>875</v>
-      </c>
-      <c r="D406">
-        <v>56.319999999999887</v>
-      </c>
-      <c r="E406" t="s">
-        <v>7</v>
-      </c>
-      <c r="F406">
-        <v>63.2</v>
-      </c>
-      <c r="G406">
-        <v>63.2</v>
-      </c>
-      <c r="H406">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A407" t="s">
-        <v>36</v>
-      </c>
-      <c r="B407" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C407">
-        <v>937.5</v>
-      </c>
-      <c r="D407">
-        <v>59.899999999999928</v>
-      </c>
-      <c r="E407" t="s">
-        <v>7</v>
-      </c>
-      <c r="F407">
-        <v>62.85</v>
-      </c>
-      <c r="G407">
-        <v>62.85</v>
-      </c>
-      <c r="H407">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A408" t="s">
-        <v>36</v>
-      </c>
-      <c r="B408" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C408">
-        <v>1000</v>
-      </c>
-      <c r="D408">
-        <v>63.419999999999902</v>
-      </c>
-      <c r="E408" t="s">
-        <v>7</v>
-      </c>
-      <c r="F408">
-        <v>63.92</v>
-      </c>
-      <c r="G408">
-        <v>63.92</v>
-      </c>
-      <c r="H408">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A409" t="s">
-        <v>36</v>
-      </c>
-      <c r="B409" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C409">
-        <v>1062.5</v>
-      </c>
-      <c r="D409">
-        <v>66.95999999999998</v>
-      </c>
-      <c r="E409" t="s">
-        <v>9</v>
-      </c>
-      <c r="F409">
-        <v>65.03</v>
-      </c>
-      <c r="G409">
-        <v>63.56</v>
-      </c>
-      <c r="H409">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A410" t="s">
-        <v>36</v>
-      </c>
-      <c r="B410" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C410">
-        <v>1125</v>
-      </c>
-      <c r="D410">
-        <v>70.500000000000057</v>
-      </c>
-      <c r="E410" t="s">
-        <v>7</v>
-      </c>
-      <c r="F410">
-        <v>63.56</v>
-      </c>
-      <c r="G410">
-        <v>63.56</v>
-      </c>
-      <c r="H410">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A411" t="s">
-        <v>36</v>
-      </c>
-      <c r="B411" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C411">
-        <v>1187.5</v>
-      </c>
-      <c r="D411">
-        <v>74.160000000000025</v>
-      </c>
-      <c r="E411" t="s">
-        <v>7</v>
-      </c>
-      <c r="F411">
-        <v>61.48</v>
-      </c>
-      <c r="G411">
-        <v>61.48</v>
-      </c>
-      <c r="H411">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A412" t="s">
-        <v>36</v>
-      </c>
-      <c r="B412" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C412">
-        <v>1250</v>
-      </c>
-      <c r="D412">
-        <v>77.699999999999989</v>
-      </c>
-      <c r="E412" t="s">
-        <v>7</v>
-      </c>
-      <c r="F412">
-        <v>63.56</v>
-      </c>
-      <c r="G412">
-        <v>63.56</v>
-      </c>
-      <c r="H412">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A413" t="s">
-        <v>36</v>
-      </c>
-      <c r="B413" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C413">
-        <v>1312.5</v>
-      </c>
-      <c r="D413">
-        <v>81.239999999999952</v>
-      </c>
-      <c r="E413" t="s">
-        <v>7</v>
-      </c>
-      <c r="F413">
-        <v>63.56</v>
-      </c>
-      <c r="G413">
-        <v>63.56</v>
-      </c>
-      <c r="H413">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A414" t="s">
-        <v>36</v>
-      </c>
-      <c r="B414" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C414">
-        <v>1375</v>
-      </c>
-      <c r="D414">
-        <v>84.739999999999952</v>
-      </c>
-      <c r="E414" t="s">
-        <v>7</v>
-      </c>
-      <c r="F414">
-        <v>64.290000000000006</v>
-      </c>
-      <c r="G414">
-        <v>64.290000000000006</v>
-      </c>
-      <c r="H414">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A415" t="s">
-        <v>36</v>
-      </c>
-      <c r="B415" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C415">
-        <v>1437.5</v>
-      </c>
-      <c r="D415">
-        <v>88.259999999999934</v>
-      </c>
-      <c r="E415" t="s">
-        <v>7</v>
-      </c>
-      <c r="F415">
-        <v>63.92</v>
-      </c>
-      <c r="G415">
-        <v>63.92</v>
-      </c>
-      <c r="H415">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A416" t="s">
-        <v>36</v>
-      </c>
-      <c r="B416" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C416">
-        <v>1500</v>
-      </c>
-      <c r="D416">
-        <v>91.799999999999898</v>
-      </c>
-      <c r="E416" t="s">
-        <v>7</v>
-      </c>
-      <c r="F416">
-        <v>63.56</v>
-      </c>
-      <c r="G416">
-        <v>63.56</v>
-      </c>
-      <c r="H416">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A417" t="s">
-        <v>36</v>
-      </c>
-      <c r="B417" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C417">
-        <v>1562.5</v>
-      </c>
-      <c r="D417">
-        <v>95.359999999999957</v>
-      </c>
-      <c r="E417" t="s">
-        <v>7</v>
-      </c>
-      <c r="F417">
-        <v>63.2</v>
-      </c>
-      <c r="G417">
-        <v>63.2</v>
-      </c>
-      <c r="H417">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A418" t="s">
-        <v>36</v>
-      </c>
-      <c r="B418" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C418">
-        <v>1625</v>
-      </c>
-      <c r="D418">
-        <v>98.919999999999902</v>
-      </c>
-      <c r="E418" t="s">
-        <v>7</v>
-      </c>
-      <c r="F418">
-        <v>63.2</v>
-      </c>
-      <c r="G418">
-        <v>63.2</v>
-      </c>
-      <c r="H418">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A419" t="s">
-        <v>36</v>
-      </c>
-      <c r="B419" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C419">
-        <v>1687.5</v>
-      </c>
-      <c r="D419">
-        <v>102.49999999999994</v>
-      </c>
-      <c r="E419" t="s">
-        <v>9</v>
-      </c>
-      <c r="F419">
-        <v>64.290000000000006</v>
-      </c>
-      <c r="G419">
-        <v>62.85</v>
-      </c>
-      <c r="H419">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A420" t="s">
-        <v>36</v>
-      </c>
-      <c r="B420" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C420">
-        <v>1750</v>
-      </c>
-      <c r="D420">
-        <v>106.07999999999998</v>
-      </c>
-      <c r="E420" t="s">
-        <v>7</v>
-      </c>
-      <c r="F420">
-        <v>62.85</v>
-      </c>
-      <c r="G420">
-        <v>62.85</v>
-      </c>
-      <c r="H420">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A421" t="s">
-        <v>36</v>
-      </c>
-      <c r="B421" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C421">
-        <v>1812.5</v>
-      </c>
-      <c r="D421">
-        <v>109.80000000000001</v>
-      </c>
-      <c r="E421" t="s">
-        <v>7</v>
-      </c>
-      <c r="F421">
-        <v>60.48</v>
-      </c>
-      <c r="G421">
-        <v>60.48</v>
-      </c>
-      <c r="H421">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A422" t="s">
-        <v>36</v>
-      </c>
-      <c r="B422" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C422">
-        <v>1875</v>
-      </c>
-      <c r="D422">
-        <v>113.39999999999991</v>
-      </c>
-      <c r="E422" t="s">
-        <v>7</v>
-      </c>
-      <c r="F422">
-        <v>62.5</v>
-      </c>
-      <c r="G422">
-        <v>62.5</v>
-      </c>
-      <c r="H422">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A423" t="s">
-        <v>36</v>
-      </c>
-      <c r="B423" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C423">
-        <v>1937.5</v>
-      </c>
-      <c r="D423">
-        <v>117.01999999999991</v>
-      </c>
-      <c r="E423" t="s">
-        <v>7</v>
-      </c>
-      <c r="F423">
-        <v>62.15</v>
-      </c>
-      <c r="G423">
-        <v>62.15</v>
-      </c>
-      <c r="H423">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A424" t="s">
-        <v>36</v>
-      </c>
-      <c r="B424" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C424">
-        <v>2000</v>
-      </c>
-      <c r="D424">
-        <v>120.61999999999981</v>
-      </c>
-      <c r="E424" t="s">
-        <v>7</v>
-      </c>
-      <c r="F424">
-        <v>62.5</v>
-      </c>
-      <c r="G424">
-        <v>62.5</v>
-      </c>
-      <c r="H424">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A425" t="s">
-        <v>36</v>
-      </c>
-      <c r="B425" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C425">
-        <v>2062.5</v>
-      </c>
-      <c r="D425">
-        <v>124.25999999999991</v>
-      </c>
-      <c r="E425" t="s">
-        <v>7</v>
-      </c>
-      <c r="F425">
-        <v>61.81</v>
-      </c>
-      <c r="G425">
-        <v>61.81</v>
-      </c>
-      <c r="H425">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A426" t="s">
-        <v>36</v>
-      </c>
-      <c r="B426" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C426">
-        <v>2125</v>
-      </c>
-      <c r="D426">
-        <v>127.9</v>
-      </c>
-      <c r="E426" t="s">
-        <v>7</v>
-      </c>
-      <c r="F426">
-        <v>61.81</v>
-      </c>
-      <c r="G426">
-        <v>61.81</v>
-      </c>
-      <c r="H426">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A427" t="s">
-        <v>36</v>
-      </c>
-      <c r="B427" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C427">
-        <v>2187.5</v>
-      </c>
-      <c r="D427">
-        <v>131.54</v>
-      </c>
-      <c r="E427" t="s">
-        <v>9</v>
-      </c>
-      <c r="F427">
-        <v>63.2</v>
-      </c>
-      <c r="G427">
-        <v>61.81</v>
-      </c>
-      <c r="H427">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A428" t="s">
-        <v>36</v>
-      </c>
-      <c r="B428" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C428">
-        <v>2250</v>
-      </c>
-      <c r="D428">
-        <v>135.23999999999992</v>
-      </c>
-      <c r="E428" t="s">
-        <v>7</v>
-      </c>
-      <c r="F428">
-        <v>60.81</v>
-      </c>
-      <c r="G428">
-        <v>60.81</v>
-      </c>
-      <c r="H428">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A429" t="s">
-        <v>36</v>
-      </c>
-      <c r="B429" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C429">
-        <v>2312.5</v>
-      </c>
-      <c r="D429">
-        <v>139.0199999999999</v>
-      </c>
-      <c r="E429" t="s">
-        <v>7</v>
-      </c>
-      <c r="F429">
-        <v>59.52</v>
-      </c>
-      <c r="G429">
-        <v>59.52</v>
-      </c>
-      <c r="H429">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A430" t="s">
-        <v>36</v>
-      </c>
-      <c r="B430" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C430">
-        <v>2375</v>
-      </c>
-      <c r="D430">
-        <v>142.75999999999991</v>
-      </c>
-      <c r="E430" t="s">
-        <v>7</v>
-      </c>
-      <c r="F430">
-        <v>60.16</v>
-      </c>
-      <c r="G430">
-        <v>60.16</v>
-      </c>
-      <c r="H430">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A431" t="s">
-        <v>36</v>
-      </c>
-      <c r="B431" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C431">
-        <v>2437.5</v>
-      </c>
-      <c r="D431">
-        <v>146.61999999999992</v>
-      </c>
-      <c r="E431" t="s">
-        <v>9</v>
-      </c>
-      <c r="F431">
-        <v>59.52</v>
-      </c>
-      <c r="G431">
-        <v>58.29</v>
-      </c>
-      <c r="H431">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A432" t="s">
-        <v>36</v>
-      </c>
-      <c r="B432" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C432">
-        <v>2500</v>
-      </c>
-      <c r="D432">
-        <v>150.29999999999987</v>
-      </c>
-      <c r="E432" t="s">
-        <v>7</v>
-      </c>
-      <c r="F432">
-        <v>61.14</v>
-      </c>
-      <c r="G432">
-        <v>61.14</v>
-      </c>
-      <c r="H432">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A433" t="s">
-        <v>36</v>
-      </c>
-      <c r="B433" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C433">
-        <v>2562.5</v>
-      </c>
-      <c r="D433">
-        <v>153.97999999999993</v>
-      </c>
-      <c r="E433" t="s">
-        <v>7</v>
-      </c>
-      <c r="F433">
-        <v>61.14</v>
-      </c>
-      <c r="G433">
-        <v>61.14</v>
-      </c>
-      <c r="H433">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A434" t="s">
-        <v>36</v>
-      </c>
-      <c r="B434" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C434">
-        <v>2625</v>
-      </c>
-      <c r="D434">
-        <v>157.6399999999999</v>
-      </c>
-      <c r="E434" t="s">
-        <v>7</v>
-      </c>
-      <c r="F434">
-        <v>61.48</v>
-      </c>
-      <c r="G434">
-        <v>61.48</v>
-      </c>
-      <c r="H434">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A435" t="s">
-        <v>36</v>
-      </c>
-      <c r="B435" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C435">
-        <v>2687.5</v>
-      </c>
-      <c r="D435">
-        <v>161.31999999999996</v>
-      </c>
-      <c r="E435" t="s">
-        <v>7</v>
-      </c>
-      <c r="F435">
-        <v>61.14</v>
-      </c>
-      <c r="G435">
-        <v>61.14</v>
-      </c>
-      <c r="H435">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A436" t="s">
-        <v>36</v>
-      </c>
-      <c r="B436" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C436">
-        <v>2750</v>
-      </c>
-      <c r="D436">
-        <v>164.92</v>
-      </c>
-      <c r="E436" t="s">
-        <v>7</v>
-      </c>
-      <c r="F436">
-        <v>62.5</v>
-      </c>
-      <c r="G436">
-        <v>62.5</v>
-      </c>
-      <c r="H436">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A437" t="s">
-        <v>36</v>
-      </c>
-      <c r="B437" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C437">
-        <v>2812.5</v>
-      </c>
-      <c r="D437">
-        <v>168.55999999999997</v>
-      </c>
-      <c r="E437" t="s">
-        <v>9</v>
-      </c>
-      <c r="F437">
-        <v>63.2</v>
-      </c>
-      <c r="G437">
-        <v>61.81</v>
-      </c>
-      <c r="H437">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A438" t="s">
-        <v>36</v>
-      </c>
-      <c r="B438" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C438">
-        <v>2875</v>
-      </c>
-      <c r="D438">
-        <v>172.17999999999986</v>
-      </c>
-      <c r="E438" t="s">
-        <v>7</v>
-      </c>
-      <c r="F438">
-        <v>62.15</v>
-      </c>
-      <c r="G438">
-        <v>62.15</v>
-      </c>
-      <c r="H438">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A439" t="s">
-        <v>36</v>
-      </c>
-      <c r="B439" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C439">
-        <v>2937.5</v>
-      </c>
-      <c r="D439">
-        <v>175.89999999999989</v>
-      </c>
-      <c r="E439" t="s">
-        <v>7</v>
-      </c>
-      <c r="F439">
-        <v>60.48</v>
-      </c>
-      <c r="G439">
-        <v>60.48</v>
-      </c>
-      <c r="H439">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A440" t="s">
-        <v>36</v>
-      </c>
-      <c r="B440" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C440">
-        <v>3000</v>
-      </c>
-      <c r="D440">
-        <v>179.45999999999995</v>
-      </c>
-      <c r="E440" t="s">
-        <v>7</v>
-      </c>
-      <c r="F440">
-        <v>63.2</v>
-      </c>
-      <c r="G440">
-        <v>63.2</v>
-      </c>
-      <c r="H440">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A441" t="s">
-        <v>36</v>
-      </c>
-      <c r="B441" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C441">
-        <v>3062.5</v>
-      </c>
-      <c r="D441">
-        <v>183.05999999999997</v>
-      </c>
-      <c r="E441" t="s">
-        <v>7</v>
-      </c>
-      <c r="F441">
-        <v>62.5</v>
-      </c>
-      <c r="G441">
-        <v>62.5</v>
-      </c>
-      <c r="H441">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A442" t="s">
-        <v>36</v>
-      </c>
-      <c r="B442" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C442">
-        <v>3125</v>
-      </c>
-      <c r="D442">
-        <v>186.61999999999992</v>
-      </c>
-      <c r="E442" t="s">
-        <v>7</v>
-      </c>
-      <c r="F442">
-        <v>63.2</v>
-      </c>
-      <c r="G442">
-        <v>63.2</v>
-      </c>
-      <c r="H442">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A443" t="s">
-        <v>36</v>
-      </c>
-      <c r="B443" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C443">
-        <v>3187.5</v>
-      </c>
-      <c r="D443">
-        <v>190.21999999999994</v>
-      </c>
-      <c r="E443" t="s">
-        <v>7</v>
-      </c>
-      <c r="F443">
-        <v>62.5</v>
-      </c>
-      <c r="G443">
-        <v>62.5</v>
-      </c>
-      <c r="H443">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A444" t="s">
-        <v>36</v>
-      </c>
-      <c r="B444" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C444">
-        <v>3250</v>
-      </c>
-      <c r="D444">
-        <v>193.77999999999989</v>
-      </c>
-      <c r="E444" t="s">
-        <v>7</v>
-      </c>
-      <c r="F444">
-        <v>63.2</v>
-      </c>
-      <c r="G444">
-        <v>63.2</v>
-      </c>
-      <c r="H444">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A445" t="s">
-        <v>36</v>
-      </c>
-      <c r="B445" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C445">
-        <v>3312.5</v>
-      </c>
-      <c r="D445">
-        <v>197.35999999999993</v>
-      </c>
-      <c r="E445" t="s">
-        <v>7</v>
-      </c>
-      <c r="F445">
-        <v>62.85</v>
-      </c>
-      <c r="G445">
-        <v>62.85</v>
-      </c>
-      <c r="H445">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A446" t="s">
-        <v>36</v>
-      </c>
-      <c r="B446" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C446">
-        <v>3375</v>
-      </c>
-      <c r="D446">
-        <v>200.95999999999995</v>
-      </c>
-      <c r="E446" t="s">
-        <v>7</v>
-      </c>
-      <c r="F446">
-        <v>62.5</v>
-      </c>
-      <c r="G446">
-        <v>62.5</v>
-      </c>
-      <c r="H446">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A447" t="s">
-        <v>36</v>
-      </c>
-      <c r="B447" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C447">
-        <v>3437.5</v>
-      </c>
-      <c r="D447">
-        <v>204.55999999999997</v>
-      </c>
-      <c r="E447" t="s">
-        <v>9</v>
-      </c>
-      <c r="F447">
-        <v>63.92</v>
-      </c>
-      <c r="G447">
-        <v>62.5</v>
-      </c>
-      <c r="H447">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A448" t="s">
-        <v>36</v>
-      </c>
-      <c r="B448" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C448">
-        <v>3500</v>
-      </c>
-      <c r="D448">
-        <v>208.21999999999983</v>
-      </c>
-      <c r="E448" t="s">
-        <v>7</v>
-      </c>
-      <c r="F448">
-        <v>61.48</v>
-      </c>
-      <c r="G448">
-        <v>61.48</v>
-      </c>
-      <c r="H448">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A449" t="s">
-        <v>36</v>
-      </c>
-      <c r="B449" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C449">
-        <v>3562.5</v>
-      </c>
-      <c r="D449">
-        <v>211.93999999999986</v>
-      </c>
-      <c r="E449" t="s">
-        <v>7</v>
-      </c>
-      <c r="F449">
-        <v>60.48</v>
-      </c>
-      <c r="G449">
-        <v>60.48</v>
-      </c>
-      <c r="H449">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A450" t="s">
-        <v>36</v>
-      </c>
-      <c r="B450" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C450">
-        <v>3625</v>
-      </c>
-      <c r="D450">
-        <v>215.61999999999992</v>
-      </c>
-      <c r="E450" t="s">
-        <v>7</v>
-      </c>
-      <c r="F450">
-        <v>61.14</v>
-      </c>
-      <c r="G450">
-        <v>61.14</v>
-      </c>
-      <c r="H450">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A451" t="s">
-        <v>36</v>
-      </c>
-      <c r="B451" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C451">
-        <v>3687.5</v>
-      </c>
-      <c r="D451">
-        <v>219.29999999999998</v>
-      </c>
-      <c r="E451" t="s">
-        <v>7</v>
-      </c>
-      <c r="F451">
-        <v>61.14</v>
-      </c>
-      <c r="G451">
-        <v>61.14</v>
-      </c>
-      <c r="H451">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A452" t="s">
-        <v>36</v>
-      </c>
-      <c r="B452" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C452">
-        <v>3750</v>
-      </c>
-      <c r="D452">
-        <v>222.9999999999998</v>
-      </c>
-      <c r="E452" t="s">
-        <v>7</v>
-      </c>
-      <c r="F452">
-        <v>60.81</v>
-      </c>
-      <c r="G452">
-        <v>60.81</v>
-      </c>
-      <c r="H452">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A453" t="s">
-        <v>36</v>
-      </c>
-      <c r="B453" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C453">
-        <v>3812.5</v>
-      </c>
-      <c r="D453">
-        <v>226.69999999999985</v>
-      </c>
-      <c r="E453" t="s">
-        <v>7</v>
-      </c>
-      <c r="F453">
-        <v>60.81</v>
-      </c>
-      <c r="G453">
-        <v>60.81</v>
-      </c>
-      <c r="H453">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A454" t="s">
-        <v>36</v>
-      </c>
-      <c r="B454" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C454">
-        <v>3875</v>
-      </c>
-      <c r="D454">
-        <v>230.41999999999987</v>
-      </c>
-      <c r="E454" t="s">
-        <v>7</v>
-      </c>
-      <c r="F454">
-        <v>60.48</v>
-      </c>
-      <c r="G454">
-        <v>60.48</v>
-      </c>
-      <c r="H454">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A455" t="s">
-        <v>36</v>
-      </c>
-      <c r="B455" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C455">
-        <v>3937.5</v>
-      </c>
-      <c r="D455">
-        <v>234.15999999999988</v>
-      </c>
-      <c r="E455" t="s">
-        <v>7</v>
-      </c>
-      <c r="F455">
-        <v>60.16</v>
-      </c>
-      <c r="G455">
-        <v>60.16</v>
-      </c>
-      <c r="H455">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A456" t="s">
-        <v>36</v>
-      </c>
-      <c r="B456" s="1">
-        <v>45029</v>
-      </c>
-      <c r="C456">
-        <v>4000</v>
-      </c>
-      <c r="D456">
-        <v>238.09999999999994</v>
-      </c>
-      <c r="E456" t="s">
-        <v>7</v>
-      </c>
-      <c r="F456">
-        <v>57.11</v>
-      </c>
-      <c r="G456">
-        <v>57.11</v>
-      </c>
-      <c r="H456">
-        <v>3.94</v>
-      </c>
-    </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B400" s="1"/>
+    </row>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B401" s="1"/>
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B402" s="1"/>
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B403" s="1"/>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B404" s="1"/>
+    </row>
+    <row r="405" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B405" s="1"/>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B406" s="1"/>
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B407" s="1"/>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B408" s="1"/>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B409" s="1"/>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B410" s="1"/>
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B411" s="1"/>
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B412" s="1"/>
+    </row>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B413" s="1"/>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B414" s="1"/>
+    </row>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B415" s="1"/>
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B416" s="1"/>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B417" s="1"/>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B418" s="1"/>
+    </row>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B419" s="1"/>
+    </row>
+    <row r="420" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B420" s="1"/>
+    </row>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B421" s="1"/>
+    </row>
+    <row r="422" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B422" s="1"/>
+    </row>
+    <row r="423" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B423" s="1"/>
+    </row>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B424" s="1"/>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B425" s="1"/>
+    </row>
+    <row r="426" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B426" s="1"/>
+    </row>
+    <row r="427" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B427" s="1"/>
+    </row>
+    <row r="428" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B428" s="1"/>
+    </row>
+    <row r="429" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B429" s="1"/>
+    </row>
+    <row r="430" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B430" s="1"/>
+    </row>
+    <row r="431" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B431" s="1"/>
+    </row>
+    <row r="432" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B432" s="1"/>
+    </row>
+    <row r="433" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B433" s="1"/>
+    </row>
+    <row r="434" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B434" s="1"/>
+    </row>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B435" s="1"/>
+    </row>
+    <row r="436" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B436" s="1"/>
+    </row>
+    <row r="437" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B437" s="1"/>
+    </row>
+    <row r="438" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B438" s="1"/>
+    </row>
+    <row r="439" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B439" s="1"/>
+    </row>
+    <row r="440" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B440" s="1"/>
+    </row>
+    <row r="441" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B441" s="1"/>
+    </row>
+    <row r="442" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B442" s="1"/>
+    </row>
+    <row r="443" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B443" s="1"/>
+    </row>
+    <row r="444" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B444" s="1"/>
+    </row>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B445" s="1"/>
+    </row>
+    <row r="446" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B446" s="1"/>
+    </row>
+    <row r="447" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B447" s="1"/>
+    </row>
+    <row r="448" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B448" s="1"/>
+    </row>
+    <row r="449" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B449" s="1"/>
+    </row>
+    <row r="450" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B450" s="1"/>
+    </row>
+    <row r="451" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B451" s="1"/>
+    </row>
+    <row r="452" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B452" s="1"/>
+    </row>
+    <row r="453" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B453" s="1"/>
+    </row>
+    <row r="454" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B454" s="1"/>
+    </row>
+    <row r="455" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B455" s="1"/>
+    </row>
+    <row r="456" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B456" s="1"/>
+    </row>
+    <row r="457" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B457" s="1"/>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="458" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B458" s="1"/>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="459" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B459" s="1"/>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="460" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B460" s="1"/>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="461" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B461" s="1"/>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="462" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B462" s="1"/>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="463" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B463" s="1"/>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="464" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B464" s="1"/>
     </row>
     <row r="465" spans="2:2" x14ac:dyDescent="0.35">

--- a/pages/TP_Master.xlsx
+++ b/pages/TP_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5E0FC2-F5C6-4684-AD5C-F36C00232EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB106A3-51B3-4474-A0CC-C45FD831F7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2402,1905 +2402,49 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>17</v>
-      </c>
-      <c r="B66" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C66">
-        <v>62.5</v>
-      </c>
-      <c r="D66">
-        <v>9.1000000029999999</v>
-      </c>
-      <c r="E66">
-        <v>9.1</v>
-      </c>
-      <c r="F66">
-        <v>24.73</v>
-      </c>
-      <c r="G66">
-        <v>24.73</v>
-      </c>
-      <c r="H66" t="s">
-        <v>9</v>
-      </c>
-      <c r="I66" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>17</v>
-      </c>
-      <c r="B67" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C67">
-        <v>125</v>
-      </c>
-      <c r="D67">
-        <v>13.960000002999999</v>
-      </c>
-      <c r="E67">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="F67">
-        <v>46.3</v>
-      </c>
-      <c r="G67">
-        <v>46.3</v>
-      </c>
-      <c r="H67" t="s">
-        <v>9</v>
-      </c>
-      <c r="I67" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>17</v>
-      </c>
-      <c r="B68" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C68">
-        <v>187.5</v>
-      </c>
-      <c r="D68">
-        <v>18.140000003000001</v>
-      </c>
-      <c r="E68">
-        <v>4.18</v>
-      </c>
-      <c r="F68">
-        <v>53.83</v>
-      </c>
-      <c r="G68">
-        <v>53.83</v>
-      </c>
-      <c r="H68" t="s">
-        <v>9</v>
-      </c>
-      <c r="I68" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>17</v>
-      </c>
-      <c r="B69" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C69">
-        <v>250</v>
-      </c>
-      <c r="D69">
-        <v>22.160000003</v>
-      </c>
-      <c r="E69">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="F69">
-        <v>55.97</v>
-      </c>
-      <c r="G69">
-        <v>55.97</v>
-      </c>
-      <c r="H69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I69" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>17</v>
-      </c>
-      <c r="B70" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C70">
-        <v>312.5</v>
-      </c>
-      <c r="D70">
-        <v>26.040000002999999</v>
-      </c>
-      <c r="E70">
-        <v>3.88</v>
-      </c>
-      <c r="F70">
-        <v>57.99</v>
-      </c>
-      <c r="G70">
-        <v>57.99</v>
-      </c>
-      <c r="H70" t="s">
-        <v>9</v>
-      </c>
-      <c r="I70" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>17</v>
-      </c>
-      <c r="B71" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C71">
-        <v>375</v>
-      </c>
-      <c r="D71">
-        <v>29.840000003</v>
-      </c>
-      <c r="E71">
-        <v>3.8</v>
-      </c>
-      <c r="F71">
-        <v>59.21</v>
-      </c>
-      <c r="G71">
-        <v>59.21</v>
-      </c>
-      <c r="H71" t="s">
-        <v>9</v>
-      </c>
-      <c r="I71" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>17</v>
-      </c>
-      <c r="B72" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C72">
-        <v>437.5</v>
-      </c>
-      <c r="D72">
-        <v>33.560000002999999</v>
-      </c>
-      <c r="E72">
-        <v>3.72</v>
-      </c>
-      <c r="F72">
-        <v>60.48</v>
-      </c>
-      <c r="G72">
-        <v>60.48</v>
-      </c>
-      <c r="H72" t="s">
-        <v>9</v>
-      </c>
-      <c r="I72" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>17</v>
-      </c>
-      <c r="B73" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C73">
-        <v>500</v>
-      </c>
-      <c r="D73">
-        <v>37.320000002999997</v>
-      </c>
-      <c r="E73">
-        <v>3.76</v>
-      </c>
-      <c r="F73">
-        <v>59.84</v>
-      </c>
-      <c r="G73">
-        <v>59.84</v>
-      </c>
-      <c r="H73" t="s">
-        <v>9</v>
-      </c>
-      <c r="I73" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>17</v>
-      </c>
-      <c r="B74" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C74">
-        <v>562.5</v>
-      </c>
-      <c r="D74">
-        <v>41.200000003</v>
-      </c>
-      <c r="E74">
-        <v>3.88</v>
-      </c>
-      <c r="F74">
-        <v>59.84</v>
-      </c>
-      <c r="G74">
-        <v>57.99</v>
-      </c>
-      <c r="H74" t="s">
-        <v>10</v>
-      </c>
-      <c r="I74" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>17</v>
-      </c>
-      <c r="B75" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C75">
-        <v>625</v>
-      </c>
-      <c r="D75">
-        <v>44.920000002999998</v>
-      </c>
-      <c r="E75">
-        <v>3.72</v>
-      </c>
-      <c r="F75">
-        <v>60.48</v>
-      </c>
-      <c r="G75">
-        <v>60.48</v>
-      </c>
-      <c r="H75" t="s">
-        <v>9</v>
-      </c>
-      <c r="I75" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>17</v>
-      </c>
-      <c r="B76" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C76">
-        <v>687.5</v>
-      </c>
-      <c r="D76">
-        <v>48.660000003</v>
-      </c>
-      <c r="E76">
-        <v>3.74</v>
-      </c>
-      <c r="F76">
-        <v>60.16</v>
-      </c>
-      <c r="G76">
-        <v>60.16</v>
-      </c>
-      <c r="H76" t="s">
-        <v>9</v>
-      </c>
-      <c r="I76" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>17</v>
-      </c>
-      <c r="B77" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C77">
-        <v>750</v>
-      </c>
-      <c r="D77">
-        <v>52.380000002999999</v>
-      </c>
-      <c r="E77">
-        <v>3.72</v>
-      </c>
-      <c r="F77">
-        <v>60.48</v>
-      </c>
-      <c r="G77">
-        <v>60.48</v>
-      </c>
-      <c r="H77" t="s">
-        <v>9</v>
-      </c>
-      <c r="I77" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>17</v>
-      </c>
-      <c r="B78" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C78">
-        <v>812.5</v>
-      </c>
-      <c r="D78">
-        <v>56.120000003000001</v>
-      </c>
-      <c r="E78">
-        <v>3.74</v>
-      </c>
-      <c r="F78">
-        <v>60.16</v>
-      </c>
-      <c r="G78">
-        <v>60.16</v>
-      </c>
-      <c r="H78" t="s">
-        <v>9</v>
-      </c>
-      <c r="I78" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>17</v>
-      </c>
-      <c r="B79" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C79">
-        <v>875</v>
-      </c>
-      <c r="D79">
-        <v>59.840000003</v>
-      </c>
-      <c r="E79">
-        <v>3.72</v>
-      </c>
-      <c r="F79">
-        <v>60.48</v>
-      </c>
-      <c r="G79">
-        <v>60.48</v>
-      </c>
-      <c r="H79" t="s">
-        <v>9</v>
-      </c>
-      <c r="I79" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>17</v>
-      </c>
-      <c r="B80" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C80">
-        <v>937.5</v>
-      </c>
-      <c r="D80">
-        <v>63.660000002999993</v>
-      </c>
-      <c r="E80">
-        <v>3.82</v>
-      </c>
-      <c r="F80">
-        <v>60.81</v>
-      </c>
-      <c r="G80">
-        <v>58.9</v>
-      </c>
-      <c r="H80" t="s">
-        <v>10</v>
-      </c>
-      <c r="I80" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>17</v>
-      </c>
-      <c r="B81" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C81">
-        <v>1000</v>
-      </c>
-      <c r="D81">
-        <v>67.380000002999992</v>
-      </c>
-      <c r="E81">
-        <v>3.72</v>
-      </c>
-      <c r="F81">
-        <v>60.48</v>
-      </c>
-      <c r="G81">
-        <v>60.48</v>
-      </c>
-      <c r="H81" t="s">
-        <v>9</v>
-      </c>
-      <c r="I81" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>17</v>
-      </c>
-      <c r="B82" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C82">
-        <v>1062.5</v>
-      </c>
-      <c r="D82">
-        <v>71.100000003000005</v>
-      </c>
-      <c r="E82">
-        <v>3.72</v>
-      </c>
-      <c r="F82">
-        <v>60.48</v>
-      </c>
-      <c r="G82">
-        <v>60.48</v>
-      </c>
-      <c r="H82" t="s">
-        <v>9</v>
-      </c>
-      <c r="I82" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>17</v>
-      </c>
-      <c r="B83" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C83">
-        <v>1125</v>
-      </c>
-      <c r="D83">
-        <v>74.820000003000004</v>
-      </c>
-      <c r="E83">
-        <v>3.72</v>
-      </c>
-      <c r="F83">
-        <v>60.48</v>
-      </c>
-      <c r="G83">
-        <v>60.48</v>
-      </c>
-      <c r="H83" t="s">
-        <v>9</v>
-      </c>
-      <c r="I83" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>17</v>
-      </c>
-      <c r="B84" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C84">
-        <v>1187.5</v>
-      </c>
-      <c r="D84">
-        <v>78.500000002999997</v>
-      </c>
-      <c r="E84">
-        <v>3.68</v>
-      </c>
-      <c r="F84">
-        <v>61.14</v>
-      </c>
-      <c r="G84">
-        <v>61.14</v>
-      </c>
-      <c r="H84" t="s">
-        <v>9</v>
-      </c>
-      <c r="I84" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>17</v>
-      </c>
-      <c r="B85" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C85">
-        <v>1250</v>
-      </c>
-      <c r="D85">
-        <v>82.220000002999996</v>
-      </c>
-      <c r="E85">
-        <v>3.72</v>
-      </c>
-      <c r="F85">
-        <v>60.48</v>
-      </c>
-      <c r="G85">
-        <v>60.48</v>
-      </c>
-      <c r="H85" t="s">
-        <v>9</v>
-      </c>
-      <c r="I85" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>17</v>
-      </c>
-      <c r="B86" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C86">
-        <v>1312.5</v>
-      </c>
-      <c r="D86">
-        <v>85.960000003000005</v>
-      </c>
-      <c r="E86">
-        <v>3.74</v>
-      </c>
-      <c r="F86">
-        <v>60.16</v>
-      </c>
-      <c r="G86">
-        <v>60.16</v>
-      </c>
-      <c r="H86" t="s">
-        <v>9</v>
-      </c>
-      <c r="I86" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>17</v>
-      </c>
-      <c r="B87" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C87">
-        <v>1375</v>
-      </c>
-      <c r="D87">
-        <v>89.680000003000004</v>
-      </c>
-      <c r="E87">
-        <v>3.72</v>
-      </c>
-      <c r="F87">
-        <v>60.48</v>
-      </c>
-      <c r="G87">
-        <v>60.48</v>
-      </c>
-      <c r="H87" t="s">
-        <v>9</v>
-      </c>
-      <c r="I87" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>17</v>
-      </c>
-      <c r="B88" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C88">
-        <v>1437.5</v>
-      </c>
-      <c r="D88">
-        <v>93.400000003000002</v>
-      </c>
-      <c r="E88">
-        <v>3.72</v>
-      </c>
-      <c r="F88">
-        <v>60.48</v>
-      </c>
-      <c r="G88">
-        <v>60.48</v>
-      </c>
-      <c r="H88" t="s">
-        <v>9</v>
-      </c>
-      <c r="I88" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>17</v>
-      </c>
-      <c r="B89" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C89">
-        <v>1500</v>
-      </c>
-      <c r="D89">
-        <v>97.140000032999993</v>
-      </c>
-      <c r="E89">
-        <v>3.74</v>
-      </c>
-      <c r="F89">
-        <v>60.16</v>
-      </c>
-      <c r="G89">
-        <v>60.16</v>
-      </c>
-      <c r="H89" t="s">
-        <v>9</v>
-      </c>
-      <c r="I89" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>17</v>
-      </c>
-      <c r="B90" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C90">
-        <v>1562.5</v>
-      </c>
-      <c r="D90">
-        <v>101.040000033</v>
-      </c>
-      <c r="E90">
-        <v>3.9</v>
-      </c>
-      <c r="F90">
-        <v>59.52</v>
-      </c>
-      <c r="G90">
-        <v>57.69</v>
-      </c>
-      <c r="H90" t="s">
-        <v>10</v>
-      </c>
-      <c r="I90" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>17</v>
-      </c>
-      <c r="B91" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C91">
-        <v>1625</v>
-      </c>
-      <c r="D91">
-        <v>104.78000003299999</v>
-      </c>
-      <c r="E91">
-        <v>3.74</v>
-      </c>
-      <c r="F91">
-        <v>60.16</v>
-      </c>
-      <c r="G91">
-        <v>60.16</v>
-      </c>
-      <c r="H91" t="s">
-        <v>9</v>
-      </c>
-      <c r="I91" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>17</v>
-      </c>
-      <c r="B92" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C92">
-        <v>1687.5</v>
-      </c>
-      <c r="D92">
-        <v>108.480000033</v>
-      </c>
-      <c r="E92">
-        <v>3.7</v>
-      </c>
-      <c r="F92">
-        <v>60.81</v>
-      </c>
-      <c r="G92">
-        <v>60.81</v>
-      </c>
-      <c r="H92" t="s">
-        <v>9</v>
-      </c>
-      <c r="I92" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>17</v>
-      </c>
-      <c r="B93" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C93">
-        <v>1750</v>
-      </c>
-      <c r="D93">
-        <v>112.20000003299999</v>
-      </c>
-      <c r="E93">
-        <v>3.72</v>
-      </c>
-      <c r="F93">
-        <v>60.48</v>
-      </c>
-      <c r="G93">
-        <v>60.48</v>
-      </c>
-      <c r="H93" t="s">
-        <v>9</v>
-      </c>
-      <c r="I93" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>17</v>
-      </c>
-      <c r="B94" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C94">
-        <v>1812.5</v>
-      </c>
-      <c r="D94">
-        <v>115.960000033</v>
-      </c>
-      <c r="E94">
-        <v>3.76</v>
-      </c>
-      <c r="F94">
-        <v>59.84</v>
-      </c>
-      <c r="G94">
-        <v>59.84</v>
-      </c>
-      <c r="H94" t="s">
-        <v>9</v>
-      </c>
-      <c r="I94" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>17</v>
-      </c>
-      <c r="B95" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C95">
-        <v>1875</v>
-      </c>
-      <c r="D95">
-        <v>119.680000033</v>
-      </c>
-      <c r="E95">
-        <v>3.72</v>
-      </c>
-      <c r="F95">
-        <v>60.48</v>
-      </c>
-      <c r="G95">
-        <v>60.48</v>
-      </c>
-      <c r="H95" t="s">
-        <v>9</v>
-      </c>
-      <c r="I95" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>17</v>
-      </c>
-      <c r="B96" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C96">
-        <v>1937.5</v>
-      </c>
-      <c r="D96">
-        <v>123.380000033</v>
-      </c>
-      <c r="E96">
-        <v>3.7</v>
-      </c>
-      <c r="F96">
-        <v>60.81</v>
-      </c>
-      <c r="G96">
-        <v>60.81</v>
-      </c>
-      <c r="H96" t="s">
-        <v>9</v>
-      </c>
-      <c r="I96" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>17</v>
-      </c>
-      <c r="B97" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C97">
-        <v>2000</v>
-      </c>
-      <c r="D97">
-        <v>127.120000033</v>
-      </c>
-      <c r="E97">
-        <v>3.74</v>
-      </c>
-      <c r="F97">
-        <v>60.16</v>
-      </c>
-      <c r="G97">
-        <v>60.16</v>
-      </c>
-      <c r="H97" t="s">
-        <v>9</v>
-      </c>
-      <c r="I97" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>17</v>
-      </c>
-      <c r="B98" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C98">
-        <v>2062.5</v>
-      </c>
-      <c r="D98">
-        <v>131.00000003299999</v>
-      </c>
-      <c r="E98">
-        <v>3.88</v>
-      </c>
-      <c r="F98">
-        <v>57.99</v>
-      </c>
-      <c r="G98">
-        <v>57.99</v>
-      </c>
-      <c r="H98" t="s">
-        <v>9</v>
-      </c>
-      <c r="I98" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>17</v>
-      </c>
-      <c r="B99" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C99">
-        <v>2125</v>
-      </c>
-      <c r="D99">
-        <v>134.64000003300001</v>
-      </c>
-      <c r="E99">
-        <v>3.64</v>
-      </c>
-      <c r="F99">
-        <v>61.81</v>
-      </c>
-      <c r="G99">
-        <v>61.81</v>
-      </c>
-      <c r="H99" t="s">
-        <v>9</v>
-      </c>
-      <c r="I99" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>17</v>
-      </c>
-      <c r="B100" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C100">
-        <v>2187.5</v>
-      </c>
-      <c r="D100">
-        <v>138.38000003299999</v>
-      </c>
-      <c r="E100">
-        <v>3.74</v>
-      </c>
-      <c r="F100">
-        <v>60.16</v>
-      </c>
-      <c r="G100">
-        <v>60.16</v>
-      </c>
-      <c r="H100" t="s">
-        <v>9</v>
-      </c>
-      <c r="I100" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>17</v>
-      </c>
-      <c r="B101" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C101">
-        <v>2250</v>
-      </c>
-      <c r="D101">
-        <v>142.14000003300001</v>
-      </c>
-      <c r="E101">
-        <v>3.76</v>
-      </c>
-      <c r="F101">
-        <v>59.84</v>
-      </c>
-      <c r="G101">
-        <v>59.84</v>
-      </c>
-      <c r="H101" t="s">
-        <v>9</v>
-      </c>
-      <c r="I101" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>17</v>
-      </c>
-      <c r="B102" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C102">
-        <v>2312.5</v>
-      </c>
-      <c r="D102">
-        <v>146.06000003299999</v>
-      </c>
-      <c r="E102">
-        <v>3.92</v>
-      </c>
-      <c r="F102">
-        <v>59.21</v>
-      </c>
-      <c r="G102">
-        <v>57.4</v>
-      </c>
-      <c r="H102" t="s">
-        <v>10</v>
-      </c>
-      <c r="I102" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>17</v>
-      </c>
-      <c r="B103" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C103">
-        <v>2375</v>
-      </c>
-      <c r="D103">
-        <v>149.82000003300001</v>
-      </c>
-      <c r="E103">
-        <v>3.76</v>
-      </c>
-      <c r="F103">
-        <v>59.84</v>
-      </c>
-      <c r="G103">
-        <v>59.84</v>
-      </c>
-      <c r="H103" t="s">
-        <v>9</v>
-      </c>
-      <c r="I103" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>17</v>
-      </c>
-      <c r="B104" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C104">
-        <v>2437.5</v>
-      </c>
-      <c r="D104">
-        <v>153.559888933</v>
-      </c>
-      <c r="E104">
-        <v>3.74</v>
-      </c>
-      <c r="F104">
-        <v>60.16</v>
-      </c>
-      <c r="G104">
-        <v>60.16</v>
-      </c>
-      <c r="H104" t="s">
-        <v>9</v>
-      </c>
-      <c r="I104" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>17</v>
-      </c>
-      <c r="B105" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C105">
-        <v>2500</v>
-      </c>
-      <c r="D105">
-        <v>157.36000003300001</v>
-      </c>
-      <c r="E105">
-        <v>3.8</v>
-      </c>
-      <c r="F105">
-        <v>59.21</v>
-      </c>
-      <c r="G105">
-        <v>59.21</v>
-      </c>
-      <c r="H105" t="s">
-        <v>9</v>
-      </c>
-      <c r="I105" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>17</v>
-      </c>
-      <c r="B106" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C106">
-        <v>2562.5</v>
-      </c>
-      <c r="D106">
-        <v>161.13838893299999</v>
-      </c>
-      <c r="E106">
-        <v>3.778</v>
-      </c>
-      <c r="F106">
-        <v>59.56</v>
-      </c>
-      <c r="G106">
-        <v>59.56</v>
-      </c>
-      <c r="H106" t="s">
-        <v>9</v>
-      </c>
-      <c r="I106" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>17</v>
-      </c>
-      <c r="B107" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C107">
-        <v>2625</v>
-      </c>
-      <c r="D107">
-        <v>164.92000003300001</v>
-      </c>
-      <c r="E107">
-        <v>3.782</v>
-      </c>
-      <c r="F107">
-        <v>59.49</v>
-      </c>
-      <c r="G107">
-        <v>59.49</v>
-      </c>
-      <c r="H107" t="s">
-        <v>9</v>
-      </c>
-      <c r="I107" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>17</v>
-      </c>
-      <c r="B108" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C108">
-        <v>2687.5</v>
-      </c>
-      <c r="D108">
-        <v>168.82000003300001</v>
-      </c>
-      <c r="E108">
-        <v>3.9</v>
-      </c>
-      <c r="F108">
-        <v>59.52</v>
-      </c>
-      <c r="G108">
-        <v>57.69</v>
-      </c>
-      <c r="H108" t="s">
-        <v>13</v>
-      </c>
-      <c r="I108" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>17</v>
-      </c>
-      <c r="B109" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C109">
-        <v>2750</v>
-      </c>
-      <c r="D109">
-        <v>172.60000003299999</v>
-      </c>
-      <c r="E109">
-        <v>3.78</v>
-      </c>
-      <c r="F109">
-        <v>59.52</v>
-      </c>
-      <c r="G109">
-        <v>59.52</v>
-      </c>
-      <c r="H109" t="s">
-        <v>9</v>
-      </c>
-      <c r="I109" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>17</v>
-      </c>
-      <c r="B110" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C110">
-        <v>2812.5</v>
-      </c>
-      <c r="D110">
-        <v>176.42000003300001</v>
-      </c>
-      <c r="E110">
-        <v>3.82</v>
-      </c>
-      <c r="F110">
-        <v>58.9</v>
-      </c>
-      <c r="G110">
-        <v>58.9</v>
-      </c>
-      <c r="H110" t="s">
-        <v>9</v>
-      </c>
-      <c r="I110" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>17</v>
-      </c>
-      <c r="B111" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C111">
-        <v>2875</v>
-      </c>
-      <c r="D111">
-        <v>180.20000003300001</v>
-      </c>
-      <c r="E111">
-        <v>3.78</v>
-      </c>
-      <c r="F111">
-        <v>59.52</v>
-      </c>
-      <c r="G111">
-        <v>59.52</v>
-      </c>
-      <c r="H111" t="s">
-        <v>9</v>
-      </c>
-      <c r="I111" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>17</v>
-      </c>
-      <c r="B112" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C112">
-        <v>2937.5</v>
-      </c>
-      <c r="D112">
-        <v>184.080000033</v>
-      </c>
-      <c r="E112">
-        <v>3.88</v>
-      </c>
-      <c r="F112">
-        <v>59.84</v>
-      </c>
-      <c r="G112">
-        <v>57.99</v>
-      </c>
-      <c r="H112" t="s">
-        <v>10</v>
-      </c>
-      <c r="I112" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>17</v>
-      </c>
-      <c r="B113" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C113">
-        <v>3000</v>
-      </c>
-      <c r="D113">
-        <v>187.86000003300001</v>
-      </c>
-      <c r="E113">
-        <v>3.78</v>
-      </c>
-      <c r="F113">
-        <v>59.52</v>
-      </c>
-      <c r="G113">
-        <v>59.52</v>
-      </c>
-      <c r="H113" t="s">
-        <v>9</v>
-      </c>
-      <c r="I113" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>17</v>
-      </c>
-      <c r="B114" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C114">
-        <v>3062.5</v>
-      </c>
-      <c r="D114">
-        <v>191.64000003300001</v>
-      </c>
-      <c r="E114">
-        <v>3.78</v>
-      </c>
-      <c r="F114">
-        <v>59.52</v>
-      </c>
-      <c r="G114">
-        <v>59.52</v>
-      </c>
-      <c r="H114" t="s">
-        <v>9</v>
-      </c>
-      <c r="I114" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>17</v>
-      </c>
-      <c r="B115" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C115">
-        <v>3125</v>
-      </c>
-      <c r="D115">
-        <v>195.400000033</v>
-      </c>
-      <c r="E115">
-        <v>3.76</v>
-      </c>
-      <c r="F115">
-        <v>59.84</v>
-      </c>
-      <c r="G115">
-        <v>59.84</v>
-      </c>
-      <c r="H115" t="s">
-        <v>9</v>
-      </c>
-      <c r="I115" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>17</v>
-      </c>
-      <c r="B116" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C116">
-        <v>3187.5</v>
-      </c>
-      <c r="D116">
-        <v>199.16000003299999</v>
-      </c>
-      <c r="E116">
-        <v>3.76</v>
-      </c>
-      <c r="F116">
-        <v>59.84</v>
-      </c>
-      <c r="G116">
-        <v>59.84</v>
-      </c>
-      <c r="H116" t="s">
-        <v>9</v>
-      </c>
-      <c r="I116" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>17</v>
-      </c>
-      <c r="B117" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C117">
-        <v>3250</v>
-      </c>
-      <c r="D117">
-        <v>202.94000003299999</v>
-      </c>
-      <c r="E117">
-        <v>3.78</v>
-      </c>
-      <c r="F117">
-        <v>59.52</v>
-      </c>
-      <c r="G117">
-        <v>59.52</v>
-      </c>
-      <c r="H117" t="s">
-        <v>9</v>
-      </c>
-      <c r="I117" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>17</v>
-      </c>
-      <c r="B118" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C118">
-        <v>3312.5</v>
-      </c>
-      <c r="D118">
-        <v>206.840000033</v>
-      </c>
-      <c r="E118">
-        <v>3.9</v>
-      </c>
-      <c r="F118">
-        <v>59.52</v>
-      </c>
-      <c r="G118">
-        <v>57.69</v>
-      </c>
-      <c r="H118" t="s">
-        <v>10</v>
-      </c>
-      <c r="I118" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>17</v>
-      </c>
-      <c r="B119" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C119">
-        <v>3375</v>
-      </c>
-      <c r="D119">
-        <v>210.60000003299999</v>
-      </c>
-      <c r="E119">
-        <v>3.76</v>
-      </c>
-      <c r="F119">
-        <v>59.84</v>
-      </c>
-      <c r="G119">
-        <v>59.84</v>
-      </c>
-      <c r="H119" t="s">
-        <v>9</v>
-      </c>
-      <c r="I119" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>17</v>
-      </c>
-      <c r="B120" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C120">
-        <v>3437.5</v>
-      </c>
-      <c r="D120">
-        <v>214.32000003300001</v>
-      </c>
-      <c r="E120">
-        <v>3.72</v>
-      </c>
-      <c r="F120">
-        <v>60.48</v>
-      </c>
-      <c r="G120">
-        <v>60.48</v>
-      </c>
-      <c r="H120" t="s">
-        <v>9</v>
-      </c>
-      <c r="I120" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>17</v>
-      </c>
-      <c r="B121" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C121">
-        <v>3500</v>
-      </c>
-      <c r="D121">
-        <v>218.10000003299999</v>
-      </c>
-      <c r="E121">
-        <v>3.78</v>
-      </c>
-      <c r="F121">
-        <v>59.52</v>
-      </c>
-      <c r="G121">
-        <v>59.52</v>
-      </c>
-      <c r="H121" t="s">
-        <v>9</v>
-      </c>
-      <c r="I121" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>17</v>
-      </c>
-      <c r="B122" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C122">
-        <v>3562.5</v>
-      </c>
-      <c r="D122">
-        <v>221.88000003299999</v>
-      </c>
-      <c r="E122">
-        <v>3.78</v>
-      </c>
-      <c r="F122">
-        <v>59.52</v>
-      </c>
-      <c r="G122">
-        <v>59.52</v>
-      </c>
-      <c r="H122" t="s">
-        <v>9</v>
-      </c>
-      <c r="I122" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>17</v>
-      </c>
-      <c r="B123" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C123">
-        <v>3625</v>
-      </c>
-      <c r="D123">
-        <v>225.620000033</v>
-      </c>
-      <c r="E123">
-        <v>3.74</v>
-      </c>
-      <c r="F123">
-        <v>60.16</v>
-      </c>
-      <c r="G123">
-        <v>60.16</v>
-      </c>
-      <c r="H123" t="s">
-        <v>9</v>
-      </c>
-      <c r="I123" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>17</v>
-      </c>
-      <c r="B124" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C124">
-        <v>3687.5</v>
-      </c>
-      <c r="D124">
-        <v>229.340000033</v>
-      </c>
-      <c r="E124">
-        <v>3.72</v>
-      </c>
-      <c r="F124">
-        <v>60.48</v>
-      </c>
-      <c r="G124">
-        <v>60.48</v>
-      </c>
-      <c r="H124" t="s">
-        <v>9</v>
-      </c>
-      <c r="I124" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>17</v>
-      </c>
-      <c r="B125" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C125">
-        <v>3750</v>
-      </c>
-      <c r="D125">
-        <v>233.080000033</v>
-      </c>
-      <c r="E125">
-        <v>3.74</v>
-      </c>
-      <c r="F125">
-        <v>60.16</v>
-      </c>
-      <c r="G125">
-        <v>60.16</v>
-      </c>
-      <c r="H125" t="s">
-        <v>9</v>
-      </c>
-      <c r="I125" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>17</v>
-      </c>
-      <c r="B126" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C126">
-        <v>3812.5</v>
-      </c>
-      <c r="D126">
-        <v>236.82000003300001</v>
-      </c>
-      <c r="E126">
-        <v>3.74</v>
-      </c>
-      <c r="F126">
-        <v>60.16</v>
-      </c>
-      <c r="G126">
-        <v>60.16</v>
-      </c>
-      <c r="H126" t="s">
-        <v>9</v>
-      </c>
-      <c r="I126" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>17</v>
-      </c>
-      <c r="B127" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C127">
-        <v>3875</v>
-      </c>
-      <c r="D127">
-        <v>240.580000033</v>
-      </c>
-      <c r="E127">
-        <v>3.76</v>
-      </c>
-      <c r="F127">
-        <v>59.84</v>
-      </c>
-      <c r="G127">
-        <v>59.84</v>
-      </c>
-      <c r="H127" t="s">
-        <v>9</v>
-      </c>
-      <c r="I127" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>17</v>
-      </c>
-      <c r="B128" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C128">
-        <v>3937.5</v>
-      </c>
-      <c r="D128">
-        <v>244.38000003299999</v>
-      </c>
-      <c r="E128">
-        <v>3.8</v>
-      </c>
-      <c r="F128">
-        <v>59.21</v>
-      </c>
-      <c r="G128">
-        <v>59.21</v>
-      </c>
-      <c r="H128" t="s">
-        <v>9</v>
-      </c>
-      <c r="I128" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>17</v>
-      </c>
-      <c r="B129" s="2">
-        <v>45069</v>
-      </c>
-      <c r="C129">
-        <v>4000</v>
-      </c>
-      <c r="D129">
-        <v>248.400000033</v>
-      </c>
-      <c r="E129">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="F129">
-        <v>55.97</v>
-      </c>
-      <c r="G129">
-        <v>55.97</v>
-      </c>
-      <c r="H129" t="s">
-        <v>14</v>
-      </c>
-      <c r="I129" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B130" s="2"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B131" s="2"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B132" s="2"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B133" s="2"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B134" s="2"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B135" s="2"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B136" s="2"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B137" s="2"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B138" s="2"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B139" s="2"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B140" s="2"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B141" s="2"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B142" s="2"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B143" s="2"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B144" s="2"/>
     </row>
     <row r="145" spans="2:2" x14ac:dyDescent="0.3">
@@ -4399,244 +2543,1908 @@
     <row r="176" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B176" s="2"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B177" s="2"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B178" s="2"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B179" s="2"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B180" s="2"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B181" s="2"/>
-    </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B182" s="2"/>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B183" s="2"/>
-    </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B184" s="2"/>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B185" s="2"/>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B186" s="2"/>
-    </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B187" s="2"/>
-    </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B188" s="2"/>
-    </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B189" s="2"/>
-    </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B190" s="2"/>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B191" s="2"/>
-    </row>
-    <row r="192" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B192" s="2"/>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B193" s="2"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B194" s="2"/>
-    </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B195" s="2"/>
-    </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B196" s="2"/>
-    </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B197" s="2"/>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B198" s="2"/>
-    </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B199" s="2"/>
-    </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B200" s="2"/>
-    </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B201" s="2"/>
-    </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B202" s="2"/>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B203" s="2"/>
-    </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B204" s="2"/>
-    </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B205" s="2"/>
-    </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B206" s="2"/>
-    </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B207" s="2"/>
-    </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B208" s="2"/>
-    </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B209" s="2"/>
-    </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B210" s="2"/>
-    </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B211" s="2"/>
-    </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B212" s="2"/>
-    </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B213" s="2"/>
-    </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B214" s="2"/>
-    </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B215" s="2"/>
-    </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B216" s="2"/>
-    </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B217" s="2"/>
-    </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B218" s="2"/>
-    </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B219" s="2"/>
-    </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B220" s="2"/>
-    </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B221" s="2"/>
-    </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B222" s="2"/>
-    </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B223" s="2"/>
-    </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B224" s="2"/>
-    </row>
-    <row r="225" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B225" s="2"/>
-    </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B226" s="2"/>
-    </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B227" s="2"/>
-    </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B228" s="2"/>
-    </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B229" s="2"/>
-    </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B230" s="2"/>
-    </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B231" s="2"/>
-    </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B232" s="2"/>
-    </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B233" s="2"/>
-    </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B234" s="2"/>
-    </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B235" s="2"/>
-    </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B236" s="2"/>
-    </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B237" s="2"/>
-    </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B238" s="2"/>
-    </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B239" s="2"/>
-    </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B240" s="2"/>
-    </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B241" s="2"/>
-    </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B242" s="2"/>
-    </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B243" s="2"/>
-    </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B244" s="2"/>
-    </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>17</v>
+      </c>
+      <c r="B181" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C181">
+        <v>62.5</v>
+      </c>
+      <c r="D181">
+        <v>9.1000000029999999</v>
+      </c>
+      <c r="E181">
+        <v>9.1</v>
+      </c>
+      <c r="F181">
+        <v>24.73</v>
+      </c>
+      <c r="G181">
+        <v>24.73</v>
+      </c>
+      <c r="H181" t="s">
+        <v>9</v>
+      </c>
+      <c r="I181" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>17</v>
+      </c>
+      <c r="B182" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C182">
+        <v>125</v>
+      </c>
+      <c r="D182">
+        <v>13.960000002999999</v>
+      </c>
+      <c r="E182">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="F182">
+        <v>46.3</v>
+      </c>
+      <c r="G182">
+        <v>46.3</v>
+      </c>
+      <c r="H182" t="s">
+        <v>9</v>
+      </c>
+      <c r="I182" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>17</v>
+      </c>
+      <c r="B183" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C183">
+        <v>187.5</v>
+      </c>
+      <c r="D183">
+        <v>18.140000003000001</v>
+      </c>
+      <c r="E183">
+        <v>4.18</v>
+      </c>
+      <c r="F183">
+        <v>53.83</v>
+      </c>
+      <c r="G183">
+        <v>53.83</v>
+      </c>
+      <c r="H183" t="s">
+        <v>9</v>
+      </c>
+      <c r="I183" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>17</v>
+      </c>
+      <c r="B184" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C184">
+        <v>250</v>
+      </c>
+      <c r="D184">
+        <v>22.160000003</v>
+      </c>
+      <c r="E184">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F184">
+        <v>55.97</v>
+      </c>
+      <c r="G184">
+        <v>55.97</v>
+      </c>
+      <c r="H184" t="s">
+        <v>9</v>
+      </c>
+      <c r="I184" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>17</v>
+      </c>
+      <c r="B185" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C185">
+        <v>312.5</v>
+      </c>
+      <c r="D185">
+        <v>26.040000002999999</v>
+      </c>
+      <c r="E185">
+        <v>3.88</v>
+      </c>
+      <c r="F185">
+        <v>57.99</v>
+      </c>
+      <c r="G185">
+        <v>57.99</v>
+      </c>
+      <c r="H185" t="s">
+        <v>9</v>
+      </c>
+      <c r="I185" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>17</v>
+      </c>
+      <c r="B186" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C186">
+        <v>375</v>
+      </c>
+      <c r="D186">
+        <v>29.840000003</v>
+      </c>
+      <c r="E186">
+        <v>3.8</v>
+      </c>
+      <c r="F186">
+        <v>59.21</v>
+      </c>
+      <c r="G186">
+        <v>59.21</v>
+      </c>
+      <c r="H186" t="s">
+        <v>9</v>
+      </c>
+      <c r="I186" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>17</v>
+      </c>
+      <c r="B187" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C187">
+        <v>437.5</v>
+      </c>
+      <c r="D187">
+        <v>33.560000002999999</v>
+      </c>
+      <c r="E187">
+        <v>3.72</v>
+      </c>
+      <c r="F187">
+        <v>60.48</v>
+      </c>
+      <c r="G187">
+        <v>60.48</v>
+      </c>
+      <c r="H187" t="s">
+        <v>9</v>
+      </c>
+      <c r="I187" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>17</v>
+      </c>
+      <c r="B188" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C188">
+        <v>500</v>
+      </c>
+      <c r="D188">
+        <v>37.320000002999997</v>
+      </c>
+      <c r="E188">
+        <v>3.76</v>
+      </c>
+      <c r="F188">
+        <v>59.84</v>
+      </c>
+      <c r="G188">
+        <v>59.84</v>
+      </c>
+      <c r="H188" t="s">
+        <v>9</v>
+      </c>
+      <c r="I188" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>17</v>
+      </c>
+      <c r="B189" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C189">
+        <v>562.5</v>
+      </c>
+      <c r="D189">
+        <v>41.200000003</v>
+      </c>
+      <c r="E189">
+        <v>3.88</v>
+      </c>
+      <c r="F189">
+        <v>59.84</v>
+      </c>
+      <c r="G189">
+        <v>57.99</v>
+      </c>
+      <c r="H189" t="s">
+        <v>10</v>
+      </c>
+      <c r="I189" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>17</v>
+      </c>
+      <c r="B190" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C190">
+        <v>625</v>
+      </c>
+      <c r="D190">
+        <v>44.920000002999998</v>
+      </c>
+      <c r="E190">
+        <v>3.72</v>
+      </c>
+      <c r="F190">
+        <v>60.48</v>
+      </c>
+      <c r="G190">
+        <v>60.48</v>
+      </c>
+      <c r="H190" t="s">
+        <v>9</v>
+      </c>
+      <c r="I190" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>17</v>
+      </c>
+      <c r="B191" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C191">
+        <v>687.5</v>
+      </c>
+      <c r="D191">
+        <v>48.660000003</v>
+      </c>
+      <c r="E191">
+        <v>3.74</v>
+      </c>
+      <c r="F191">
+        <v>60.16</v>
+      </c>
+      <c r="G191">
+        <v>60.16</v>
+      </c>
+      <c r="H191" t="s">
+        <v>9</v>
+      </c>
+      <c r="I191" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>17</v>
+      </c>
+      <c r="B192" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C192">
+        <v>750</v>
+      </c>
+      <c r="D192">
+        <v>52.380000002999999</v>
+      </c>
+      <c r="E192">
+        <v>3.72</v>
+      </c>
+      <c r="F192">
+        <v>60.48</v>
+      </c>
+      <c r="G192">
+        <v>60.48</v>
+      </c>
+      <c r="H192" t="s">
+        <v>9</v>
+      </c>
+      <c r="I192" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>17</v>
+      </c>
+      <c r="B193" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C193">
+        <v>812.5</v>
+      </c>
+      <c r="D193">
+        <v>56.120000003000001</v>
+      </c>
+      <c r="E193">
+        <v>3.74</v>
+      </c>
+      <c r="F193">
+        <v>60.16</v>
+      </c>
+      <c r="G193">
+        <v>60.16</v>
+      </c>
+      <c r="H193" t="s">
+        <v>9</v>
+      </c>
+      <c r="I193" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>17</v>
+      </c>
+      <c r="B194" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C194">
+        <v>875</v>
+      </c>
+      <c r="D194">
+        <v>59.840000003</v>
+      </c>
+      <c r="E194">
+        <v>3.72</v>
+      </c>
+      <c r="F194">
+        <v>60.48</v>
+      </c>
+      <c r="G194">
+        <v>60.48</v>
+      </c>
+      <c r="H194" t="s">
+        <v>9</v>
+      </c>
+      <c r="I194" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>17</v>
+      </c>
+      <c r="B195" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C195">
+        <v>937.5</v>
+      </c>
+      <c r="D195">
+        <v>63.660000002999993</v>
+      </c>
+      <c r="E195">
+        <v>3.82</v>
+      </c>
+      <c r="F195">
+        <v>60.81</v>
+      </c>
+      <c r="G195">
+        <v>58.9</v>
+      </c>
+      <c r="H195" t="s">
+        <v>10</v>
+      </c>
+      <c r="I195" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>17</v>
+      </c>
+      <c r="B196" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C196">
+        <v>1000</v>
+      </c>
+      <c r="D196">
+        <v>67.380000002999992</v>
+      </c>
+      <c r="E196">
+        <v>3.72</v>
+      </c>
+      <c r="F196">
+        <v>60.48</v>
+      </c>
+      <c r="G196">
+        <v>60.48</v>
+      </c>
+      <c r="H196" t="s">
+        <v>9</v>
+      </c>
+      <c r="I196" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>17</v>
+      </c>
+      <c r="B197" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C197">
+        <v>1062.5</v>
+      </c>
+      <c r="D197">
+        <v>71.100000003000005</v>
+      </c>
+      <c r="E197">
+        <v>3.72</v>
+      </c>
+      <c r="F197">
+        <v>60.48</v>
+      </c>
+      <c r="G197">
+        <v>60.48</v>
+      </c>
+      <c r="H197" t="s">
+        <v>9</v>
+      </c>
+      <c r="I197" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>17</v>
+      </c>
+      <c r="B198" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C198">
+        <v>1125</v>
+      </c>
+      <c r="D198">
+        <v>74.820000003000004</v>
+      </c>
+      <c r="E198">
+        <v>3.72</v>
+      </c>
+      <c r="F198">
+        <v>60.48</v>
+      </c>
+      <c r="G198">
+        <v>60.48</v>
+      </c>
+      <c r="H198" t="s">
+        <v>9</v>
+      </c>
+      <c r="I198" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>17</v>
+      </c>
+      <c r="B199" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C199">
+        <v>1187.5</v>
+      </c>
+      <c r="D199">
+        <v>78.500000002999997</v>
+      </c>
+      <c r="E199">
+        <v>3.68</v>
+      </c>
+      <c r="F199">
+        <v>61.14</v>
+      </c>
+      <c r="G199">
+        <v>61.14</v>
+      </c>
+      <c r="H199" t="s">
+        <v>9</v>
+      </c>
+      <c r="I199" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>17</v>
+      </c>
+      <c r="B200" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C200">
+        <v>1250</v>
+      </c>
+      <c r="D200">
+        <v>82.220000002999996</v>
+      </c>
+      <c r="E200">
+        <v>3.72</v>
+      </c>
+      <c r="F200">
+        <v>60.48</v>
+      </c>
+      <c r="G200">
+        <v>60.48</v>
+      </c>
+      <c r="H200" t="s">
+        <v>9</v>
+      </c>
+      <c r="I200" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>17</v>
+      </c>
+      <c r="B201" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C201">
+        <v>1312.5</v>
+      </c>
+      <c r="D201">
+        <v>85.960000003000005</v>
+      </c>
+      <c r="E201">
+        <v>3.74</v>
+      </c>
+      <c r="F201">
+        <v>60.16</v>
+      </c>
+      <c r="G201">
+        <v>60.16</v>
+      </c>
+      <c r="H201" t="s">
+        <v>9</v>
+      </c>
+      <c r="I201" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>17</v>
+      </c>
+      <c r="B202" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C202">
+        <v>1375</v>
+      </c>
+      <c r="D202">
+        <v>89.680000003000004</v>
+      </c>
+      <c r="E202">
+        <v>3.72</v>
+      </c>
+      <c r="F202">
+        <v>60.48</v>
+      </c>
+      <c r="G202">
+        <v>60.48</v>
+      </c>
+      <c r="H202" t="s">
+        <v>9</v>
+      </c>
+      <c r="I202" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>17</v>
+      </c>
+      <c r="B203" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C203">
+        <v>1437.5</v>
+      </c>
+      <c r="D203">
+        <v>93.400000003000002</v>
+      </c>
+      <c r="E203">
+        <v>3.72</v>
+      </c>
+      <c r="F203">
+        <v>60.48</v>
+      </c>
+      <c r="G203">
+        <v>60.48</v>
+      </c>
+      <c r="H203" t="s">
+        <v>9</v>
+      </c>
+      <c r="I203" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>17</v>
+      </c>
+      <c r="B204" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C204">
+        <v>1500</v>
+      </c>
+      <c r="D204">
+        <v>97.140000032999993</v>
+      </c>
+      <c r="E204">
+        <v>3.74</v>
+      </c>
+      <c r="F204">
+        <v>60.16</v>
+      </c>
+      <c r="G204">
+        <v>60.16</v>
+      </c>
+      <c r="H204" t="s">
+        <v>9</v>
+      </c>
+      <c r="I204" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>17</v>
+      </c>
+      <c r="B205" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C205">
+        <v>1562.5</v>
+      </c>
+      <c r="D205">
+        <v>101.040000033</v>
+      </c>
+      <c r="E205">
+        <v>3.9</v>
+      </c>
+      <c r="F205">
+        <v>59.52</v>
+      </c>
+      <c r="G205">
+        <v>57.69</v>
+      </c>
+      <c r="H205" t="s">
+        <v>10</v>
+      </c>
+      <c r="I205" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>17</v>
+      </c>
+      <c r="B206" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C206">
+        <v>1625</v>
+      </c>
+      <c r="D206">
+        <v>104.78000003299999</v>
+      </c>
+      <c r="E206">
+        <v>3.74</v>
+      </c>
+      <c r="F206">
+        <v>60.16</v>
+      </c>
+      <c r="G206">
+        <v>60.16</v>
+      </c>
+      <c r="H206" t="s">
+        <v>9</v>
+      </c>
+      <c r="I206" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>17</v>
+      </c>
+      <c r="B207" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C207">
+        <v>1687.5</v>
+      </c>
+      <c r="D207">
+        <v>108.480000033</v>
+      </c>
+      <c r="E207">
+        <v>3.7</v>
+      </c>
+      <c r="F207">
+        <v>60.81</v>
+      </c>
+      <c r="G207">
+        <v>60.81</v>
+      </c>
+      <c r="H207" t="s">
+        <v>9</v>
+      </c>
+      <c r="I207" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>17</v>
+      </c>
+      <c r="B208" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C208">
+        <v>1750</v>
+      </c>
+      <c r="D208">
+        <v>112.20000003299999</v>
+      </c>
+      <c r="E208">
+        <v>3.72</v>
+      </c>
+      <c r="F208">
+        <v>60.48</v>
+      </c>
+      <c r="G208">
+        <v>60.48</v>
+      </c>
+      <c r="H208" t="s">
+        <v>9</v>
+      </c>
+      <c r="I208" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>17</v>
+      </c>
+      <c r="B209" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C209">
+        <v>1812.5</v>
+      </c>
+      <c r="D209">
+        <v>115.960000033</v>
+      </c>
+      <c r="E209">
+        <v>3.76</v>
+      </c>
+      <c r="F209">
+        <v>59.84</v>
+      </c>
+      <c r="G209">
+        <v>59.84</v>
+      </c>
+      <c r="H209" t="s">
+        <v>9</v>
+      </c>
+      <c r="I209" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>17</v>
+      </c>
+      <c r="B210" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C210">
+        <v>1875</v>
+      </c>
+      <c r="D210">
+        <v>119.680000033</v>
+      </c>
+      <c r="E210">
+        <v>3.72</v>
+      </c>
+      <c r="F210">
+        <v>60.48</v>
+      </c>
+      <c r="G210">
+        <v>60.48</v>
+      </c>
+      <c r="H210" t="s">
+        <v>9</v>
+      </c>
+      <c r="I210" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>17</v>
+      </c>
+      <c r="B211" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C211">
+        <v>1937.5</v>
+      </c>
+      <c r="D211">
+        <v>123.380000033</v>
+      </c>
+      <c r="E211">
+        <v>3.7</v>
+      </c>
+      <c r="F211">
+        <v>60.81</v>
+      </c>
+      <c r="G211">
+        <v>60.81</v>
+      </c>
+      <c r="H211" t="s">
+        <v>9</v>
+      </c>
+      <c r="I211" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>17</v>
+      </c>
+      <c r="B212" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C212">
+        <v>2000</v>
+      </c>
+      <c r="D212">
+        <v>127.120000033</v>
+      </c>
+      <c r="E212">
+        <v>3.74</v>
+      </c>
+      <c r="F212">
+        <v>60.16</v>
+      </c>
+      <c r="G212">
+        <v>60.16</v>
+      </c>
+      <c r="H212" t="s">
+        <v>9</v>
+      </c>
+      <c r="I212" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>17</v>
+      </c>
+      <c r="B213" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C213">
+        <v>2062.5</v>
+      </c>
+      <c r="D213">
+        <v>131.00000003299999</v>
+      </c>
+      <c r="E213">
+        <v>3.88</v>
+      </c>
+      <c r="F213">
+        <v>57.99</v>
+      </c>
+      <c r="G213">
+        <v>57.99</v>
+      </c>
+      <c r="H213" t="s">
+        <v>9</v>
+      </c>
+      <c r="I213" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>17</v>
+      </c>
+      <c r="B214" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C214">
+        <v>2125</v>
+      </c>
+      <c r="D214">
+        <v>134.64000003300001</v>
+      </c>
+      <c r="E214">
+        <v>3.64</v>
+      </c>
+      <c r="F214">
+        <v>61.81</v>
+      </c>
+      <c r="G214">
+        <v>61.81</v>
+      </c>
+      <c r="H214" t="s">
+        <v>9</v>
+      </c>
+      <c r="I214" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>17</v>
+      </c>
+      <c r="B215" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C215">
+        <v>2187.5</v>
+      </c>
+      <c r="D215">
+        <v>138.38000003299999</v>
+      </c>
+      <c r="E215">
+        <v>3.74</v>
+      </c>
+      <c r="F215">
+        <v>60.16</v>
+      </c>
+      <c r="G215">
+        <v>60.16</v>
+      </c>
+      <c r="H215" t="s">
+        <v>9</v>
+      </c>
+      <c r="I215" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>17</v>
+      </c>
+      <c r="B216" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C216">
+        <v>2250</v>
+      </c>
+      <c r="D216">
+        <v>142.14000003300001</v>
+      </c>
+      <c r="E216">
+        <v>3.76</v>
+      </c>
+      <c r="F216">
+        <v>59.84</v>
+      </c>
+      <c r="G216">
+        <v>59.84</v>
+      </c>
+      <c r="H216" t="s">
+        <v>9</v>
+      </c>
+      <c r="I216" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>17</v>
+      </c>
+      <c r="B217" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C217">
+        <v>2312.5</v>
+      </c>
+      <c r="D217">
+        <v>146.06000003299999</v>
+      </c>
+      <c r="E217">
+        <v>3.92</v>
+      </c>
+      <c r="F217">
+        <v>59.21</v>
+      </c>
+      <c r="G217">
+        <v>57.4</v>
+      </c>
+      <c r="H217" t="s">
+        <v>10</v>
+      </c>
+      <c r="I217" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>17</v>
+      </c>
+      <c r="B218" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C218">
+        <v>2375</v>
+      </c>
+      <c r="D218">
+        <v>149.82000003300001</v>
+      </c>
+      <c r="E218">
+        <v>3.76</v>
+      </c>
+      <c r="F218">
+        <v>59.84</v>
+      </c>
+      <c r="G218">
+        <v>59.84</v>
+      </c>
+      <c r="H218" t="s">
+        <v>9</v>
+      </c>
+      <c r="I218" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>17</v>
+      </c>
+      <c r="B219" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C219">
+        <v>2437.5</v>
+      </c>
+      <c r="D219">
+        <v>153.559888933</v>
+      </c>
+      <c r="E219">
+        <v>3.74</v>
+      </c>
+      <c r="F219">
+        <v>60.16</v>
+      </c>
+      <c r="G219">
+        <v>60.16</v>
+      </c>
+      <c r="H219" t="s">
+        <v>9</v>
+      </c>
+      <c r="I219" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>17</v>
+      </c>
+      <c r="B220" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C220">
+        <v>2500</v>
+      </c>
+      <c r="D220">
+        <v>157.36000003300001</v>
+      </c>
+      <c r="E220">
+        <v>3.8</v>
+      </c>
+      <c r="F220">
+        <v>59.21</v>
+      </c>
+      <c r="G220">
+        <v>59.21</v>
+      </c>
+      <c r="H220" t="s">
+        <v>9</v>
+      </c>
+      <c r="I220" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>17</v>
+      </c>
+      <c r="B221" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C221">
+        <v>2562.5</v>
+      </c>
+      <c r="D221">
+        <v>161.13838893299999</v>
+      </c>
+      <c r="E221">
+        <v>3.778</v>
+      </c>
+      <c r="F221">
+        <v>59.56</v>
+      </c>
+      <c r="G221">
+        <v>59.56</v>
+      </c>
+      <c r="H221" t="s">
+        <v>9</v>
+      </c>
+      <c r="I221" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>17</v>
+      </c>
+      <c r="B222" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C222">
+        <v>2625</v>
+      </c>
+      <c r="D222">
+        <v>164.92000003300001</v>
+      </c>
+      <c r="E222">
+        <v>3.782</v>
+      </c>
+      <c r="F222">
+        <v>59.49</v>
+      </c>
+      <c r="G222">
+        <v>59.49</v>
+      </c>
+      <c r="H222" t="s">
+        <v>9</v>
+      </c>
+      <c r="I222" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>17</v>
+      </c>
+      <c r="B223" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C223">
+        <v>2687.5</v>
+      </c>
+      <c r="D223">
+        <v>168.82000003300001</v>
+      </c>
+      <c r="E223">
+        <v>3.9</v>
+      </c>
+      <c r="F223">
+        <v>59.52</v>
+      </c>
+      <c r="G223">
+        <v>57.69</v>
+      </c>
+      <c r="H223" t="s">
+        <v>13</v>
+      </c>
+      <c r="I223" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>17</v>
+      </c>
+      <c r="B224" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C224">
+        <v>2750</v>
+      </c>
+      <c r="D224">
+        <v>172.60000003299999</v>
+      </c>
+      <c r="E224">
+        <v>3.78</v>
+      </c>
+      <c r="F224">
+        <v>59.52</v>
+      </c>
+      <c r="G224">
+        <v>59.52</v>
+      </c>
+      <c r="H224" t="s">
+        <v>9</v>
+      </c>
+      <c r="I224" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>17</v>
+      </c>
+      <c r="B225" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C225">
+        <v>2812.5</v>
+      </c>
+      <c r="D225">
+        <v>176.42000003300001</v>
+      </c>
+      <c r="E225">
+        <v>3.82</v>
+      </c>
+      <c r="F225">
+        <v>58.9</v>
+      </c>
+      <c r="G225">
+        <v>58.9</v>
+      </c>
+      <c r="H225" t="s">
+        <v>9</v>
+      </c>
+      <c r="I225" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>17</v>
+      </c>
+      <c r="B226" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C226">
+        <v>2875</v>
+      </c>
+      <c r="D226">
+        <v>180.20000003300001</v>
+      </c>
+      <c r="E226">
+        <v>3.78</v>
+      </c>
+      <c r="F226">
+        <v>59.52</v>
+      </c>
+      <c r="G226">
+        <v>59.52</v>
+      </c>
+      <c r="H226" t="s">
+        <v>9</v>
+      </c>
+      <c r="I226" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>17</v>
+      </c>
+      <c r="B227" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C227">
+        <v>2937.5</v>
+      </c>
+      <c r="D227">
+        <v>184.080000033</v>
+      </c>
+      <c r="E227">
+        <v>3.88</v>
+      </c>
+      <c r="F227">
+        <v>59.84</v>
+      </c>
+      <c r="G227">
+        <v>57.99</v>
+      </c>
+      <c r="H227" t="s">
+        <v>10</v>
+      </c>
+      <c r="I227" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>17</v>
+      </c>
+      <c r="B228" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C228">
+        <v>3000</v>
+      </c>
+      <c r="D228">
+        <v>187.86000003300001</v>
+      </c>
+      <c r="E228">
+        <v>3.78</v>
+      </c>
+      <c r="F228">
+        <v>59.52</v>
+      </c>
+      <c r="G228">
+        <v>59.52</v>
+      </c>
+      <c r="H228" t="s">
+        <v>9</v>
+      </c>
+      <c r="I228" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>17</v>
+      </c>
+      <c r="B229" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C229">
+        <v>3062.5</v>
+      </c>
+      <c r="D229">
+        <v>191.64000003300001</v>
+      </c>
+      <c r="E229">
+        <v>3.78</v>
+      </c>
+      <c r="F229">
+        <v>59.52</v>
+      </c>
+      <c r="G229">
+        <v>59.52</v>
+      </c>
+      <c r="H229" t="s">
+        <v>9</v>
+      </c>
+      <c r="I229" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>17</v>
+      </c>
+      <c r="B230" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C230">
+        <v>3125</v>
+      </c>
+      <c r="D230">
+        <v>195.400000033</v>
+      </c>
+      <c r="E230">
+        <v>3.76</v>
+      </c>
+      <c r="F230">
+        <v>59.84</v>
+      </c>
+      <c r="G230">
+        <v>59.84</v>
+      </c>
+      <c r="H230" t="s">
+        <v>9</v>
+      </c>
+      <c r="I230" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>17</v>
+      </c>
+      <c r="B231" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C231">
+        <v>3187.5</v>
+      </c>
+      <c r="D231">
+        <v>199.16000003299999</v>
+      </c>
+      <c r="E231">
+        <v>3.76</v>
+      </c>
+      <c r="F231">
+        <v>59.84</v>
+      </c>
+      <c r="G231">
+        <v>59.84</v>
+      </c>
+      <c r="H231" t="s">
+        <v>9</v>
+      </c>
+      <c r="I231" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>17</v>
+      </c>
+      <c r="B232" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C232">
+        <v>3250</v>
+      </c>
+      <c r="D232">
+        <v>202.94000003299999</v>
+      </c>
+      <c r="E232">
+        <v>3.78</v>
+      </c>
+      <c r="F232">
+        <v>59.52</v>
+      </c>
+      <c r="G232">
+        <v>59.52</v>
+      </c>
+      <c r="H232" t="s">
+        <v>9</v>
+      </c>
+      <c r="I232" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>17</v>
+      </c>
+      <c r="B233" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C233">
+        <v>3312.5</v>
+      </c>
+      <c r="D233">
+        <v>206.840000033</v>
+      </c>
+      <c r="E233">
+        <v>3.9</v>
+      </c>
+      <c r="F233">
+        <v>59.52</v>
+      </c>
+      <c r="G233">
+        <v>57.69</v>
+      </c>
+      <c r="H233" t="s">
+        <v>10</v>
+      </c>
+      <c r="I233" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>17</v>
+      </c>
+      <c r="B234" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C234">
+        <v>3375</v>
+      </c>
+      <c r="D234">
+        <v>210.60000003299999</v>
+      </c>
+      <c r="E234">
+        <v>3.76</v>
+      </c>
+      <c r="F234">
+        <v>59.84</v>
+      </c>
+      <c r="G234">
+        <v>59.84</v>
+      </c>
+      <c r="H234" t="s">
+        <v>9</v>
+      </c>
+      <c r="I234" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>17</v>
+      </c>
+      <c r="B235" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C235">
+        <v>3437.5</v>
+      </c>
+      <c r="D235">
+        <v>214.32000003300001</v>
+      </c>
+      <c r="E235">
+        <v>3.72</v>
+      </c>
+      <c r="F235">
+        <v>60.48</v>
+      </c>
+      <c r="G235">
+        <v>60.48</v>
+      </c>
+      <c r="H235" t="s">
+        <v>9</v>
+      </c>
+      <c r="I235" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>17</v>
+      </c>
+      <c r="B236" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C236">
+        <v>3500</v>
+      </c>
+      <c r="D236">
+        <v>218.10000003299999</v>
+      </c>
+      <c r="E236">
+        <v>3.78</v>
+      </c>
+      <c r="F236">
+        <v>59.52</v>
+      </c>
+      <c r="G236">
+        <v>59.52</v>
+      </c>
+      <c r="H236" t="s">
+        <v>9</v>
+      </c>
+      <c r="I236" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>17</v>
+      </c>
+      <c r="B237" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C237">
+        <v>3562.5</v>
+      </c>
+      <c r="D237">
+        <v>221.88000003299999</v>
+      </c>
+      <c r="E237">
+        <v>3.78</v>
+      </c>
+      <c r="F237">
+        <v>59.52</v>
+      </c>
+      <c r="G237">
+        <v>59.52</v>
+      </c>
+      <c r="H237" t="s">
+        <v>9</v>
+      </c>
+      <c r="I237" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>17</v>
+      </c>
+      <c r="B238" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C238">
+        <v>3625</v>
+      </c>
+      <c r="D238">
+        <v>225.620000033</v>
+      </c>
+      <c r="E238">
+        <v>3.74</v>
+      </c>
+      <c r="F238">
+        <v>60.16</v>
+      </c>
+      <c r="G238">
+        <v>60.16</v>
+      </c>
+      <c r="H238" t="s">
+        <v>9</v>
+      </c>
+      <c r="I238" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>17</v>
+      </c>
+      <c r="B239" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C239">
+        <v>3687.5</v>
+      </c>
+      <c r="D239">
+        <v>229.340000033</v>
+      </c>
+      <c r="E239">
+        <v>3.72</v>
+      </c>
+      <c r="F239">
+        <v>60.48</v>
+      </c>
+      <c r="G239">
+        <v>60.48</v>
+      </c>
+      <c r="H239" t="s">
+        <v>9</v>
+      </c>
+      <c r="I239" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>17</v>
+      </c>
+      <c r="B240" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C240">
+        <v>3750</v>
+      </c>
+      <c r="D240">
+        <v>233.080000033</v>
+      </c>
+      <c r="E240">
+        <v>3.74</v>
+      </c>
+      <c r="F240">
+        <v>60.16</v>
+      </c>
+      <c r="G240">
+        <v>60.16</v>
+      </c>
+      <c r="H240" t="s">
+        <v>9</v>
+      </c>
+      <c r="I240" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>17</v>
+      </c>
+      <c r="B241" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C241">
+        <v>3812.5</v>
+      </c>
+      <c r="D241">
+        <v>236.82000003300001</v>
+      </c>
+      <c r="E241">
+        <v>3.74</v>
+      </c>
+      <c r="F241">
+        <v>60.16</v>
+      </c>
+      <c r="G241">
+        <v>60.16</v>
+      </c>
+      <c r="H241" t="s">
+        <v>9</v>
+      </c>
+      <c r="I241" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>17</v>
+      </c>
+      <c r="B242" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C242">
+        <v>3875</v>
+      </c>
+      <c r="D242">
+        <v>240.580000033</v>
+      </c>
+      <c r="E242">
+        <v>3.76</v>
+      </c>
+      <c r="F242">
+        <v>59.84</v>
+      </c>
+      <c r="G242">
+        <v>59.84</v>
+      </c>
+      <c r="H242" t="s">
+        <v>9</v>
+      </c>
+      <c r="I242" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>17</v>
+      </c>
+      <c r="B243" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C243">
+        <v>3937.5</v>
+      </c>
+      <c r="D243">
+        <v>244.38000003299999</v>
+      </c>
+      <c r="E243">
+        <v>3.8</v>
+      </c>
+      <c r="F243">
+        <v>59.21</v>
+      </c>
+      <c r="G243">
+        <v>59.21</v>
+      </c>
+      <c r="H243" t="s">
+        <v>9</v>
+      </c>
+      <c r="I243" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>17</v>
+      </c>
+      <c r="B244" s="2">
+        <v>45069</v>
+      </c>
+      <c r="C244">
+        <v>4000</v>
+      </c>
+      <c r="D244">
+        <v>248.400000033</v>
+      </c>
+      <c r="E244">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F244">
+        <v>55.97</v>
+      </c>
+      <c r="G244">
+        <v>55.97</v>
+      </c>
+      <c r="H244" t="s">
+        <v>14</v>
+      </c>
+      <c r="I244" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B245" s="2"/>
     </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B246" s="2"/>
     </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B247" s="2"/>
     </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B248" s="2"/>
     </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B249" s="2"/>
     </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B250" s="2"/>
     </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B251" s="2"/>
     </row>
-    <row r="252" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B252" s="2"/>
     </row>
-    <row r="253" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B253" s="2"/>
     </row>
-    <row r="254" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B254" s="2"/>
     </row>
-    <row r="255" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B255" s="2"/>
     </row>
-    <row r="256" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B256" s="2"/>
     </row>
     <row r="257" spans="2:2" x14ac:dyDescent="0.3">

--- a/pages/TP_Master.xlsx
+++ b/pages/TP_Master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867BE1A3-2DAF-4EED-A941-B95B64BE6D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA9002C-8685-4277-8E57-B96CAC51E0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,24 +49,6 @@
     <t>Front</t>
   </si>
   <si>
-    <t>2023 Jakarta NC WTP Qual</t>
-  </si>
-  <si>
-    <t>2023 Jakarta NC WTP Round 1</t>
-  </si>
-  <si>
-    <t>2023 Jakarta NC WTP Final</t>
-  </si>
-  <si>
-    <t>2023 Cairo NC WTP Qual</t>
-  </si>
-  <si>
-    <t>2023 Cairo NC WTP Round 1</t>
-  </si>
-  <si>
-    <t>2023 Cairo NC WTP Final</t>
-  </si>
-  <si>
     <t>No Change</t>
   </si>
   <si>
@@ -96,6 +78,24 @@
   <si>
     <t>Jessie Hodges</t>
   </si>
+  <si>
+    <t>2023 Jakarta NC NZL WTP Qual</t>
+  </si>
+  <si>
+    <t>2023 Jakarta NC NZL WTP R1</t>
+  </si>
+  <si>
+    <t>2023 Jakarta NC NZL WTP Final</t>
+  </si>
+  <si>
+    <t>2023 Cairo NC NZL WTP Qual</t>
+  </si>
+  <si>
+    <t>2023 Cairo NC NZL WTP R1</t>
+  </si>
+  <si>
+    <t>2023 Cairo NC NZL WTP Final</t>
+  </si>
 </sst>
 </file>
 
@@ -104,7 +104,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +116,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -545,7 +551,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>45069</v>
@@ -566,15 +572,15 @@
         <v>24.82</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2">
         <v>45069</v>
@@ -595,15 +601,15 @@
         <v>46.55</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2">
         <v>45069</v>
@@ -624,15 +630,15 @@
         <v>53.15</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2">
         <v>45069</v>
@@ -653,15 +659,15 @@
         <v>55.91</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2">
         <v>45069</v>
@@ -682,15 +688,15 @@
         <v>57.54</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2">
         <v>45069</v>
@@ -711,15 +717,15 @@
         <v>58.7</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2">
         <v>45069</v>
@@ -740,15 +746,15 @@
         <v>59.21</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2">
         <v>45069</v>
@@ -769,15 +775,15 @@
         <v>59.4</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2">
         <v>45069</v>
@@ -798,15 +804,15 @@
         <v>57.03</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2">
         <v>45069</v>
@@ -827,15 +833,15 @@
         <v>60.27</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2">
         <v>45069</v>
@@ -856,15 +862,15 @@
         <v>59.21</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2">
         <v>45069</v>
@@ -885,15 +891,15 @@
         <v>60.31</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2">
         <v>45069</v>
@@ -914,15 +920,15 @@
         <v>59.7</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2">
         <v>45069</v>
@@ -943,15 +949,15 @@
         <v>59.73</v>
       </c>
       <c r="H15" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2">
         <v>45069</v>
@@ -972,15 +978,15 @@
         <v>58.18</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
         <v>45069</v>
@@ -1001,15 +1007,15 @@
         <v>59.73</v>
       </c>
       <c r="H17" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" t="s">
         <v>15</v>
-      </c>
-      <c r="I17" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2">
         <v>45069</v>
@@ -1030,15 +1036,15 @@
         <v>60.81</v>
       </c>
       <c r="H18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" t="s">
         <v>15</v>
-      </c>
-      <c r="I18" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2">
         <v>45069</v>
@@ -1059,15 +1065,15 @@
         <v>60.27</v>
       </c>
       <c r="H19" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" t="s">
         <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2">
         <v>45069</v>
@@ -1088,15 +1094,15 @@
         <v>59.73</v>
       </c>
       <c r="H20" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" t="s">
         <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2">
         <v>45069</v>
@@ -1117,15 +1123,15 @@
         <v>60.27</v>
       </c>
       <c r="H21" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21" t="s">
         <v>15</v>
-      </c>
-      <c r="I21" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2">
         <v>45069</v>
@@ -1146,15 +1152,15 @@
         <v>59.73</v>
       </c>
       <c r="H22" t="s">
+        <v>9</v>
+      </c>
+      <c r="I22" t="s">
         <v>15</v>
-      </c>
-      <c r="I22" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2">
         <v>45069</v>
@@ -1175,15 +1181,15 @@
         <v>59.73</v>
       </c>
       <c r="H23" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" t="s">
         <v>15</v>
-      </c>
-      <c r="I23" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B24" s="2">
         <v>45069</v>
@@ -1204,15 +1210,15 @@
         <v>59.73</v>
       </c>
       <c r="H24" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" t="s">
         <v>15</v>
-      </c>
-      <c r="I24" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B25" s="2">
         <v>45069</v>
@@ -1233,15 +1239,15 @@
         <v>59.73</v>
       </c>
       <c r="H25" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" t="s">
         <v>15</v>
-      </c>
-      <c r="I25" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B26" s="2">
         <v>45069</v>
@@ -1262,15 +1268,15 @@
         <v>57.69</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I26" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B27" s="2">
         <v>45069</v>
@@ -1291,15 +1297,15 @@
         <v>59.73</v>
       </c>
       <c r="H27" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I27" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B28" s="2">
         <v>45069</v>
@@ -1320,15 +1326,15 @@
         <v>59.73</v>
       </c>
       <c r="H28" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I28" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B29" s="2">
         <v>45069</v>
@@ -1349,15 +1355,15 @@
         <v>59.21</v>
       </c>
       <c r="H29" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I29" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B30" s="2">
         <v>45069</v>
@@ -1378,15 +1384,15 @@
         <v>59.73</v>
       </c>
       <c r="H30" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I30" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B31" s="2">
         <v>45069</v>
@@ -1407,15 +1413,15 @@
         <v>59.73</v>
       </c>
       <c r="H31" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B32" s="2">
         <v>45069</v>
@@ -1436,15 +1442,15 @@
         <v>59.21</v>
       </c>
       <c r="H32" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I32" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B33" s="2">
         <v>45069</v>
@@ -1465,15 +1471,15 @@
         <v>58.7</v>
       </c>
       <c r="H33" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I33" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B34" s="2">
         <v>45069</v>
@@ -1494,15 +1500,15 @@
         <v>58.7</v>
       </c>
       <c r="H34" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I34" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B35" s="2">
         <v>45069</v>
@@ -1523,15 +1529,15 @@
         <v>59.21</v>
       </c>
       <c r="H35" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I35" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B36" s="2">
         <v>45069</v>
@@ -1552,15 +1558,15 @@
         <v>57.69</v>
       </c>
       <c r="H36" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I36" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B37" s="2">
         <v>45069</v>
@@ -1581,15 +1587,15 @@
         <v>58.18</v>
       </c>
       <c r="H37" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I37" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B38" s="2">
         <v>45069</v>
@@ -1610,15 +1616,15 @@
         <v>57.21</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B39" s="2">
         <v>45069</v>
@@ -1639,15 +1645,15 @@
         <v>58.7</v>
       </c>
       <c r="H39" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B40" s="2">
         <v>45069</v>
@@ -1668,15 +1674,15 @@
         <v>59.21</v>
       </c>
       <c r="H40" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B41" s="2">
         <v>45069</v>
@@ -1697,15 +1703,15 @@
         <v>58.7</v>
       </c>
       <c r="H41" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B42" s="2">
         <v>45069</v>
@@ -1726,15 +1732,15 @@
         <v>59.76</v>
       </c>
       <c r="H42" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B43" s="2">
         <v>45069</v>
@@ -1755,15 +1761,15 @@
         <v>59.7</v>
       </c>
       <c r="H43" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B44" s="2">
         <v>45069</v>
@@ -1784,15 +1790,15 @@
         <v>57.69</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B45" s="2">
         <v>45069</v>
@@ -1813,15 +1819,15 @@
         <v>59.73</v>
       </c>
       <c r="H45" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I45" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B46" s="2">
         <v>45069</v>
@@ -1842,15 +1848,15 @@
         <v>58.7</v>
       </c>
       <c r="H46" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B47" s="2">
         <v>45069</v>
@@ -1871,15 +1877,15 @@
         <v>60.81</v>
       </c>
       <c r="H47" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I47" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B48" s="2">
         <v>45069</v>
@@ -1900,15 +1906,15 @@
         <v>59.21</v>
       </c>
       <c r="H48" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I48" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B49" s="2">
         <v>45069</v>
@@ -1929,15 +1935,15 @@
         <v>60.27</v>
       </c>
       <c r="H49" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I49" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B50" s="2">
         <v>45069</v>
@@ -1958,15 +1964,15 @@
         <v>58.18</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I50" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B51" s="2">
         <v>45069</v>
@@ -1987,15 +1993,15 @@
         <v>60.27</v>
       </c>
       <c r="H51" t="s">
+        <v>9</v>
+      </c>
+      <c r="I51" t="s">
         <v>15</v>
-      </c>
-      <c r="I51" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B52" s="2">
         <v>45069</v>
@@ -2016,15 +2022,15 @@
         <v>59.21</v>
       </c>
       <c r="H52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I52" t="s">
         <v>15</v>
-      </c>
-      <c r="I52" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B53" s="2">
         <v>45069</v>
@@ -2045,15 +2051,15 @@
         <v>59.21</v>
       </c>
       <c r="H53" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" t="s">
         <v>15</v>
-      </c>
-      <c r="I53" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B54" s="2">
         <v>45069</v>
@@ -2074,15 +2080,15 @@
         <v>59.21</v>
       </c>
       <c r="H54" t="s">
+        <v>9</v>
+      </c>
+      <c r="I54" t="s">
         <v>15</v>
-      </c>
-      <c r="I54" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B55" s="2">
         <v>45069</v>
@@ -2103,15 +2109,15 @@
         <v>59.21</v>
       </c>
       <c r="H55" t="s">
+        <v>9</v>
+      </c>
+      <c r="I55" t="s">
         <v>15</v>
-      </c>
-      <c r="I55" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B56" s="2">
         <v>45069</v>
@@ -2132,15 +2138,15 @@
         <v>59.21</v>
       </c>
       <c r="H56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I56" t="s">
         <v>15</v>
-      </c>
-      <c r="I56" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B57" s="2">
         <v>45069</v>
@@ -2161,15 +2167,15 @@
         <v>59.21</v>
       </c>
       <c r="H57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I57" t="s">
         <v>15</v>
-      </c>
-      <c r="I57" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B58" s="2">
         <v>45069</v>
@@ -2190,15 +2196,15 @@
         <v>58.7</v>
       </c>
       <c r="H58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" t="s">
         <v>15</v>
-      </c>
-      <c r="I58" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B59" s="2">
         <v>45069</v>
@@ -2219,15 +2225,15 @@
         <v>59.21</v>
       </c>
       <c r="H59" t="s">
+        <v>9</v>
+      </c>
+      <c r="I59" t="s">
         <v>15</v>
-      </c>
-      <c r="I59" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B60" s="2">
         <v>45069</v>
@@ -2248,15 +2254,15 @@
         <v>56.25</v>
       </c>
       <c r="H60" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I60" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B61" s="2">
         <v>45069</v>
@@ -2277,15 +2283,15 @@
         <v>59.21</v>
       </c>
       <c r="H61" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I61" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B62" s="2">
         <v>45069</v>
@@ -2306,15 +2312,15 @@
         <v>59.73</v>
       </c>
       <c r="H62" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I62" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B63" s="2">
         <v>45069</v>
@@ -2335,15 +2341,15 @@
         <v>60.81</v>
       </c>
       <c r="H63" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I63" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B64" s="2">
         <v>45069</v>
@@ -2364,15 +2370,15 @@
         <v>60.27</v>
       </c>
       <c r="H64" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I64" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B65" s="2">
         <v>45069</v>
@@ -2393,15 +2399,15 @@
         <v>49.27</v>
       </c>
       <c r="H65" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I65" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B66" s="2">
         <v>45075</v>
@@ -2422,15 +2428,15 @@
         <v>25.09</v>
       </c>
       <c r="H66" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B67" s="2">
         <v>45075</v>
@@ -2451,15 +2457,15 @@
         <v>46.88</v>
       </c>
       <c r="H67" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B68" s="2">
         <v>45075</v>
@@ -2480,15 +2486,15 @@
         <v>53.57</v>
       </c>
       <c r="H68" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B69" s="2">
         <v>45075</v>
@@ -2509,15 +2515,15 @@
         <v>56.25</v>
       </c>
       <c r="H69" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B70" s="2">
         <v>45075</v>
@@ -2538,15 +2544,15 @@
         <v>58.7</v>
       </c>
       <c r="H70" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B71" s="2">
         <v>45075</v>
@@ -2567,15 +2573,15 @@
         <v>59.21</v>
       </c>
       <c r="H71" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B72" s="2">
         <v>45075</v>
@@ -2596,15 +2602,15 @@
         <v>59.73</v>
       </c>
       <c r="H72" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B73" s="2">
         <v>45075</v>
@@ -2625,15 +2631,15 @@
         <v>59.73</v>
       </c>
       <c r="H73" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B74" s="2">
         <v>45075</v>
@@ -2654,15 +2660,15 @@
         <v>58.18</v>
       </c>
       <c r="H74" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B75" s="2">
         <v>45075</v>
@@ -2683,15 +2689,15 @@
         <v>61.36</v>
       </c>
       <c r="H75" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I75" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B76" s="2">
         <v>45075</v>
@@ -2712,15 +2718,15 @@
         <v>60.27</v>
       </c>
       <c r="H76" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I76" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B77" s="2">
         <v>45075</v>
@@ -2741,15 +2747,15 @@
         <v>60.81</v>
       </c>
       <c r="H77" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I77" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B78" s="2">
         <v>45075</v>
@@ -2770,15 +2776,15 @@
         <v>60.27</v>
       </c>
       <c r="H78" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I78" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B79" s="2">
         <v>45075</v>
@@ -2799,15 +2805,15 @@
         <v>60.81</v>
       </c>
       <c r="H79" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I79" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B80" s="2">
         <v>45075</v>
@@ -2828,15 +2834,15 @@
         <v>58.18</v>
       </c>
       <c r="H80" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I80" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B81" s="2">
         <v>45075</v>
@@ -2857,15 +2863,15 @@
         <v>60.27</v>
       </c>
       <c r="H81" t="s">
+        <v>9</v>
+      </c>
+      <c r="I81" t="s">
         <v>15</v>
-      </c>
-      <c r="I81" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B82" s="2">
         <v>45075</v>
@@ -2886,15 +2892,15 @@
         <v>60.27</v>
       </c>
       <c r="H82" t="s">
+        <v>9</v>
+      </c>
+      <c r="I82" t="s">
         <v>15</v>
-      </c>
-      <c r="I82" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B83" s="2">
         <v>45075</v>
@@ -2915,15 +2921,15 @@
         <v>60.81</v>
       </c>
       <c r="H83" t="s">
+        <v>9</v>
+      </c>
+      <c r="I83" t="s">
         <v>15</v>
-      </c>
-      <c r="I83" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B84" s="2">
         <v>45075</v>
@@ -2944,15 +2950,15 @@
         <v>60.27</v>
       </c>
       <c r="H84" t="s">
+        <v>9</v>
+      </c>
+      <c r="I84" t="s">
         <v>15</v>
-      </c>
-      <c r="I84" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B85" s="2">
         <v>45075</v>
@@ -2973,15 +2979,15 @@
         <v>60.27</v>
       </c>
       <c r="H85" t="s">
+        <v>9</v>
+      </c>
+      <c r="I85" t="s">
         <v>15</v>
-      </c>
-      <c r="I85" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B86" s="2">
         <v>45075</v>
@@ -3002,15 +3008,15 @@
         <v>60.27</v>
       </c>
       <c r="H86" t="s">
+        <v>9</v>
+      </c>
+      <c r="I86" t="s">
         <v>15</v>
-      </c>
-      <c r="I86" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B87" s="2">
         <v>45075</v>
@@ -3031,15 +3037,15 @@
         <v>60.81</v>
       </c>
       <c r="H87" t="s">
+        <v>9</v>
+      </c>
+      <c r="I87" t="s">
         <v>15</v>
-      </c>
-      <c r="I87" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B88" s="2">
         <v>45075</v>
@@ -3060,15 +3066,15 @@
         <v>60.27</v>
       </c>
       <c r="H88" t="s">
+        <v>9</v>
+      </c>
+      <c r="I88" t="s">
         <v>15</v>
-      </c>
-      <c r="I88" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B89" s="2">
         <v>45075</v>
@@ -3089,15 +3095,15 @@
         <v>59.86</v>
       </c>
       <c r="H89" t="s">
+        <v>9</v>
+      </c>
+      <c r="I89" t="s">
         <v>15</v>
-      </c>
-      <c r="I89" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B90" s="2">
         <v>45075</v>
@@ -3118,15 +3124,15 @@
         <v>57.57</v>
       </c>
       <c r="H90" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I90" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B91" s="2">
         <v>45075</v>
@@ -3147,15 +3153,15 @@
         <v>60.81</v>
       </c>
       <c r="H91" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I91" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B92" s="2">
         <v>45075</v>
@@ -3176,15 +3182,15 @@
         <v>59.73</v>
       </c>
       <c r="H92" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I92" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B93" s="2">
         <v>45075</v>
@@ -3205,15 +3211,15 @@
         <v>59.73</v>
       </c>
       <c r="H93" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I93" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B94" s="2">
         <v>45075</v>
@@ -3234,15 +3240,15 @@
         <v>59.73</v>
       </c>
       <c r="H94" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I94" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B95" s="2">
         <v>45075</v>
@@ -3263,15 +3269,15 @@
         <v>60.27</v>
       </c>
       <c r="H95" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I95" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B96" s="2">
         <v>45075</v>
@@ -3292,15 +3298,15 @@
         <v>59.73</v>
       </c>
       <c r="H96" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I96" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B97" s="2">
         <v>45075</v>
@@ -3321,15 +3327,15 @@
         <v>59.21</v>
       </c>
       <c r="H97" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I97" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B98" s="2">
         <v>45075</v>
@@ -3350,15 +3356,15 @@
         <v>59.73</v>
       </c>
       <c r="H98" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I98" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B99" s="2">
         <v>45075</v>
@@ -3379,15 +3385,15 @@
         <v>60.27</v>
       </c>
       <c r="H99" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I99" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B100" s="2">
         <v>45075</v>
@@ -3408,15 +3414,15 @@
         <v>57.69</v>
       </c>
       <c r="H100" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I100" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B101" s="2">
         <v>45075</v>
@@ -3437,15 +3443,15 @@
         <v>60.27</v>
       </c>
       <c r="H101" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B102" s="2">
         <v>45075</v>
@@ -3466,15 +3472,15 @@
         <v>60.27</v>
       </c>
       <c r="H102" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B103" s="2">
         <v>45075</v>
@@ -3495,15 +3501,15 @@
         <v>60.27</v>
       </c>
       <c r="H103" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B104" s="2">
         <v>45075</v>
@@ -3524,15 +3530,15 @@
         <v>58.7</v>
       </c>
       <c r="H104" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B105" s="2">
         <v>45075</v>
@@ -3553,15 +3559,15 @@
         <v>59.73</v>
       </c>
       <c r="H105" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I105" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B106" s="2">
         <v>45075</v>
@@ -3582,15 +3588,15 @@
         <v>60.32</v>
       </c>
       <c r="H106" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I106" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B107" s="2">
         <v>45075</v>
@@ -3611,15 +3617,15 @@
         <v>59.68</v>
       </c>
       <c r="H107" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I107" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B108" s="2">
         <v>45075</v>
@@ -3640,15 +3646,15 @@
         <v>59.21</v>
       </c>
       <c r="H108" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I108" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B109" s="2">
         <v>45075</v>
@@ -3669,15 +3675,15 @@
         <v>59.21</v>
       </c>
       <c r="H109" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I109" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B110" s="2">
         <v>45075</v>
@@ -3698,15 +3704,15 @@
         <v>57.69</v>
       </c>
       <c r="H110" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I110" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B111" s="2">
         <v>45075</v>
@@ -3727,15 +3733,15 @@
         <v>59.73</v>
       </c>
       <c r="H111" t="s">
+        <v>9</v>
+      </c>
+      <c r="I111" t="s">
         <v>15</v>
-      </c>
-      <c r="I111" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B112" s="2">
         <v>45075</v>
@@ -3756,15 +3762,15 @@
         <v>59.21</v>
       </c>
       <c r="H112" t="s">
+        <v>9</v>
+      </c>
+      <c r="I112" t="s">
         <v>15</v>
-      </c>
-      <c r="I112" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B113" s="2">
         <v>45075</v>
@@ -3785,15 +3791,15 @@
         <v>59.73</v>
       </c>
       <c r="H113" t="s">
+        <v>9</v>
+      </c>
+      <c r="I113" t="s">
         <v>15</v>
-      </c>
-      <c r="I113" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B114" s="2">
         <v>45075</v>
@@ -3814,15 +3820,15 @@
         <v>59.73</v>
       </c>
       <c r="H114" t="s">
+        <v>9</v>
+      </c>
+      <c r="I114" t="s">
         <v>15</v>
-      </c>
-      <c r="I114" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B115" s="2">
         <v>45075</v>
@@ -3843,15 +3849,15 @@
         <v>59.73</v>
       </c>
       <c r="H115" t="s">
+        <v>9</v>
+      </c>
+      <c r="I115" t="s">
         <v>15</v>
-      </c>
-      <c r="I115" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B116" s="2">
         <v>45075</v>
@@ -3872,15 +3878,15 @@
         <v>59.21</v>
       </c>
       <c r="H116" t="s">
+        <v>9</v>
+      </c>
+      <c r="I116" t="s">
         <v>15</v>
-      </c>
-      <c r="I116" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B117" s="2">
         <v>45075</v>
@@ -3901,15 +3907,15 @@
         <v>59.73</v>
       </c>
       <c r="H117" t="s">
+        <v>9</v>
+      </c>
+      <c r="I117" t="s">
         <v>15</v>
-      </c>
-      <c r="I117" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B118" s="2">
         <v>45075</v>
@@ -3930,15 +3936,15 @@
         <v>57.8</v>
       </c>
       <c r="H118" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I118" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B119" s="2">
         <v>45075</v>
@@ -3959,15 +3965,15 @@
         <v>59.1</v>
       </c>
       <c r="H119" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I119" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B120" s="2">
         <v>45075</v>
@@ -3988,15 +3994,15 @@
         <v>58.18</v>
       </c>
       <c r="H120" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I120" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B121" s="2">
         <v>45075</v>
@@ -4017,15 +4023,15 @@
         <v>57.21</v>
       </c>
       <c r="H121" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I121" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B122" s="2">
         <v>45075</v>
@@ -4046,15 +4052,15 @@
         <v>57.21</v>
       </c>
       <c r="H122" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I122" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B123" s="2">
         <v>45075</v>
@@ -4075,15 +4081,15 @@
         <v>57.21</v>
       </c>
       <c r="H123" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I123" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B124" s="2">
         <v>45075</v>
@@ -4104,15 +4110,15 @@
         <v>57.21</v>
       </c>
       <c r="H124" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I124" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B125" s="2">
         <v>45075</v>
@@ -4133,15 +4139,15 @@
         <v>56.25</v>
       </c>
       <c r="H125" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I125" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B126" s="2">
         <v>45075</v>
@@ -4162,15 +4168,15 @@
         <v>56.25</v>
       </c>
       <c r="H126" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I126" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B127" s="2">
         <v>45075</v>
@@ -4191,15 +4197,15 @@
         <v>55.79</v>
       </c>
       <c r="H127" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I127" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B128" s="2">
         <v>45075</v>
@@ -4220,15 +4226,15 @@
         <v>54.44</v>
       </c>
       <c r="H128" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I128" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B129" s="2">
         <v>45075</v>
@@ -4249,15 +4255,15 @@
         <v>51.52</v>
       </c>
       <c r="H129" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I129" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B130" s="2">
         <v>45069</v>
@@ -4278,15 +4284,15 @@
         <v>24.73</v>
       </c>
       <c r="H130" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I130" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B131" s="2">
         <v>45069</v>
@@ -4307,15 +4313,15 @@
         <v>46.3</v>
       </c>
       <c r="H131" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I131" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B132" s="2">
         <v>45069</v>
@@ -4336,15 +4342,15 @@
         <v>53.83</v>
       </c>
       <c r="H132" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I132" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B133" s="2">
         <v>45069</v>
@@ -4365,15 +4371,15 @@
         <v>55.97</v>
       </c>
       <c r="H133" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I133" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B134" s="2">
         <v>45069</v>
@@ -4394,15 +4400,15 @@
         <v>57.99</v>
       </c>
       <c r="H134" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I134" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B135" s="2">
         <v>45069</v>
@@ -4423,15 +4429,15 @@
         <v>59.21</v>
       </c>
       <c r="H135" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I135" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B136" s="2">
         <v>45069</v>
@@ -4452,15 +4458,15 @@
         <v>60.48</v>
       </c>
       <c r="H136" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I136" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B137" s="2">
         <v>45069</v>
@@ -4481,15 +4487,15 @@
         <v>59.84</v>
       </c>
       <c r="H137" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I137" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B138" s="2">
         <v>45069</v>
@@ -4510,15 +4516,15 @@
         <v>57.99</v>
       </c>
       <c r="H138" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I138" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B139" s="2">
         <v>45069</v>
@@ -4539,15 +4545,15 @@
         <v>60.48</v>
       </c>
       <c r="H139" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I139" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B140" s="2">
         <v>45069</v>
@@ -4568,15 +4574,15 @@
         <v>60.16</v>
       </c>
       <c r="H140" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I140" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B141" s="2">
         <v>45069</v>
@@ -4597,15 +4603,15 @@
         <v>60.48</v>
       </c>
       <c r="H141" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I141" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B142" s="2">
         <v>45069</v>
@@ -4626,15 +4632,15 @@
         <v>60.16</v>
       </c>
       <c r="H142" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I142" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B143" s="2">
         <v>45069</v>
@@ -4655,15 +4661,15 @@
         <v>60.48</v>
       </c>
       <c r="H143" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I143" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B144" s="2">
         <v>45069</v>
@@ -4684,15 +4690,15 @@
         <v>58.9</v>
       </c>
       <c r="H144" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I144" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B145" s="2">
         <v>45069</v>
@@ -4713,15 +4719,15 @@
         <v>60.48</v>
       </c>
       <c r="H145" t="s">
+        <v>9</v>
+      </c>
+      <c r="I145" t="s">
         <v>15</v>
-      </c>
-      <c r="I145" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B146" s="2">
         <v>45069</v>
@@ -4742,15 +4748,15 @@
         <v>60.48</v>
       </c>
       <c r="H146" t="s">
+        <v>9</v>
+      </c>
+      <c r="I146" t="s">
         <v>15</v>
-      </c>
-      <c r="I146" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B147" s="2">
         <v>45069</v>
@@ -4771,15 +4777,15 @@
         <v>60.48</v>
       </c>
       <c r="H147" t="s">
+        <v>9</v>
+      </c>
+      <c r="I147" t="s">
         <v>15</v>
-      </c>
-      <c r="I147" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B148" s="2">
         <v>45069</v>
@@ -4800,15 +4806,15 @@
         <v>61.14</v>
       </c>
       <c r="H148" t="s">
+        <v>9</v>
+      </c>
+      <c r="I148" t="s">
         <v>15</v>
-      </c>
-      <c r="I148" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B149" s="2">
         <v>45069</v>
@@ -4829,15 +4835,15 @@
         <v>60.48</v>
       </c>
       <c r="H149" t="s">
+        <v>9</v>
+      </c>
+      <c r="I149" t="s">
         <v>15</v>
-      </c>
-      <c r="I149" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B150" s="2">
         <v>45069</v>
@@ -4858,15 +4864,15 @@
         <v>60.16</v>
       </c>
       <c r="H150" t="s">
+        <v>9</v>
+      </c>
+      <c r="I150" t="s">
         <v>15</v>
-      </c>
-      <c r="I150" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B151" s="2">
         <v>45069</v>
@@ -4887,15 +4893,15 @@
         <v>60.48</v>
       </c>
       <c r="H151" t="s">
+        <v>9</v>
+      </c>
+      <c r="I151" t="s">
         <v>15</v>
-      </c>
-      <c r="I151" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B152" s="2">
         <v>45069</v>
@@ -4916,15 +4922,15 @@
         <v>60.48</v>
       </c>
       <c r="H152" t="s">
+        <v>9</v>
+      </c>
+      <c r="I152" t="s">
         <v>15</v>
-      </c>
-      <c r="I152" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B153" s="2">
         <v>45069</v>
@@ -4945,15 +4951,15 @@
         <v>60.16</v>
       </c>
       <c r="H153" t="s">
+        <v>9</v>
+      </c>
+      <c r="I153" t="s">
         <v>15</v>
-      </c>
-      <c r="I153" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B154" s="2">
         <v>45069</v>
@@ -4974,15 +4980,15 @@
         <v>57.69</v>
       </c>
       <c r="H154" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I154" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B155" s="2">
         <v>45069</v>
@@ -5003,15 +5009,15 @@
         <v>60.16</v>
       </c>
       <c r="H155" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I155" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B156" s="2">
         <v>45069</v>
@@ -5032,15 +5038,15 @@
         <v>60.81</v>
       </c>
       <c r="H156" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I156" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B157" s="2">
         <v>45069</v>
@@ -5061,15 +5067,15 @@
         <v>60.48</v>
       </c>
       <c r="H157" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I157" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B158" s="2">
         <v>45069</v>
@@ -5090,15 +5096,15 @@
         <v>59.84</v>
       </c>
       <c r="H158" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I158" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B159" s="2">
         <v>45069</v>
@@ -5119,15 +5125,15 @@
         <v>60.48</v>
       </c>
       <c r="H159" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I159" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B160" s="2">
         <v>45069</v>
@@ -5148,15 +5154,15 @@
         <v>60.81</v>
       </c>
       <c r="H160" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I160" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B161" s="2">
         <v>45069</v>
@@ -5177,15 +5183,15 @@
         <v>60.16</v>
       </c>
       <c r="H161" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I161" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B162" s="2">
         <v>45069</v>
@@ -5206,15 +5212,15 @@
         <v>57.99</v>
       </c>
       <c r="H162" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I162" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B163" s="2">
         <v>45069</v>
@@ -5235,15 +5241,15 @@
         <v>61.81</v>
       </c>
       <c r="H163" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I163" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B164" s="2">
         <v>45069</v>
@@ -5264,15 +5270,15 @@
         <v>60.16</v>
       </c>
       <c r="H164" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I164" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B165" s="2">
         <v>45069</v>
@@ -5293,15 +5299,15 @@
         <v>59.84</v>
       </c>
       <c r="H165" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I165" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B166" s="2">
         <v>45069</v>
@@ -5322,15 +5328,15 @@
         <v>57.4</v>
       </c>
       <c r="H166" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I166" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B167" s="2">
         <v>45069</v>
@@ -5351,15 +5357,15 @@
         <v>59.84</v>
       </c>
       <c r="H167" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I167" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B168" s="2">
         <v>45069</v>
@@ -5380,15 +5386,15 @@
         <v>60.16</v>
       </c>
       <c r="H168" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I168" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B169" s="2">
         <v>45069</v>
@@ -5409,15 +5415,15 @@
         <v>59.21</v>
       </c>
       <c r="H169" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I169" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B170" s="2">
         <v>45069</v>
@@ -5438,15 +5444,15 @@
         <v>59.56</v>
       </c>
       <c r="H170" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I170" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B171" s="2">
         <v>45069</v>
@@ -5467,15 +5473,15 @@
         <v>59.49</v>
       </c>
       <c r="H171" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I171" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B172" s="2">
         <v>45069</v>
@@ -5496,15 +5502,15 @@
         <v>57.69</v>
       </c>
       <c r="H172" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I172" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B173" s="2">
         <v>45069</v>
@@ -5525,15 +5531,15 @@
         <v>59.52</v>
       </c>
       <c r="H173" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I173" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B174" s="2">
         <v>45069</v>
@@ -5554,15 +5560,15 @@
         <v>58.9</v>
       </c>
       <c r="H174" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I174" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B175" s="2">
         <v>45069</v>
@@ -5583,15 +5589,15 @@
         <v>59.52</v>
       </c>
       <c r="H175" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I175" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B176" s="2">
         <v>45069</v>
@@ -5612,15 +5618,15 @@
         <v>57.99</v>
       </c>
       <c r="H176" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I176" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B177" s="2">
         <v>45069</v>
@@ -5641,15 +5647,15 @@
         <v>59.52</v>
       </c>
       <c r="H177" t="s">
+        <v>9</v>
+      </c>
+      <c r="I177" t="s">
         <v>15</v>
-      </c>
-      <c r="I177" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B178" s="2">
         <v>45069</v>
@@ -5670,15 +5676,15 @@
         <v>59.52</v>
       </c>
       <c r="H178" t="s">
+        <v>9</v>
+      </c>
+      <c r="I178" t="s">
         <v>15</v>
-      </c>
-      <c r="I178" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B179" s="2">
         <v>45069</v>
@@ -5699,15 +5705,15 @@
         <v>59.84</v>
       </c>
       <c r="H179" t="s">
+        <v>9</v>
+      </c>
+      <c r="I179" t="s">
         <v>15</v>
-      </c>
-      <c r="I179" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B180" s="2">
         <v>45069</v>
@@ -5728,15 +5734,15 @@
         <v>59.84</v>
       </c>
       <c r="H180" t="s">
+        <v>9</v>
+      </c>
+      <c r="I180" t="s">
         <v>15</v>
-      </c>
-      <c r="I180" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B181" s="2">
         <v>45069</v>
@@ -5757,15 +5763,15 @@
         <v>59.52</v>
       </c>
       <c r="H181" t="s">
+        <v>9</v>
+      </c>
+      <c r="I181" t="s">
         <v>15</v>
-      </c>
-      <c r="I181" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B182" s="2">
         <v>45069</v>
@@ -5786,15 +5792,15 @@
         <v>57.69</v>
       </c>
       <c r="H182" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I182" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B183" s="2">
         <v>45069</v>
@@ -5815,15 +5821,15 @@
         <v>59.84</v>
       </c>
       <c r="H183" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I183" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B184" s="2">
         <v>45069</v>
@@ -5844,15 +5850,15 @@
         <v>60.48</v>
       </c>
       <c r="H184" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I184" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B185" s="2">
         <v>45069</v>
@@ -5873,15 +5879,15 @@
         <v>59.52</v>
       </c>
       <c r="H185" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I185" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B186" s="2">
         <v>45069</v>
@@ -5902,15 +5908,15 @@
         <v>59.52</v>
       </c>
       <c r="H186" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I186" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B187" s="2">
         <v>45069</v>
@@ -5931,15 +5937,15 @@
         <v>60.16</v>
       </c>
       <c r="H187" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I187" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B188" s="2">
         <v>45069</v>
@@ -5960,15 +5966,15 @@
         <v>60.48</v>
       </c>
       <c r="H188" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I188" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B189" s="2">
         <v>45069</v>
@@ -5989,15 +5995,15 @@
         <v>60.16</v>
       </c>
       <c r="H189" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I189" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B190" s="2">
         <v>45069</v>
@@ -6018,15 +6024,15 @@
         <v>60.16</v>
       </c>
       <c r="H190" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I190" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B191" s="2">
         <v>45069</v>
@@ -6047,15 +6053,15 @@
         <v>59.84</v>
       </c>
       <c r="H191" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I191" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B192" s="2">
         <v>45069</v>
@@ -6076,15 +6082,15 @@
         <v>59.21</v>
       </c>
       <c r="H192" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I192" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B193" s="2">
         <v>45069</v>
@@ -6105,15 +6111,15 @@
         <v>55.97</v>
       </c>
       <c r="H193" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I193" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B194" s="2">
         <v>45075</v>
@@ -6134,15 +6140,15 @@
         <v>24.89</v>
       </c>
       <c r="H194" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I194" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B195" s="2">
         <v>45075</v>
@@ -6163,15 +6169,15 @@
         <v>45.92</v>
       </c>
       <c r="H195" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I195" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B196" s="2">
         <v>45075</v>
@@ -6192,15 +6198,15 @@
         <v>50.9</v>
       </c>
       <c r="H196" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I196" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B197" s="2">
         <v>45075</v>
@@ -6221,15 +6227,15 @@
         <v>53.07</v>
       </c>
       <c r="H197" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I197" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B198" s="2">
         <v>45075</v>
@@ -6250,15 +6256,15 @@
         <v>56.82</v>
       </c>
       <c r="H198" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I198" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B199" s="2">
         <v>45075</v>
@@ -6279,15 +6285,15 @@
         <v>58.29</v>
       </c>
       <c r="H199" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I199" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B200" s="2">
         <v>45075</v>
@@ -6308,15 +6314,15 @@
         <v>58.29</v>
       </c>
       <c r="H200" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I200" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B201" s="2">
         <v>45075</v>
@@ -6337,15 +6343,15 @@
         <v>57.69</v>
       </c>
       <c r="H201" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I201" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B202" s="2">
         <v>45075</v>
@@ -6366,15 +6372,15 @@
         <v>56.82</v>
       </c>
       <c r="H202" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I202" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B203" s="2">
         <v>45075</v>
@@ -6395,15 +6401,15 @@
         <v>60.48</v>
       </c>
       <c r="H203" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I203" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B204" s="2">
         <v>45075</v>
@@ -6424,15 +6430,15 @@
         <v>60.48</v>
       </c>
       <c r="H204" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I204" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B205" s="2">
         <v>45075</v>
@@ -6453,15 +6459,15 @@
         <v>59.52</v>
       </c>
       <c r="H205" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I205" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B206" s="2">
         <v>45075</v>
@@ -6482,15 +6488,15 @@
         <v>59.21</v>
       </c>
       <c r="H206" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I206" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B207" s="2">
         <v>45075</v>
@@ -6511,15 +6517,15 @@
         <v>59.84</v>
       </c>
       <c r="H207" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I207" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B208" s="2">
         <v>45075</v>
@@ -6540,15 +6546,15 @@
         <v>58.9</v>
       </c>
       <c r="H208" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I208" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B209" s="2">
         <v>45075</v>
@@ -6569,15 +6575,15 @@
         <v>57.99</v>
       </c>
       <c r="H209" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I209" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B210" s="2">
         <v>45075</v>
@@ -6598,15 +6604,15 @@
         <v>57.11</v>
       </c>
       <c r="H210" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I210" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B211" s="2">
         <v>45075</v>
@@ -6627,15 +6633,15 @@
         <v>60.16</v>
       </c>
       <c r="H211" t="s">
+        <v>9</v>
+      </c>
+      <c r="I211" t="s">
         <v>15</v>
-      </c>
-      <c r="I211" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B212" s="2">
         <v>45075</v>
@@ -6656,15 +6662,15 @@
         <v>59.21</v>
       </c>
       <c r="H212" t="s">
+        <v>9</v>
+      </c>
+      <c r="I212" t="s">
         <v>15</v>
-      </c>
-      <c r="I212" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B213" s="2">
         <v>45075</v>
@@ -6685,15 +6691,15 @@
         <v>58.9</v>
       </c>
       <c r="H213" t="s">
+        <v>9</v>
+      </c>
+      <c r="I213" t="s">
         <v>15</v>
-      </c>
-      <c r="I213" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B214" s="2">
         <v>45075</v>
@@ -6714,15 +6720,15 @@
         <v>59.21</v>
       </c>
       <c r="H214" t="s">
+        <v>9</v>
+      </c>
+      <c r="I214" t="s">
         <v>15</v>
-      </c>
-      <c r="I214" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B215" s="2">
         <v>45075</v>
@@ -6743,15 +6749,15 @@
         <v>59.52</v>
       </c>
       <c r="H215" t="s">
+        <v>9</v>
+      </c>
+      <c r="I215" t="s">
         <v>15</v>
-      </c>
-      <c r="I215" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B216" s="2">
         <v>45075</v>
@@ -6772,15 +6778,15 @@
         <v>58.59</v>
       </c>
       <c r="H216" t="s">
+        <v>9</v>
+      </c>
+      <c r="I216" t="s">
         <v>15</v>
-      </c>
-      <c r="I216" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B217" s="2">
         <v>45075</v>
@@ -6801,15 +6807,15 @@
         <v>57.99</v>
       </c>
       <c r="H217" t="s">
+        <v>9</v>
+      </c>
+      <c r="I217" t="s">
         <v>15</v>
-      </c>
-      <c r="I217" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B218" s="2">
         <v>45075</v>
@@ -6830,15 +6836,15 @@
         <v>58.59</v>
       </c>
       <c r="H218" t="s">
+        <v>9</v>
+      </c>
+      <c r="I218" t="s">
         <v>15</v>
-      </c>
-      <c r="I218" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B219" s="2">
         <v>45075</v>
@@ -6859,15 +6865,15 @@
         <v>59.21</v>
       </c>
       <c r="H219" t="s">
+        <v>9</v>
+      </c>
+      <c r="I219" t="s">
         <v>15</v>
-      </c>
-      <c r="I219" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B220" s="2">
         <v>45075</v>
@@ -6888,15 +6894,15 @@
         <v>56.25</v>
       </c>
       <c r="H220" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I220" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B221" s="2">
         <v>45075</v>
@@ -6917,15 +6923,15 @@
         <v>57.11</v>
       </c>
       <c r="H221" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I221" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B222" s="2">
         <v>45075</v>
@@ -6946,15 +6952,15 @@
         <v>58.59</v>
       </c>
       <c r="H222" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I222" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B223" s="2">
         <v>45075</v>
@@ -6975,15 +6981,15 @@
         <v>59.21</v>
       </c>
       <c r="H223" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I223" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B224" s="2">
         <v>45075</v>
@@ -7004,15 +7010,15 @@
         <v>58.59</v>
       </c>
       <c r="H224" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I224" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B225" s="2">
         <v>45075</v>
@@ -7033,15 +7039,15 @@
         <v>56.82</v>
       </c>
       <c r="H225" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I225" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B226" s="2">
         <v>45075</v>
@@ -7062,15 +7068,15 @@
         <v>57.4</v>
       </c>
       <c r="H226" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I226" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B227" s="2">
         <v>45075</v>
@@ -7091,15 +7097,15 @@
         <v>57.4</v>
       </c>
       <c r="H227" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I227" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B228" s="2">
         <v>45075</v>
@@ -7120,15 +7126,15 @@
         <v>54.61</v>
       </c>
       <c r="H228" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I228" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B229" s="2">
         <v>45075</v>
@@ -7149,15 +7155,15 @@
         <v>56.53</v>
       </c>
       <c r="H229" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I229" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B230" s="2">
         <v>45075</v>
@@ -7178,15 +7184,15 @@
         <v>58.29</v>
       </c>
       <c r="H230" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I230" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B231" s="2">
         <v>45075</v>
@@ -7207,15 +7213,15 @@
         <v>59.52</v>
       </c>
       <c r="H231" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I231" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B232" s="2">
         <v>45075</v>
@@ -7236,15 +7242,15 @@
         <v>57.11</v>
       </c>
       <c r="H232" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I232" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B233" s="2">
         <v>45075</v>
@@ -7265,15 +7271,15 @@
         <v>58.59</v>
       </c>
       <c r="H233" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I233" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B234" s="2">
         <v>45075</v>
@@ -7294,15 +7300,15 @@
         <v>59.52</v>
       </c>
       <c r="H234" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I234" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B235" s="2">
         <v>45075</v>
@@ -7323,15 +7329,15 @@
         <v>60.48</v>
       </c>
       <c r="H235" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I235" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B236" s="2">
         <v>45075</v>
@@ -7352,15 +7358,15 @@
         <v>58.9</v>
       </c>
       <c r="H236" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I236" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B237" s="2">
         <v>45075</v>
@@ -7381,15 +7387,15 @@
         <v>58.59</v>
       </c>
       <c r="H237" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I237" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B238" s="2">
         <v>45075</v>
@@ -7410,15 +7416,15 @@
         <v>59.21</v>
       </c>
       <c r="H238" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I238" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B239" s="2">
         <v>45075</v>
@@ -7439,15 +7445,15 @@
         <v>60.16</v>
       </c>
       <c r="H239" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I239" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B240" s="2">
         <v>45075</v>
@@ -7468,15 +7474,15 @@
         <v>59.84</v>
       </c>
       <c r="H240" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I240" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B241" s="2">
         <v>45075</v>
@@ -7497,15 +7503,15 @@
         <v>59.21</v>
       </c>
       <c r="H241" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I241" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B242" s="2">
         <v>45075</v>
@@ -7526,15 +7532,15 @@
         <v>59.84</v>
       </c>
       <c r="H242" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I242" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B243" s="2">
         <v>45075</v>
@@ -7555,15 +7561,15 @@
         <v>60.16</v>
       </c>
       <c r="H243" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I243" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B244" s="2">
         <v>45075</v>
@@ -7574,7 +7580,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B245" s="2">
         <v>45075</v>
@@ -7585,7 +7591,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B246" s="2">
         <v>45075</v>
@@ -7596,7 +7602,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B247" s="2">
         <v>45075</v>
@@ -7607,7 +7613,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B248" s="2">
         <v>45075</v>
@@ -7618,7 +7624,7 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B249" s="2">
         <v>45075</v>
@@ -7629,7 +7635,7 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B250" s="2">
         <v>45075</v>
@@ -7640,7 +7646,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B251" s="2">
         <v>45075</v>
@@ -7651,7 +7657,7 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B252" s="2">
         <v>45075</v>
@@ -7662,7 +7668,7 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B253" s="2">
         <v>45075</v>
@@ -7673,7 +7679,7 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B254" s="2">
         <v>45075</v>
@@ -7684,7 +7690,7 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B255" s="2">
         <v>45075</v>
@@ -7695,7 +7701,7 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B256" s="2">
         <v>45075</v>
@@ -7706,7 +7712,7 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B257" s="2">
         <v>45075</v>
@@ -7717,7 +7723,7 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B258" s="2">
         <v>45075</v>
@@ -7738,15 +7744,15 @@
         <v>24.3</v>
       </c>
       <c r="H258" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I258" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B259" s="2">
         <v>45075</v>
@@ -7767,15 +7773,15 @@
         <v>44.82</v>
       </c>
       <c r="H259" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I259" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B260" s="2">
         <v>45075</v>
@@ -7796,15 +7802,15 @@
         <v>51.37</v>
       </c>
       <c r="H260" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I260" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B261" s="2">
         <v>45075</v>
@@ -7825,15 +7831,15 @@
         <v>54.09</v>
       </c>
       <c r="H261" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I261" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B262" s="2">
         <v>45075</v>
@@ -7854,15 +7860,15 @@
         <v>56.25</v>
       </c>
       <c r="H262" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I262" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B263" s="2">
         <v>45075</v>
@@ -7883,15 +7889,15 @@
         <v>57.4</v>
       </c>
       <c r="H263" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I263" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B264" s="2">
         <v>45075</v>
@@ -7912,15 +7918,15 @@
         <v>57.69</v>
       </c>
       <c r="H264" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I264" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B265" s="2">
         <v>45075</v>
@@ -7941,15 +7947,15 @@
         <v>57.99</v>
       </c>
       <c r="H265" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I265" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B266" s="2">
         <v>45075</v>
@@ -7970,15 +7976,15 @@
         <v>56.25</v>
       </c>
       <c r="H266" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I266" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B267" s="2">
         <v>45075</v>
@@ -7999,15 +8005,15 @@
         <v>58.29</v>
       </c>
       <c r="H267" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I267" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B268" s="2">
         <v>45075</v>
@@ -8028,15 +8034,15 @@
         <v>58.9</v>
       </c>
       <c r="H268" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I268" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B269" s="2">
         <v>45075</v>
@@ -8057,15 +8063,15 @@
         <v>58.59</v>
       </c>
       <c r="H269" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I269" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B270" s="2">
         <v>45075</v>
@@ -8086,15 +8092,15 @@
         <v>58.29</v>
       </c>
       <c r="H270" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I270" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B271" s="2">
         <v>45075</v>
@@ -8115,15 +8121,15 @@
         <v>58.29</v>
       </c>
       <c r="H271" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I271" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B272" s="2">
         <v>45075</v>
@@ -8144,15 +8150,15 @@
         <v>57.11</v>
       </c>
       <c r="H272" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I272" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B273" s="2">
         <v>45075</v>
@@ -8173,15 +8179,15 @@
         <v>57.11</v>
       </c>
       <c r="H273" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I273" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B274" s="2">
         <v>45075</v>
@@ -8202,15 +8208,15 @@
         <v>55.15</v>
       </c>
       <c r="H274" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I274" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B275" s="2">
         <v>45075</v>
@@ -8231,15 +8237,15 @@
         <v>57.4</v>
       </c>
       <c r="H275" t="s">
+        <v>9</v>
+      </c>
+      <c r="I275" t="s">
         <v>15</v>
-      </c>
-      <c r="I275" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B276" s="2">
         <v>45075</v>
@@ -8260,15 +8266,15 @@
         <v>57.69</v>
       </c>
       <c r="H276" t="s">
+        <v>9</v>
+      </c>
+      <c r="I276" t="s">
         <v>15</v>
-      </c>
-      <c r="I276" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B277" s="2">
         <v>45075</v>
@@ -8289,15 +8295,15 @@
         <v>57.4</v>
       </c>
       <c r="H277" t="s">
+        <v>9</v>
+      </c>
+      <c r="I277" t="s">
         <v>15</v>
-      </c>
-      <c r="I277" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B278" s="2">
         <v>45075</v>
@@ -8318,15 +8324,15 @@
         <v>57.99</v>
       </c>
       <c r="H278" t="s">
+        <v>9</v>
+      </c>
+      <c r="I278" t="s">
         <v>15</v>
-      </c>
-      <c r="I278" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B279" s="2">
         <v>45075</v>
@@ -8347,15 +8353,15 @@
         <v>58.29</v>
       </c>
       <c r="H279" t="s">
+        <v>9</v>
+      </c>
+      <c r="I279" t="s">
         <v>15</v>
-      </c>
-      <c r="I279" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B280" s="2">
         <v>45075</v>
@@ -8376,15 +8382,15 @@
         <v>58.29</v>
       </c>
       <c r="H280" t="s">
+        <v>9</v>
+      </c>
+      <c r="I280" t="s">
         <v>15</v>
-      </c>
-      <c r="I280" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B281" s="2">
         <v>45075</v>
@@ -8405,15 +8411,15 @@
         <v>58.59</v>
       </c>
       <c r="H281" t="s">
+        <v>9</v>
+      </c>
+      <c r="I281" t="s">
         <v>15</v>
-      </c>
-      <c r="I281" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B282" s="2">
         <v>45075</v>
@@ -8434,15 +8440,15 @@
         <v>58.29</v>
       </c>
       <c r="H282" t="s">
+        <v>9</v>
+      </c>
+      <c r="I282" t="s">
         <v>15</v>
-      </c>
-      <c r="I282" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B283" s="2">
         <v>45075</v>
@@ -8463,15 +8469,15 @@
         <v>58.29</v>
       </c>
       <c r="H283" t="s">
+        <v>9</v>
+      </c>
+      <c r="I283" t="s">
         <v>15</v>
-      </c>
-      <c r="I283" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B284" s="2">
         <v>45075</v>
@@ -8492,15 +8498,15 @@
         <v>55.97</v>
       </c>
       <c r="H284" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I284" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B285" s="2">
         <v>45075</v>
@@ -8521,15 +8527,15 @@
         <v>57.69</v>
       </c>
       <c r="H285" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I285" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B286" s="2">
         <v>45075</v>
@@ -8550,15 +8556,15 @@
         <v>57.4</v>
       </c>
       <c r="H286" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I286" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B287" s="2">
         <v>45075</v>
@@ -8579,15 +8585,15 @@
         <v>57.11</v>
       </c>
       <c r="H287" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I287" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B288" s="2">
         <v>45075</v>
@@ -8608,15 +8614,15 @@
         <v>56.82</v>
       </c>
       <c r="H288" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I288" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B289" s="2">
         <v>45075</v>
@@ -8637,15 +8643,15 @@
         <v>57.4</v>
       </c>
       <c r="H289" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I289" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B290" s="2">
         <v>45075</v>
@@ -8666,15 +8672,15 @@
         <v>55.42</v>
       </c>
       <c r="H290" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I290" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B291" s="2">
         <v>45075</v>
@@ -8695,15 +8701,15 @@
         <v>57.69</v>
       </c>
       <c r="H291" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I291" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B292" s="2">
         <v>45075</v>
@@ -8724,15 +8730,15 @@
         <v>58.29</v>
       </c>
       <c r="H292" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I292" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B293" s="2">
         <v>45075</v>
@@ -8753,15 +8759,15 @@
         <v>57.99</v>
       </c>
       <c r="H293" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I293" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B294" s="2">
         <v>45075</v>
@@ -8782,15 +8788,15 @@
         <v>56.25</v>
       </c>
       <c r="H294" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I294" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B295" s="2">
         <v>45075</v>
@@ -8811,15 +8817,15 @@
         <v>58.29</v>
       </c>
       <c r="H295" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I295" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B296" s="2">
         <v>45075</v>
@@ -8840,15 +8846,15 @@
         <v>58.29</v>
       </c>
       <c r="H296" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I296" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B297" s="2">
         <v>45075</v>
@@ -8869,15 +8875,15 @@
         <v>57.69</v>
       </c>
       <c r="H297" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I297" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B298" s="2">
         <v>45075</v>
@@ -8898,15 +8904,15 @@
         <v>57.11</v>
       </c>
       <c r="H298" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I298" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B299" s="2">
         <v>45075</v>
@@ -8927,15 +8933,15 @@
         <v>57.4</v>
       </c>
       <c r="H299" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I299" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B300" s="2">
         <v>45075</v>
@@ -8956,15 +8962,15 @@
         <v>57.69</v>
       </c>
       <c r="H300" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I300" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B301" s="2">
         <v>45075</v>
@@ -8985,15 +8991,15 @@
         <v>56.82</v>
       </c>
       <c r="H301" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I301" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B302" s="2">
         <v>45075</v>
@@ -9014,15 +9020,15 @@
         <v>54.61</v>
       </c>
       <c r="H302" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I302" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B303" s="2">
         <v>45075</v>
@@ -9043,15 +9049,15 @@
         <v>57.11</v>
       </c>
       <c r="H303" t="s">
+        <v>9</v>
+      </c>
+      <c r="I303" t="s">
         <v>15</v>
-      </c>
-      <c r="I303" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B304" s="2">
         <v>45075</v>
@@ -9072,15 +9078,15 @@
         <v>57.11</v>
       </c>
       <c r="H304" t="s">
+        <v>9</v>
+      </c>
+      <c r="I304" t="s">
         <v>15</v>
-      </c>
-      <c r="I304" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B305" s="2">
         <v>45075</v>
@@ -9101,15 +9107,15 @@
         <v>57.11</v>
       </c>
       <c r="H305" t="s">
+        <v>9</v>
+      </c>
+      <c r="I305" t="s">
         <v>15</v>
-      </c>
-      <c r="I305" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B306" s="2">
         <v>45075</v>
@@ -9130,15 +9136,15 @@
         <v>56.82</v>
       </c>
       <c r="H306" t="s">
+        <v>9</v>
+      </c>
+      <c r="I306" t="s">
         <v>15</v>
-      </c>
-      <c r="I306" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B307" s="2">
         <v>45075</v>
@@ -9159,15 +9165,15 @@
         <v>57.11</v>
       </c>
       <c r="H307" t="s">
+        <v>9</v>
+      </c>
+      <c r="I307" t="s">
         <v>15</v>
-      </c>
-      <c r="I307" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B308" s="2">
         <v>45075</v>
@@ -9188,15 +9194,15 @@
         <v>56.82</v>
       </c>
       <c r="H308" t="s">
+        <v>9</v>
+      </c>
+      <c r="I308" t="s">
         <v>15</v>
-      </c>
-      <c r="I308" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B309" s="2">
         <v>45075</v>
@@ -9217,15 +9223,15 @@
         <v>56.82</v>
       </c>
       <c r="H309" t="s">
+        <v>9</v>
+      </c>
+      <c r="I309" t="s">
         <v>15</v>
-      </c>
-      <c r="I309" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B310" s="2">
         <v>45075</v>
@@ -9246,15 +9252,15 @@
         <v>56.25</v>
       </c>
       <c r="H310" t="s">
+        <v>9</v>
+      </c>
+      <c r="I310" t="s">
         <v>15</v>
-      </c>
-      <c r="I310" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B311" s="2">
         <v>45075</v>
@@ -9275,15 +9281,15 @@
         <v>56.53</v>
       </c>
       <c r="H311" t="s">
+        <v>9</v>
+      </c>
+      <c r="I311" t="s">
         <v>15</v>
-      </c>
-      <c r="I311" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B312" s="2">
         <v>45075</v>
@@ -9304,15 +9310,15 @@
         <v>54.35</v>
       </c>
       <c r="H312" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I312" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B313" s="2">
         <v>45075</v>
@@ -9333,15 +9339,15 @@
         <v>55.42</v>
       </c>
       <c r="H313" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I313" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B314" s="2">
         <v>45075</v>
@@ -9362,15 +9368,15 @@
         <v>52.33</v>
       </c>
       <c r="H314" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I314" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B315" s="2">
         <v>45075</v>
@@ -9391,15 +9397,15 @@
         <v>55.42</v>
       </c>
       <c r="H315" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I315" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B316" s="2">
         <v>45075</v>
@@ -9420,15 +9426,15 @@
         <v>57.11</v>
       </c>
       <c r="H316" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I316" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B317" s="2">
         <v>45075</v>
@@ -9449,15 +9455,15 @@
         <v>57.69</v>
       </c>
       <c r="H317" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I317" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B318" s="2">
         <v>45075</v>
@@ -9478,15 +9484,15 @@
         <v>56.82</v>
       </c>
       <c r="H318" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I318" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B319" s="2">
         <v>45075</v>
@@ -9507,15 +9513,15 @@
         <v>57.11</v>
       </c>
       <c r="H319" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I319" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B320" s="2">
         <v>45075</v>
@@ -9536,15 +9542,15 @@
         <v>57.4</v>
       </c>
       <c r="H320" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I320" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B321" s="2">
         <v>45075</v>
@@ -9565,15 +9571,15 @@
         <v>52.57</v>
       </c>
       <c r="H321" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I321" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B322" s="2">
         <v>45075</v>
@@ -9594,15 +9600,15 @@
         <v>24.67</v>
       </c>
       <c r="H322" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I322" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B323" s="2">
         <v>45075</v>
@@ -9623,15 +9629,15 @@
         <v>44.82</v>
       </c>
       <c r="H323" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I323" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B324" s="2">
         <v>45075</v>
@@ -9652,15 +9658,15 @@
         <v>51.61</v>
       </c>
       <c r="H324" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I324" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B325" s="2">
         <v>45075</v>
@@ -9681,15 +9687,15 @@
         <v>54.09</v>
       </c>
       <c r="H325" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I325" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B326" s="2">
         <v>45075</v>
@@ -9710,15 +9716,15 @@
         <v>55.69</v>
       </c>
       <c r="H326" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I326" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B327" s="2">
         <v>45075</v>
@@ -9739,15 +9745,15 @@
         <v>56.53</v>
       </c>
       <c r="H327" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I327" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B328" s="2">
         <v>45075</v>
@@ -9768,15 +9774,15 @@
         <v>57.4</v>
       </c>
       <c r="H328" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I328" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B329" s="2">
         <v>45075</v>
@@ -9797,15 +9803,15 @@
         <v>57.69</v>
       </c>
       <c r="H329" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I329" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B330" s="2">
         <v>45075</v>
@@ -9826,15 +9832,15 @@
         <v>55.97</v>
       </c>
       <c r="H330" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I330" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B331" s="2">
         <v>45075</v>
@@ -9855,15 +9861,15 @@
         <v>57.99</v>
       </c>
       <c r="H331" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I331" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B332" s="2">
         <v>45075</v>
@@ -9884,15 +9890,15 @@
         <v>58.9</v>
       </c>
       <c r="H332" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I332" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B333" s="2">
         <v>45075</v>
@@ -9913,15 +9919,15 @@
         <v>58.9</v>
       </c>
       <c r="H333" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I333" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B334" s="2">
         <v>45075</v>
@@ -9942,15 +9948,15 @@
         <v>58.29</v>
       </c>
       <c r="H334" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I334" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B335" s="2">
         <v>45075</v>
@@ -9971,15 +9977,15 @@
         <v>57.99</v>
       </c>
       <c r="H335" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I335" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B336" s="2">
         <v>45075</v>
@@ -10000,15 +10006,15 @@
         <v>58.29</v>
       </c>
       <c r="H336" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I336" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B337" s="2">
         <v>45075</v>
@@ -10029,15 +10035,15 @@
         <v>58.29</v>
       </c>
       <c r="H337" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I337" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B338" s="2">
         <v>45075</v>
@@ -10058,15 +10064,15 @@
         <v>56.25</v>
       </c>
       <c r="H338" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I338" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B339" s="2">
         <v>45075</v>
@@ -10087,15 +10093,15 @@
         <v>57.69</v>
       </c>
       <c r="H339" t="s">
+        <v>9</v>
+      </c>
+      <c r="I339" t="s">
         <v>15</v>
-      </c>
-      <c r="I339" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B340" s="2">
         <v>45075</v>
@@ -10116,15 +10122,15 @@
         <v>58.9</v>
       </c>
       <c r="H340" t="s">
+        <v>9</v>
+      </c>
+      <c r="I340" t="s">
         <v>15</v>
-      </c>
-      <c r="I340" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B341" s="2">
         <v>45075</v>
@@ -10145,15 +10151,15 @@
         <v>59.21</v>
       </c>
       <c r="H341" t="s">
+        <v>9</v>
+      </c>
+      <c r="I341" t="s">
         <v>15</v>
-      </c>
-      <c r="I341" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B342" s="2">
         <v>45075</v>
@@ -10174,15 +10180,15 @@
         <v>59.21</v>
       </c>
       <c r="H342" t="s">
+        <v>9</v>
+      </c>
+      <c r="I342" t="s">
         <v>15</v>
-      </c>
-      <c r="I342" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B343" s="2">
         <v>45075</v>
@@ -10203,15 +10209,15 @@
         <v>58.9</v>
       </c>
       <c r="H343" t="s">
+        <v>9</v>
+      </c>
+      <c r="I343" t="s">
         <v>15</v>
-      </c>
-      <c r="I343" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B344" s="2">
         <v>45075</v>
@@ -10232,15 +10238,15 @@
         <v>59.21</v>
       </c>
       <c r="H344" t="s">
+        <v>9</v>
+      </c>
+      <c r="I344" t="s">
         <v>15</v>
-      </c>
-      <c r="I344" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B345" s="2">
         <v>45075</v>
@@ -10261,15 +10267,15 @@
         <v>59.52</v>
       </c>
       <c r="H345" t="s">
+        <v>9</v>
+      </c>
+      <c r="I345" t="s">
         <v>15</v>
-      </c>
-      <c r="I345" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B346" s="2">
         <v>45075</v>
@@ -10290,15 +10296,15 @@
         <v>57.11</v>
       </c>
       <c r="H346" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I346" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B347" s="2">
         <v>45075</v>
@@ -10319,15 +10325,15 @@
         <v>58.29</v>
       </c>
       <c r="H347" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I347" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B348" s="2">
         <v>45075</v>
@@ -10348,15 +10354,15 @@
         <v>58.9</v>
       </c>
       <c r="H348" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I348" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B349" s="2">
         <v>45075</v>
@@ -10377,15 +10383,15 @@
         <v>58.59</v>
       </c>
       <c r="H349" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I349" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B350" s="2">
         <v>45075</v>
@@ -10406,15 +10412,15 @@
         <v>58.9</v>
       </c>
       <c r="H350" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I350" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B351" s="2">
         <v>45075</v>
@@ -10435,15 +10441,15 @@
         <v>57.4</v>
       </c>
       <c r="H351" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I351" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B352" s="2">
         <v>45075</v>
@@ -10464,15 +10470,15 @@
         <v>58.29</v>
       </c>
       <c r="H352" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I352" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B353" s="2">
         <v>45075</v>
@@ -10493,15 +10499,15 @@
         <v>58.29</v>
       </c>
       <c r="H353" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I353" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B354" s="2">
         <v>45075</v>
@@ -10522,15 +10528,15 @@
         <v>56.53</v>
       </c>
       <c r="H354" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I354" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B355" s="2">
         <v>45075</v>
@@ -10551,15 +10557,15 @@
         <v>58.59</v>
       </c>
       <c r="H355" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I355" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B356" s="2">
         <v>45075</v>
@@ -10580,15 +10586,15 @@
         <v>58.9</v>
       </c>
       <c r="H356" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I356" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B357" s="2">
         <v>45075</v>
@@ -10609,15 +10615,15 @@
         <v>58.59</v>
       </c>
       <c r="H357" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I357" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B358" s="2">
         <v>45075</v>
@@ -10638,15 +10644,15 @@
         <v>56.53</v>
       </c>
       <c r="H358" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I358" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B359" s="2">
         <v>45075</v>
@@ -10667,15 +10673,15 @@
         <v>58.29</v>
       </c>
       <c r="H359" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I359" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B360" s="2">
         <v>45075</v>
@@ -10696,15 +10702,15 @@
         <v>58.29</v>
       </c>
       <c r="H360" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I360" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B361" s="2">
         <v>45075</v>
@@ -10725,15 +10731,15 @@
         <v>58.59</v>
       </c>
       <c r="H361" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I361" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B362" s="2">
         <v>45075</v>
@@ -10754,15 +10760,15 @@
         <v>57.99</v>
       </c>
       <c r="H362" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I362" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B363" s="2">
         <v>45075</v>
@@ -10783,15 +10789,15 @@
         <v>57.69</v>
       </c>
       <c r="H363" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I363" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B364" s="2">
         <v>45075</v>
@@ -10812,15 +10818,15 @@
         <v>57.69</v>
       </c>
       <c r="H364" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I364" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B365" s="2">
         <v>45075</v>
@@ -10841,15 +10847,15 @@
         <v>57.99</v>
       </c>
       <c r="H365" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I365" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B366" s="2">
         <v>45075</v>
@@ -10870,15 +10876,15 @@
         <v>56.25</v>
       </c>
       <c r="H366" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I366" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B367" s="2">
         <v>45075</v>
@@ -10899,15 +10905,15 @@
         <v>57.99</v>
       </c>
       <c r="H367" t="s">
+        <v>9</v>
+      </c>
+      <c r="I367" t="s">
         <v>15</v>
-      </c>
-      <c r="I367" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B368" s="2">
         <v>45075</v>
@@ -10928,15 +10934,15 @@
         <v>58.9</v>
       </c>
       <c r="H368" t="s">
+        <v>9</v>
+      </c>
+      <c r="I368" t="s">
         <v>15</v>
-      </c>
-      <c r="I368" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B369" s="2">
         <v>45075</v>
@@ -10957,15 +10963,15 @@
         <v>59.52</v>
       </c>
       <c r="H369" t="s">
+        <v>9</v>
+      </c>
+      <c r="I369" t="s">
         <v>15</v>
-      </c>
-      <c r="I369" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B370" s="2">
         <v>45075</v>
@@ -10986,15 +10992,15 @@
         <v>59.52</v>
       </c>
       <c r="H370" t="s">
+        <v>9</v>
+      </c>
+      <c r="I370" t="s">
         <v>15</v>
-      </c>
-      <c r="I370" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B371" s="2">
         <v>45075</v>
@@ -11015,15 +11021,15 @@
         <v>58.9</v>
       </c>
       <c r="H371" t="s">
+        <v>9</v>
+      </c>
+      <c r="I371" t="s">
         <v>15</v>
-      </c>
-      <c r="I371" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B372" s="2">
         <v>45075</v>
@@ -11044,15 +11050,15 @@
         <v>58.9</v>
       </c>
       <c r="H372" t="s">
+        <v>9</v>
+      </c>
+      <c r="I372" t="s">
         <v>15</v>
-      </c>
-      <c r="I372" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B373" s="2">
         <v>45075</v>
@@ -11073,15 +11079,15 @@
         <v>59.21</v>
       </c>
       <c r="H373" t="s">
+        <v>9</v>
+      </c>
+      <c r="I373" t="s">
         <v>15</v>
-      </c>
-      <c r="I373" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B374" s="2">
         <v>45075</v>
@@ -11102,15 +11108,15 @@
         <v>56.82</v>
       </c>
       <c r="H374" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I374" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B375" s="2">
         <v>45075</v>
@@ -11131,15 +11137,15 @@
         <v>58.9</v>
       </c>
       <c r="H375" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I375" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B376" s="2">
         <v>45075</v>
@@ -11160,15 +11166,15 @@
         <v>58.59</v>
       </c>
       <c r="H376" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I376" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B377" s="2">
         <v>45075</v>
@@ -11189,15 +11195,15 @@
         <v>57.69</v>
       </c>
       <c r="H377" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I377" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B378" s="2">
         <v>45075</v>
@@ -11218,15 +11224,15 @@
         <v>56.25</v>
       </c>
       <c r="H378" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I378" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B379" s="2">
         <v>45075</v>
@@ -11247,15 +11253,15 @@
         <v>57.99</v>
       </c>
       <c r="H379" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I379" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B380" s="2">
         <v>45075</v>
@@ -11276,15 +11282,15 @@
         <v>58.59</v>
       </c>
       <c r="H380" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I380" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B381" s="2">
         <v>45075</v>
@@ -11305,15 +11311,15 @@
         <v>59.52</v>
       </c>
       <c r="H381" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I381" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B382" s="2">
         <v>45075</v>
@@ -11334,15 +11340,15 @@
         <v>59.21</v>
       </c>
       <c r="H382" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I382" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B383" s="2">
         <v>45075</v>
@@ -11363,15 +11369,15 @@
         <v>59.21</v>
       </c>
       <c r="H383" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I383" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B384" s="2">
         <v>45075</v>
@@ -11392,15 +11398,15 @@
         <v>58.59</v>
       </c>
       <c r="H384" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I384" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B385" s="2">
         <v>45075</v>
@@ -11421,13 +11427,14 @@
         <v>54.88</v>
       </c>
       <c r="H385" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I385" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/TP_Master.xlsx
+++ b/pages/TP_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA9002C-8685-4277-8E57-B96CAC51E0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C9F875-B896-4364-97A0-B383E58578C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="32">
   <si>
     <t>Title</t>
   </si>
@@ -96,6 +96,27 @@
   <si>
     <t>2023 Cairo NC NZL WTP Final</t>
   </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>https://youtu.be/36hx4KwX5BQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/3mlXc7RP4VU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/IW_hEMwb4vo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/bT1lvX9hQsY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/oySGIhmjh9U</t>
+  </si>
+  <si>
+    <t>https://youtu.be/tnM5oUI2bqk</t>
+  </si>
 </sst>
 </file>
 
@@ -104,7 +125,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,6 +147,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -135,7 +164,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -158,18 +187,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -506,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I385"/>
+  <dimension ref="A1:J385"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.33203125" bestFit="1" customWidth="1"/>
@@ -518,9 +564,10 @@
     <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,8 +595,11 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -577,8 +627,11 @@
       <c r="I2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -607,7 +660,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -636,7 +689,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -665,7 +718,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -694,7 +747,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -723,7 +776,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -752,7 +805,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -781,7 +834,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -810,7 +863,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -839,7 +892,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -868,7 +921,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -897,7 +950,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -926,7 +979,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -955,7 +1008,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -2376,7 +2429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -2405,7 +2458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>20</v>
       </c>
@@ -2433,8 +2486,11 @@
       <c r="I66" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J66" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>20</v>
       </c>
@@ -2463,7 +2519,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>20</v>
       </c>
@@ -2492,7 +2548,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>20</v>
       </c>
@@ -2521,7 +2577,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>20</v>
       </c>
@@ -2550,7 +2606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>20</v>
       </c>
@@ -2579,7 +2635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>20</v>
       </c>
@@ -2608,7 +2664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>20</v>
       </c>
@@ -2637,7 +2693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>20</v>
       </c>
@@ -2666,7 +2722,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>20</v>
       </c>
@@ -2695,7 +2751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>20</v>
       </c>
@@ -2724,7 +2780,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>20</v>
       </c>
@@ -2753,7 +2809,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>20</v>
       </c>
@@ -2782,7 +2838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>20</v>
       </c>
@@ -2811,7 +2867,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>20</v>
       </c>
@@ -4232,7 +4288,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>20</v>
       </c>
@@ -4261,7 +4317,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>21</v>
       </c>
@@ -4289,8 +4345,11 @@
       <c r="I130" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J130" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>21</v>
       </c>
@@ -4319,7 +4378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>21</v>
       </c>
@@ -4348,7 +4407,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>21</v>
       </c>
@@ -4377,7 +4436,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>21</v>
       </c>
@@ -4406,7 +4465,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>21</v>
       </c>
@@ -4435,7 +4494,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>21</v>
       </c>
@@ -4464,7 +4523,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>21</v>
       </c>
@@ -4493,7 +4552,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>21</v>
       </c>
@@ -4522,7 +4581,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>21</v>
       </c>
@@ -4551,7 +4610,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>21</v>
       </c>
@@ -4580,7 +4639,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>21</v>
       </c>
@@ -4609,7 +4668,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>21</v>
       </c>
@@ -4638,7 +4697,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>21</v>
       </c>
@@ -4667,7 +4726,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>21</v>
       </c>
@@ -6088,7 +6147,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>21</v>
       </c>
@@ -6117,7 +6176,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>22</v>
       </c>
@@ -6145,8 +6204,11 @@
       <c r="I194" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J194" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>22</v>
       </c>
@@ -6175,7 +6237,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>22</v>
       </c>
@@ -6204,7 +6266,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>22</v>
       </c>
@@ -6233,7 +6295,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>22</v>
       </c>
@@ -6262,7 +6324,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>22</v>
       </c>
@@ -6291,7 +6353,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>22</v>
       </c>
@@ -6320,7 +6382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>22</v>
       </c>
@@ -6349,7 +6411,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>22</v>
       </c>
@@ -6378,7 +6440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>22</v>
       </c>
@@ -6407,7 +6469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>22</v>
       </c>
@@ -6436,7 +6498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>22</v>
       </c>
@@ -6465,7 +6527,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>22</v>
       </c>
@@ -6494,7 +6556,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>22</v>
       </c>
@@ -6523,7 +6585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>22</v>
       </c>
@@ -7710,7 +7772,7 @@
         <v>3937.5</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>22</v>
       </c>
@@ -7721,7 +7783,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>23</v>
       </c>
@@ -7749,8 +7811,11 @@
       <c r="I258" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J258" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>23</v>
       </c>
@@ -7779,7 +7844,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>23</v>
       </c>
@@ -7808,7 +7873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>23</v>
       </c>
@@ -7837,7 +7902,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>23</v>
       </c>
@@ -7866,7 +7931,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>23</v>
       </c>
@@ -7895,7 +7960,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>23</v>
       </c>
@@ -7924,7 +7989,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>23</v>
       </c>
@@ -7953,7 +8018,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>23</v>
       </c>
@@ -7982,7 +8047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>23</v>
       </c>
@@ -8011,7 +8076,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>23</v>
       </c>
@@ -8040,7 +8105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>23</v>
       </c>
@@ -8069,7 +8134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>23</v>
       </c>
@@ -8098,7 +8163,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>23</v>
       </c>
@@ -8127,7 +8192,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>23</v>
       </c>
@@ -9548,7 +9613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>23</v>
       </c>
@@ -9577,7 +9642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>24</v>
       </c>
@@ -9605,8 +9670,11 @@
       <c r="I322" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J322" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>24</v>
       </c>
@@ -9635,7 +9703,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>24</v>
       </c>
@@ -9664,7 +9732,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>24</v>
       </c>
@@ -9693,7 +9761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>24</v>
       </c>
@@ -9722,7 +9790,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>24</v>
       </c>
@@ -9751,7 +9819,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>24</v>
       </c>
@@ -9780,7 +9848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>24</v>
       </c>
@@ -9809,7 +9877,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>24</v>
       </c>
@@ -9838,7 +9906,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>24</v>
       </c>
@@ -9867,7 +9935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>24</v>
       </c>
@@ -9896,7 +9964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>24</v>
       </c>
@@ -9925,7 +9993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>24</v>
       </c>
@@ -9954,7 +10022,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>24</v>
       </c>
@@ -9983,7 +10051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>24</v>
       </c>
@@ -11435,6 +11503,13 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="J130" r:id="rId1" xr:uid="{388F875D-EACB-43A9-B8DF-4CD5E396EAB3}"/>
+    <hyperlink ref="J258" r:id="rId2" xr:uid="{D272DCBE-F0BE-4E23-8F4F-D57B8C5AAF30}"/>
+    <hyperlink ref="J194" r:id="rId3" xr:uid="{BD2928A3-5321-4609-966A-E6AC05921DD3}"/>
+    <hyperlink ref="J322" r:id="rId4" xr:uid="{4E75736E-11E9-47F3-8583-8F07990508C7}"/>
+    <hyperlink ref="J66" r:id="rId5" xr:uid="{D62A3ECB-652B-4971-891C-4597D59BEB58}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/TP_Master.xlsx
+++ b/pages/TP_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B229CE8-4EC8-435D-9C08-9C76F0376DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCCACD9-1896-42CC-9930-DBE820B5EBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,7 +146,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +168,12 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -6181,7 +6187,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B194" s="2">
         <v>45075</v>
@@ -6213,7 +6219,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B195" s="2">
         <v>45075</v>
@@ -6242,7 +6248,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B196" s="2">
         <v>45075</v>
@@ -6271,7 +6277,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B197" s="2">
         <v>45075</v>
@@ -6300,7 +6306,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B198" s="2">
         <v>45075</v>
@@ -6329,7 +6335,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B199" s="2">
         <v>45075</v>
@@ -6358,7 +6364,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B200" s="2">
         <v>45075</v>
@@ -6387,7 +6393,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B201" s="2">
         <v>45075</v>
@@ -6416,7 +6422,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B202" s="2">
         <v>45075</v>
@@ -6445,7 +6451,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B203" s="2">
         <v>45075</v>
@@ -6474,7 +6480,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B204" s="2">
         <v>45075</v>
@@ -6503,7 +6509,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B205" s="2">
         <v>45075</v>
@@ -6532,7 +6538,7 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B206" s="2">
         <v>45075</v>
@@ -6561,7 +6567,7 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B207" s="2">
         <v>45075</v>
@@ -6590,7 +6596,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B208" s="2">
         <v>45075</v>
@@ -6619,7 +6625,7 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B209" s="2">
         <v>45075</v>
@@ -6648,7 +6654,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B210" s="2">
         <v>45075</v>
@@ -6677,7 +6683,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B211" s="2">
         <v>45075</v>
@@ -6706,7 +6712,7 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B212" s="2">
         <v>45075</v>
@@ -6735,7 +6741,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B213" s="2">
         <v>45075</v>
@@ -6764,7 +6770,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B214" s="2">
         <v>45075</v>
@@ -6793,7 +6799,7 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B215" s="2">
         <v>45075</v>
@@ -6822,7 +6828,7 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B216" s="2">
         <v>45075</v>
@@ -6851,7 +6857,7 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B217" s="2">
         <v>45075</v>
@@ -6880,7 +6886,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B218" s="2">
         <v>45075</v>
@@ -6909,7 +6915,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B219" s="2">
         <v>45075</v>
@@ -6938,7 +6944,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B220" s="2">
         <v>45075</v>
@@ -6967,7 +6973,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B221" s="2">
         <v>45075</v>
@@ -6991,12 +6997,12 @@
         <v>18</v>
       </c>
       <c r="I221" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B222" s="2">
         <v>45075</v>
@@ -7020,12 +7026,12 @@
         <v>18</v>
       </c>
       <c r="I222" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B223" s="2">
         <v>45075</v>
@@ -7049,12 +7055,12 @@
         <v>18</v>
       </c>
       <c r="I223" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B224" s="2">
         <v>45075</v>
@@ -7078,12 +7084,12 @@
         <v>18</v>
       </c>
       <c r="I224" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B225" s="2">
         <v>45075</v>
@@ -7107,12 +7113,12 @@
         <v>18</v>
       </c>
       <c r="I225" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B226" s="2">
         <v>45075</v>
@@ -7136,12 +7142,12 @@
         <v>18</v>
       </c>
       <c r="I226" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B227" s="2">
         <v>45075</v>
@@ -7165,12 +7171,12 @@
         <v>18</v>
       </c>
       <c r="I227" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B228" s="2">
         <v>45075</v>
@@ -7194,12 +7200,12 @@
         <v>19</v>
       </c>
       <c r="I228" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B229" s="2">
         <v>45075</v>
@@ -7228,7 +7234,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B230" s="2">
         <v>45075</v>
@@ -7257,7 +7263,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B231" s="2">
         <v>45075</v>
@@ -7286,7 +7292,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B232" s="2">
         <v>45075</v>
@@ -7315,7 +7321,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B233" s="2">
         <v>45075</v>
@@ -7344,7 +7350,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B234" s="2">
         <v>45075</v>
@@ -7373,7 +7379,7 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B235" s="2">
         <v>45075</v>
@@ -7402,7 +7408,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B236" s="2">
         <v>45075</v>
@@ -7431,7 +7437,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B237" s="2">
         <v>45075</v>
@@ -7460,7 +7466,7 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B238" s="2">
         <v>45075</v>
@@ -7489,7 +7495,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B239" s="2">
         <v>45075</v>
@@ -7518,7 +7524,7 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B240" s="2">
         <v>45075</v>
@@ -7547,7 +7553,7 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B241" s="2">
         <v>45075</v>
@@ -7576,7 +7582,7 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B242" s="2">
         <v>45075</v>
@@ -7605,7 +7611,7 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B243" s="2">
         <v>45075</v>
@@ -7634,7 +7640,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B244" s="2">
         <v>45075</v>
@@ -7645,7 +7651,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B245" s="2">
         <v>45075</v>
@@ -7656,7 +7662,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B246" s="2">
         <v>45075</v>
@@ -7667,7 +7673,7 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B247" s="2">
         <v>45075</v>
@@ -7678,7 +7684,7 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B248" s="2">
         <v>45075</v>
@@ -7689,7 +7695,7 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B249" s="2">
         <v>45075</v>
@@ -7700,7 +7706,7 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B250" s="2">
         <v>45075</v>
@@ -7711,7 +7717,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B251" s="2">
         <v>45075</v>
@@ -7722,7 +7728,7 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B252" s="2">
         <v>45075</v>
@@ -7733,7 +7739,7 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B253" s="2">
         <v>45075</v>
@@ -7744,7 +7750,7 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B254" s="2">
         <v>45075</v>
@@ -7755,7 +7761,7 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B255" s="2">
         <v>45075</v>
@@ -7766,7 +7772,7 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B256" s="2">
         <v>45075</v>
@@ -7777,7 +7783,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B257" s="2">
         <v>45075</v>
@@ -7788,7 +7794,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B258" s="2">
         <v>45075</v>
@@ -7820,7 +7826,7 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B259" s="2">
         <v>45075</v>
@@ -7849,7 +7855,7 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B260" s="2">
         <v>45075</v>
@@ -7878,7 +7884,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B261" s="2">
         <v>45075</v>
@@ -7907,7 +7913,7 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B262" s="2">
         <v>45075</v>
@@ -7936,7 +7942,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B263" s="2">
         <v>45075</v>
@@ -7965,7 +7971,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B264" s="2">
         <v>45075</v>
@@ -7994,7 +8000,7 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B265" s="2">
         <v>45075</v>
@@ -8023,7 +8029,7 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B266" s="2">
         <v>45075</v>
@@ -8052,7 +8058,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B267" s="2">
         <v>45075</v>
@@ -8081,7 +8087,7 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B268" s="2">
         <v>45075</v>
@@ -8110,7 +8116,7 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B269" s="2">
         <v>45075</v>
@@ -8139,7 +8145,7 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B270" s="2">
         <v>45075</v>
@@ -8168,7 +8174,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B271" s="2">
         <v>45075</v>
@@ -8197,7 +8203,7 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B272" s="2">
         <v>45075</v>
@@ -8226,7 +8232,7 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B273" s="2">
         <v>45075</v>
@@ -8255,7 +8261,7 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B274" s="2">
         <v>45075</v>
@@ -8284,7 +8290,7 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B275" s="2">
         <v>45075</v>
@@ -8313,7 +8319,7 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B276" s="2">
         <v>45075</v>
@@ -8342,7 +8348,7 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B277" s="2">
         <v>45075</v>
@@ -8371,7 +8377,7 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B278" s="2">
         <v>45075</v>
@@ -8400,7 +8406,7 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B279" s="2">
         <v>45075</v>
@@ -8429,7 +8435,7 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B280" s="2">
         <v>45075</v>
@@ -8458,7 +8464,7 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B281" s="2">
         <v>45075</v>
@@ -8487,7 +8493,7 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B282" s="2">
         <v>45075</v>
@@ -8516,7 +8522,7 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B283" s="2">
         <v>45075</v>
@@ -8545,7 +8551,7 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B284" s="2">
         <v>45075</v>
@@ -8574,7 +8580,7 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B285" s="2">
         <v>45075</v>
@@ -8598,12 +8604,12 @@
         <v>18</v>
       </c>
       <c r="I285" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B286" s="2">
         <v>45075</v>
@@ -8627,12 +8633,12 @@
         <v>18</v>
       </c>
       <c r="I286" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B287" s="2">
         <v>45075</v>
@@ -8656,12 +8662,12 @@
         <v>18</v>
       </c>
       <c r="I287" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B288" s="2">
         <v>45075</v>
@@ -8685,12 +8691,12 @@
         <v>18</v>
       </c>
       <c r="I288" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B289" s="2">
         <v>45075</v>
@@ -8714,12 +8720,12 @@
         <v>18</v>
       </c>
       <c r="I289" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B290" s="2">
         <v>45075</v>
@@ -8743,12 +8749,12 @@
         <v>19</v>
       </c>
       <c r="I290" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B291" s="2">
         <v>45075</v>
@@ -8777,7 +8783,7 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B292" s="2">
         <v>45075</v>
@@ -8806,7 +8812,7 @@
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B293" s="2">
         <v>45075</v>
@@ -8835,7 +8841,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B294" s="2">
         <v>45075</v>
@@ -8864,7 +8870,7 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B295" s="2">
         <v>45075</v>
@@ -8893,7 +8899,7 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B296" s="2">
         <v>45075</v>
@@ -8922,7 +8928,7 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B297" s="2">
         <v>45075</v>
@@ -8951,7 +8957,7 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B298" s="2">
         <v>45075</v>
@@ -8980,7 +8986,7 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B299" s="2">
         <v>45075</v>
@@ -9009,7 +9015,7 @@
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B300" s="2">
         <v>45075</v>
@@ -9038,7 +9044,7 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B301" s="2">
         <v>45075</v>
@@ -9067,7 +9073,7 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B302" s="2">
         <v>45075</v>
@@ -9096,7 +9102,7 @@
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B303" s="2">
         <v>45075</v>
@@ -9125,7 +9131,7 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B304" s="2">
         <v>45075</v>
@@ -9154,7 +9160,7 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B305" s="2">
         <v>45075</v>
@@ -9183,7 +9189,7 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B306" s="2">
         <v>45075</v>
@@ -9212,7 +9218,7 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B307" s="2">
         <v>45075</v>
@@ -9241,7 +9247,7 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B308" s="2">
         <v>45075</v>
@@ -9270,7 +9276,7 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B309" s="2">
         <v>45075</v>
@@ -9299,7 +9305,7 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B310" s="2">
         <v>45075</v>
@@ -9328,7 +9334,7 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B311" s="2">
         <v>45075</v>
@@ -9357,7 +9363,7 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B312" s="2">
         <v>45075</v>
@@ -9386,7 +9392,7 @@
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B313" s="2">
         <v>45075</v>
@@ -9410,12 +9416,12 @@
         <v>18</v>
       </c>
       <c r="I313" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B314" s="2">
         <v>45075</v>
@@ -9439,12 +9445,12 @@
         <v>19</v>
       </c>
       <c r="I314" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B315" s="2">
         <v>45075</v>
@@ -9473,7 +9479,7 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B316" s="2">
         <v>45075</v>
@@ -9502,7 +9508,7 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B317" s="2">
         <v>45075</v>
@@ -9531,7 +9537,7 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B318" s="2">
         <v>45075</v>
@@ -9560,7 +9566,7 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B319" s="2">
         <v>45075</v>
@@ -9589,7 +9595,7 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B320" s="2">
         <v>45075</v>
@@ -9618,7 +9624,7 @@
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B321" s="2">
         <v>45075</v>
@@ -15223,6 +15229,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="J66" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/pages/TP_Master.xlsx
+++ b/pages/TP_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCCACD9-1896-42CC-9930-DBE820B5EBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E44724-CC4C-4EEF-BC3C-40C05ADDA497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10605,7 +10605,7 @@
         <v>56.53</v>
       </c>
       <c r="H354" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I354" t="s">
         <v>26</v>
